--- a/publications.xlsx
+++ b/publications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF6547B-5CB7-4DBC-A57F-33DAAF879FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DD225E-A429-47BE-9FBD-3AF1011DDA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="papers" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3556" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="1524">
   <si>
     <t>title</t>
   </si>
@@ -3836,9 +3836,6 @@
     <t>J. Transp. Health</t>
   </si>
   <si>
-    <t>Vandeninden, Bram; Bouland, Catherine; Devleesschauwer, Brecht; Vanpoucke, Charlotte; Hooyberghs, Hans; Otavova, Martina; Faes, Christel; De Clercq, Eva M.</t>
-  </si>
-  <si>
     <t>Assessing mental health from registry data: What is the best proxy?</t>
   </si>
   <si>
@@ -3989,15 +3986,9 @@
     <t>Unravelling demographic and socioeconomic patterns of COVID-19 death and other causes of death: results of an individual-level analysis of exhaustive cause of death data in Belgium, 2020</t>
   </si>
   <si>
-    <t>Cannabis use is not associated with altered levels of physical activity. Evidence from  the Belgian Health Interview Survey</t>
-  </si>
-  <si>
     <t>Vernaillen, Brent; Devleesschauwer, Brecht; Vansteelandt, Stijn; Gisle, Lydia; Drieskens, Sabine; Damian, Elena</t>
   </si>
   <si>
-    <t>Addiction</t>
-  </si>
-  <si>
     <t>Cavillot, Lisa; Van den Borre, Laura; Vanthomme, Katrien; Scohy, Aline; Deboosere, Patrick; Devleesschauwer, Brecht; Speybroeck, Niko; Gadeyne, Sylvie</t>
   </si>
   <si>
@@ -4442,9 +4433,6 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/39708616/</t>
   </si>
   <si>
-    <t>The burden of disease attributable to high body mass index in Belgium: a comparative risk assessment analysis</t>
-  </si>
-  <si>
     <t>BMJ Public Health</t>
   </si>
   <si>
@@ -4551,6 +4539,72 @@
   </si>
   <si>
     <t>Colston, Josh M; Flynn, Thomas G; Denton, Andrea H; Schiaffino, Francesca; Majowicz, Shannon E; Devleesschauwer, Brecht; Di Bari, Carlotta; Minato, Yuki; Kosek, Margaret N</t>
+  </si>
+  <si>
+    <t>Assessing the burden of congenital toxoplasmosis in Burundi, 2020</t>
+  </si>
+  <si>
+    <t>Minani, Salvator; Di Bari, Carlotta; Devleesschauwer, Brecht; Gasogo, Anastasie; Ntirandekura, Jean-Bosco; Gabriël, Sarah; Trevisan, Chiara</t>
+  </si>
+  <si>
+    <t>Cannabis use is not associated with altered levels of physical activity: evidence from the repeated cross-sectional Belgian Health Interview Survey</t>
+  </si>
+  <si>
+    <t>Journal of Cannabis Research</t>
+  </si>
+  <si>
+    <t>J. Cannabis Res.</t>
+  </si>
+  <si>
+    <t>10.1186/s42238-025-00278-8</t>
+  </si>
+  <si>
+    <t>Burden of disease attributable to high body mass index in Belgium: a comparative risk assessment analysis</t>
+  </si>
+  <si>
+    <t>Vandeninden, Bram; Devleesschauwer, Brecht; Otavova, Martina; Vanpoucke, Charlotte; Hooyberghs, Hans; Faes, Christel; Bouland, Catherine; De Clercq, Eva M.</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-025-98123-8</t>
+  </si>
+  <si>
+    <t>e0012681</t>
+  </si>
+  <si>
+    <t>e093018</t>
+  </si>
+  <si>
+    <t>10.1136/bmjopen-2024-093018</t>
+  </si>
+  <si>
+    <t>Towards a burden of disease research agenda</t>
+  </si>
+  <si>
+    <t>Gorasso, Vanessa; Assunçao, Ricardo; Charalampous, Periklis; Haagsma, Juanita A; Hilderink, Henk; Santric-Milicevic, Milena; Pires, Sara Monteiro; Plass, Dietrich; von der Lippe, Elena; Wyper, Grant; Devleesschauwer, Brecht</t>
+  </si>
+  <si>
+    <t>The attributable burden of disease due to cigarette smoking in Belgium: mortality patterns and trends from 2013 to 2021</t>
+  </si>
+  <si>
+    <t>Burden of disease using Disability Adjusted Life Years in the Middle East and North Africa (MENA) region: protocol of a systematic review</t>
+  </si>
+  <si>
+    <t>Mathew, Simy; Rifai, R; Grivna, M; Ostlundh, Linda; Devleesschauwer, Brecht; Adam, Balazs</t>
+  </si>
+  <si>
+    <t>Nayani, Sarah; Guariguata, Leonor; Croes, Sarah; Schmidt, Masja; Gisle, Lydia; Vynckier, Pieter; Verhaeghe, Nick; De Pauw, Robby; Devleesschauwer, Brecht</t>
+  </si>
+  <si>
+    <t>Post-acute healthcare expenditure following COVID-19 hospitalization and associated social inequalities in Belgium: a matched cohort study</t>
+  </si>
+  <si>
+    <t>Years of life lost due to COVID-19 attributable to social deprivation in metropolitan France, 2020</t>
+  </si>
+  <si>
+    <t>Boiy, Elin; Cavillot, Lisa; Devleesschauwer, Brecht; De Pauw, Robby; De Smedt, Delphine; Gadeyne, Sylvie; Gorasso, Vanessa; Schmidt, Masja; Vanthomme, Katrien; Verhaege, Nick; Van den Borre, Laura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haneef, Romana; Mahrouseh, Nour; Bessonneau, Pascal; Vandentorren, Stephanie; Minier, Nicolas; Chin, Francis; Bruyère, Olivier; Devleesschauwer, Brecht; Wyper, Grant M A </t>
   </si>
 </sst>
 </file>
@@ -4892,86 +4946,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5135,6 +5109,86 @@
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5149,74 +5203,74 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U271" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:U271" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U270">
-    <sortCondition ref="K1:K270"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U273" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:U273" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U273">
+    <sortCondition ref="K1:K273"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="51"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="50" dataCellStyle="Neutral"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="47"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="46"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="45"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="44"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="43"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="42"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="43"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="42" dataCellStyle="Neutral"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="39"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="38"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="36"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="35"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="34"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="A1:J12" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N50">
     <sortCondition ref="H1:H50"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G19" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:G19" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G19">
-    <sortCondition ref="F1:F19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G23" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:G23" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
+    <sortCondition ref="F1:F23"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="13">
       <calculatedColumnFormula>TODAY()-F2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5225,18 +5279,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:F5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
     <sortCondition ref="E1:E14"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="5">
       <calculatedColumnFormula>(TODAY()-E2)/365</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5565,7 +5619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U271"/>
+  <dimension ref="A1:U273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -18880,7 +18934,7 @@
         <v>101</v>
       </c>
       <c r="H245" s="18" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="I245" s="18" t="s">
         <v>14</v>
@@ -18897,7 +18951,7 @@
       </c>
       <c r="N245" s="11"/>
       <c r="O245" s="19" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="P245" s="7"/>
       <c r="Q245" s="24"/>
@@ -18915,7 +18969,7 @@
         <v>1088</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>1138</v>
@@ -18933,7 +18987,7 @@
         <v>91</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="I246" s="18" t="s">
         <v>14</v>
@@ -18950,7 +19004,7 @@
       </c>
       <c r="N246" s="11"/>
       <c r="O246" s="19" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="P246" s="7"/>
       <c r="Q246" s="24"/>
@@ -18986,7 +19040,7 @@
         <v>125</v>
       </c>
       <c r="H247" s="18" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="I247" s="18" t="s">
         <v>14</v>
@@ -19003,7 +19057,7 @@
       </c>
       <c r="N247" s="11"/>
       <c r="O247" s="19" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="P247" s="7"/>
       <c r="Q247" s="24"/>
@@ -19056,7 +19110,7 @@
       </c>
       <c r="N248" s="11"/>
       <c r="O248" s="19" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="P248" s="7"/>
       <c r="Q248" s="24"/>
@@ -19109,7 +19163,7 @@
       </c>
       <c r="N249" s="11"/>
       <c r="O249" s="19" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="P249" s="7"/>
       <c r="Q249" s="24"/>
@@ -19162,7 +19216,7 @@
       </c>
       <c r="N250" s="11"/>
       <c r="O250" s="19" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="P250" s="7"/>
       <c r="Q250" s="24"/>
@@ -19215,7 +19269,7 @@
       </c>
       <c r="N251" s="11"/>
       <c r="O251" s="19" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="P251" s="7"/>
       <c r="Q251" s="24"/>
@@ -19230,10 +19284,10 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>668</v>
@@ -19268,7 +19322,7 @@
       </c>
       <c r="N252" s="11"/>
       <c r="O252" s="19" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="P252" s="7"/>
       <c r="Q252" s="24"/>
@@ -19286,7 +19340,7 @@
         <v>1136</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>89</v>
@@ -19321,7 +19375,7 @@
       </c>
       <c r="N253" s="11"/>
       <c r="O253" s="19" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="P253" s="7"/>
       <c r="Q253" s="24"/>
@@ -19336,7 +19390,7 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B254" s="7" t="s">
         <v>1262</v>
@@ -19374,7 +19428,7 @@
       </c>
       <c r="N254" s="11"/>
       <c r="O254" s="19" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="P254" s="7"/>
       <c r="Q254" s="24"/>
@@ -19389,10 +19443,10 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>813</v>
@@ -19427,7 +19481,7 @@
       </c>
       <c r="N255" s="11"/>
       <c r="O255" s="19" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="P255" s="7"/>
       <c r="Q255" s="24"/>
@@ -19480,7 +19534,7 @@
       </c>
       <c r="N256" s="11"/>
       <c r="O256" s="19" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="P256" s="7"/>
       <c r="Q256" s="24"/>
@@ -19495,7 +19549,7 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B257" s="7" t="s">
         <v>1063</v>
@@ -19533,7 +19587,7 @@
       </c>
       <c r="N257" s="11"/>
       <c r="O257" s="19" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="P257" s="7"/>
       <c r="Q257" s="24"/>
@@ -19548,10 +19602,10 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B258" s="7" t="s">
         <v>1275</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>1276</v>
       </c>
       <c r="C258" s="7" t="s">
         <v>108</v>
@@ -19586,7 +19640,7 @@
       </c>
       <c r="N258" s="11"/>
       <c r="O258" s="19" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="P258" s="7"/>
       <c r="Q258" s="24"/>
@@ -19601,16 +19655,16 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E259" s="18">
         <v>2024</v>
@@ -19639,7 +19693,7 @@
       </c>
       <c r="N259" s="11"/>
       <c r="O259" s="19" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="P259" s="7"/>
       <c r="Q259" s="24"/>
@@ -19654,16 +19708,16 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E260" s="18">
         <v>2024</v>
@@ -19675,7 +19729,7 @@
         <v>69</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="I260" s="18" t="s">
         <v>14</v>
@@ -19692,7 +19746,7 @@
       </c>
       <c r="N260" s="11"/>
       <c r="O260" s="19" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="P260" s="7"/>
       <c r="Q260" s="24"/>
@@ -19707,10 +19761,10 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C261" s="7" t="s">
         <v>267</v>
@@ -19745,7 +19799,7 @@
       </c>
       <c r="N261" s="11"/>
       <c r="O261" s="19" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="P261" s="7"/>
       <c r="Q261" s="24"/>
@@ -19798,7 +19852,7 @@
       </c>
       <c r="N262" s="11"/>
       <c r="O262" s="19" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="P262" s="7"/>
       <c r="Q262" s="24"/>
@@ -19813,16 +19867,16 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>1469</v>
+        <v>1508</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>1213</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="E263" s="18">
         <v>2025</v>
@@ -19834,7 +19888,7 @@
         <v>14</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="I263" s="18" t="s">
         <v>14</v>
@@ -19851,7 +19905,7 @@
       </c>
       <c r="N263" s="11"/>
       <c r="O263" s="19" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="P263" s="7"/>
       <c r="Q263" s="24"/>
@@ -19862,16 +19916,16 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="C264" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D264" s="7" t="s">
         <v>1289</v>
-      </c>
-      <c r="D264" s="7" t="s">
-        <v>1290</v>
       </c>
       <c r="E264" s="18">
         <v>2025</v>
@@ -19900,7 +19954,7 @@
       </c>
       <c r="N264" s="11"/>
       <c r="O264" s="19" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="P264" s="7"/>
       <c r="Q264" s="24"/>
@@ -19915,10 +19969,10 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B265" s="7" t="s">
         <v>1293</v>
-      </c>
-      <c r="B265" s="7" t="s">
-        <v>1294</v>
       </c>
       <c r="C265" s="7" t="s">
         <v>1138</v>
@@ -19936,7 +19990,7 @@
         <v>101</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="I265" s="18" t="s">
         <v>14</v>
@@ -19953,7 +20007,7 @@
       </c>
       <c r="N265" s="11"/>
       <c r="O265" s="19" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="P265" s="7"/>
       <c r="Q265" s="24"/>
@@ -19964,16 +20018,16 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>267</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="E266" s="18">
         <v>2025</v>
@@ -20002,7 +20056,7 @@
       </c>
       <c r="N266" s="11"/>
       <c r="O266" s="19" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="P266" s="7"/>
       <c r="Q266" s="24"/>
@@ -20013,10 +20067,10 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="B267" s="7" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="C267" s="7" t="s">
         <v>287</v>
@@ -20051,7 +20105,7 @@
       </c>
       <c r="N267" s="11"/>
       <c r="O267" s="19" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="P267" s="7"/>
       <c r="Q267" s="24"/>
@@ -20062,16 +20116,16 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="E268" s="18">
         <v>2025</v>
@@ -20086,10 +20140,10 @@
         <v>14</v>
       </c>
       <c r="I268" s="18" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="J268" s="18" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="K268" s="42">
         <v>45706</v>
@@ -20100,7 +20154,7 @@
       </c>
       <c r="N268" s="11"/>
       <c r="O268" s="19" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="P268" s="7"/>
       <c r="Q268" s="24"/>
@@ -20110,48 +20164,48 @@
       <c r="U268" s="7"/>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A269" s="13" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B269" s="13" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C269" s="13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D269" s="13" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E269" s="14">
-        <v>2024</v>
-      </c>
-      <c r="F269" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G269" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H269" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I269" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J269" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K269" s="31">
-        <v>46023</v>
-      </c>
-      <c r="L269" s="31"/>
-      <c r="M269" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N269" s="45"/>
-      <c r="O269" s="44" t="s">
-        <v>1265</v>
-      </c>
-      <c r="P269" s="27"/>
+      <c r="A269" s="7" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B269" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="D269" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="E269" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F269" s="18">
+        <v>15</v>
+      </c>
+      <c r="G269" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="H269" s="18" t="s">
+        <v>1512</v>
+      </c>
+      <c r="I269" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J269" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K269" s="42">
+        <v>45750</v>
+      </c>
+      <c r="L269" s="42"/>
+      <c r="M269" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N269" s="11"/>
+      <c r="O269" s="19" t="s">
+        <v>1513</v>
+      </c>
+      <c r="P269" s="7"/>
       <c r="Q269" s="24"/>
       <c r="R269" s="25"/>
       <c r="S269" s="7"/>
@@ -20159,46 +20213,48 @@
       <c r="U269" s="7"/>
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A270" s="13" t="s">
-        <v>1348</v>
-      </c>
-      <c r="B270" s="13" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C270" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D270" s="13" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E270" s="14">
+      <c r="A270" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E270" s="18">
         <v>2025</v>
       </c>
-      <c r="F270" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G270" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H270" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I270" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J270" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K270" s="31">
-        <v>46024</v>
-      </c>
-      <c r="L270" s="31"/>
-      <c r="M270" s="31"/>
-      <c r="N270" s="45"/>
-      <c r="O270" s="44" t="s">
-        <v>1501</v>
-      </c>
-      <c r="P270" s="27"/>
+      <c r="F270" s="18">
+        <v>15</v>
+      </c>
+      <c r="G270" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H270" s="18">
+        <v>13683</v>
+      </c>
+      <c r="I270" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J270" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K270" s="42">
+        <v>45768</v>
+      </c>
+      <c r="L270" s="42"/>
+      <c r="M270" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N270" s="11"/>
+      <c r="O270" s="19" t="s">
+        <v>1510</v>
+      </c>
+      <c r="P270" s="7"/>
       <c r="Q270" s="24"/>
       <c r="R270" s="25"/>
       <c r="S270" s="7"/>
@@ -20206,80 +20262,182 @@
       <c r="U270" s="7"/>
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A271" s="13" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B271" s="13" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C271" s="13" t="s">
-        <v>723</v>
-      </c>
-      <c r="D271" s="13" t="s">
-        <v>723</v>
-      </c>
-      <c r="E271" s="14">
+      <c r="A271" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B271" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C271" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E271" s="18">
         <v>2025</v>
       </c>
-      <c r="F271" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G271" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H271" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I271" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J271" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K271" s="31">
-        <v>46025</v>
-      </c>
-      <c r="L271" s="31"/>
-      <c r="M271" s="31"/>
-      <c r="N271" s="45"/>
-      <c r="O271" s="44"/>
-      <c r="P271" s="27"/>
+      <c r="F271" s="18">
+        <v>19</v>
+      </c>
+      <c r="G271" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="H271" s="18" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I271" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J271" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K271" s="42">
+        <v>45769</v>
+      </c>
+      <c r="L271" s="42"/>
+      <c r="M271" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N271" s="11"/>
+      <c r="O271" s="19" t="s">
+        <v>1497</v>
+      </c>
+      <c r="P271" s="7"/>
       <c r="Q271" s="24"/>
       <c r="R271" s="25"/>
       <c r="S271" s="7"/>
       <c r="T271" s="7"/>
       <c r="U271" s="7"/>
     </row>
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A272" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B272" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E272" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F272" s="18">
+        <v>7</v>
+      </c>
+      <c r="G272" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H272" s="18">
+        <v>22</v>
+      </c>
+      <c r="I272" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J272" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K272" s="42">
+        <v>45772</v>
+      </c>
+      <c r="L272" s="42"/>
+      <c r="M272" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N272" s="11"/>
+      <c r="O272" s="19" t="s">
+        <v>1507</v>
+      </c>
+      <c r="P272" s="7"/>
+      <c r="Q272" s="24"/>
+      <c r="R272" s="25"/>
+      <c r="S272" s="7"/>
+      <c r="T272" s="7"/>
+      <c r="U272" s="7"/>
+    </row>
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A273" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B273" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C273" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D273" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E273" s="14">
+        <v>2025</v>
+      </c>
+      <c r="F273" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G273" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H273" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I273" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J273" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K273" s="31">
+        <v>46023</v>
+      </c>
+      <c r="L273" s="31"/>
+      <c r="M273" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N273" s="45"/>
+      <c r="O273" s="44" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P273" s="27"/>
+      <c r="Q273" s="24"/>
+      <c r="R273" s="25"/>
+      <c r="S273" s="7"/>
+      <c r="T273" s="7"/>
+      <c r="U273" s="7"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T248:V1048576 T243:V245 T246:U246">
-    <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="31" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T113:U113">
-    <cfRule type="cellIs" dxfId="10" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="30" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U241:U242">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="4" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T247:U247">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20678,7 +20836,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="40.7109375" customWidth="1"/>
@@ -20716,7 +20874,7 @@
       </c>
       <c r="J1" s="55">
         <f ca="1">AVERAGE(G:G)</f>
-        <v>159</v>
+        <v>163.5</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>1164</v>
@@ -20741,153 +20899,153 @@
       </c>
       <c r="G2" s="12">
         <f ca="1">TODAY()-F2</f>
-        <v>599</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="10">
-        <v>45434</v>
+        <v>45488</v>
       </c>
       <c r="G3" s="12">
         <f ca="1">TODAY()-F3</f>
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1476</v>
+        <v>1324</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1267</v>
+        <v>1327</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>373</v>
+        <v>252</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="10">
-        <v>45480</v>
+        <v>45524</v>
       </c>
       <c r="G4" s="12">
         <f ca="1">TODAY()-F4</f>
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1307</v>
+        <v>1333</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1308</v>
+        <v>1334</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="10">
-        <v>45488</v>
+        <v>45562</v>
       </c>
       <c r="G5" s="12">
         <f ca="1">TODAY()-F5</f>
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1327</v>
+        <v>1347</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1330</v>
+        <v>1348</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>344</v>
+        <v>1314</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="10">
-        <v>45524</v>
+        <v>45600</v>
       </c>
       <c r="G6" s="12">
         <f ca="1">TODAY()-F6</f>
-        <v>221</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1336</v>
+        <v>1517</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1337</v>
+        <v>1518</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1335</v>
+        <v>723</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1338</v>
+        <v>723</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="10">
-        <v>45562</v>
+        <v>45602</v>
       </c>
       <c r="G7" s="12">
         <f ca="1">TODAY()-F7</f>
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>160</v>
+        <v>1095</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1315</v>
+        <v>1096</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="10">
-        <v>45600</v>
+        <v>45624</v>
       </c>
       <c r="G8" s="12">
         <f ca="1">TODAY()-F8</f>
-        <v>145</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1339</v>
+        <v>1458</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1340</v>
+        <v>1321</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1095</v>
+        <v>89</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1096</v>
+        <v>89</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="10">
@@ -20895,119 +21053,119 @@
       </c>
       <c r="G9" s="12">
         <f ca="1">TODAY()-F9</f>
-        <v>121</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1324</v>
+        <v>1455</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>89</v>
+        <v>1456</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>1457</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="10">
-        <v>45624</v>
+        <v>45635</v>
       </c>
       <c r="G10" s="12">
         <f ca="1">TODAY()-F10</f>
-        <v>121</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1459</v>
+        <v>267</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1460</v>
+        <v>268</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="10">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="G11" s="12">
         <f ca="1">TODAY()-F11</f>
-        <v>110</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>267</v>
+        <v>668</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>268</v>
+        <v>669</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="10">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="G12" s="12">
         <f ca="1">TODAY()-F12</f>
-        <v>109</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1453</v>
+        <v>1467</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1454</v>
+        <v>1468</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>668</v>
+        <v>1466</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="E13" s="7"/>
+        <v>1466</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>1469</v>
+      </c>
       <c r="F13" s="10">
-        <v>45637</v>
+        <v>45663</v>
       </c>
       <c r="G13" s="12">
         <f ca="1">TODAY()-F13</f>
-        <v>108</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1470</v>
+        <v>287</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1470</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>1473</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="E14" s="7"/>
       <c r="F14" s="10">
-        <v>45663</v>
+        <v>45671</v>
       </c>
       <c r="G14" s="12">
         <f ca="1">TODAY()-F14</f>
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -21018,106 +21176,194 @@
         <v>1478</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>287</v>
+        <v>89</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>330</v>
+        <v>89</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="10">
-        <v>45671</v>
+        <v>45681</v>
       </c>
       <c r="G15" s="12">
         <f ca="1">TODAY()-F15</f>
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1481</v>
+        <v>1315</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1482</v>
+        <v>1319</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>89</v>
+        <v>723</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>89</v>
+        <v>723</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="10">
-        <v>45681</v>
+        <v>45705</v>
       </c>
       <c r="G16" s="12">
         <f ca="1">TODAY()-F16</f>
-        <v>64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1316</v>
+        <v>1499</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1322</v>
+        <v>1500</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>723</v>
+        <v>267</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>723</v>
+        <v>268</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="10">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G17" s="12">
         <f ca="1">TODAY()-F17</f>
-        <v>40</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1503</v>
+        <v>1481</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1504</v>
+        <v>1482</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>267</v>
+        <v>1483</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>268</v>
+        <v>1484</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="10">
-        <v>45709</v>
+        <v>45729</v>
       </c>
       <c r="G18" s="12">
         <f ca="1">TODAY()-F18</f>
-        <v>36</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1485</v>
+        <v>1502</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1486</v>
+        <v>1503</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1487</v>
+        <v>160</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1488</v>
+        <v>1314</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="10">
-        <v>45729</v>
+        <v>45735</v>
       </c>
       <c r="G19" s="12">
         <f ca="1">TODAY()-F19</f>
-        <v>16</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="10">
+        <v>45764</v>
+      </c>
+      <c r="G20" s="12">
+        <f ca="1">TODAY()-F20</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="10">
+        <v>45785</v>
+      </c>
+      <c r="G21" s="12">
+        <f ca="1">TODAY()-F21</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="10">
+        <v>45790</v>
+      </c>
+      <c r="G22" s="12">
+        <f ca="1">TODAY()-F22</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10">
+        <v>45803</v>
+      </c>
+      <c r="G23" s="12">
+        <f ca="1">TODAY()-F23</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -21179,7 +21425,7 @@
       </c>
       <c r="F2" s="40">
         <f t="shared" ref="F2:F4" ca="1" si="0">(TODAY()-E2)/365</f>
-        <v>9.4164383561643827</v>
+        <v>9.580821917808219</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21200,7 +21446,7 @@
       </c>
       <c r="F3" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.4164383561643827</v>
+        <v>9.580821917808219</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21221,7 +21467,7 @@
       </c>
       <c r="F4" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>8.794520547945206</v>
+        <v>8.9589041095890405</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21242,7 +21488,7 @@
       </c>
       <c r="F5" s="40">
         <f ca="1">(TODAY()-E5)/365</f>
-        <v>7.1643835616438354</v>
+        <v>7.3287671232876717</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -21316,7 +21562,7 @@
         <v>1045</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="C2" s="52" t="s">
         <v>175</v>
@@ -21970,16 +22216,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B34" s="15">
         <v>2024</v>
       </c>
       <c r="C34" s="49" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D34" s="49" t="s">
         <v>1269</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>1270</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>1044</v>
@@ -21990,16 +22236,16 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B35" s="15">
         <v>2024</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>1044</v>
@@ -22010,16 +22256,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B36" s="15">
         <v>2024</v>
       </c>
       <c r="C36" s="49" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D36" s="49" t="s">
         <v>1284</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>1285</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>1044</v>
@@ -22030,16 +22276,16 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B37" s="15">
         <v>2024</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>1044</v>
@@ -22050,16 +22296,16 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B38" s="15">
         <v>2024</v>
       </c>
       <c r="C38" s="49" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D38" s="49" t="s">
         <v>1300</v>
-      </c>
-      <c r="D38" s="49" t="s">
-        <v>1301</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>1044</v>
@@ -22070,16 +22316,16 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B39" s="15">
         <v>2024</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>1044</v>
@@ -22090,16 +22336,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B40" s="15">
         <v>2024</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>1044</v>
@@ -22110,16 +22356,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="B41" s="15">
         <v>2024</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>1044</v>
@@ -22130,16 +22376,16 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="B42" s="15">
         <v>2024</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>1044</v>
@@ -22153,16 +22399,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B43" s="15">
         <v>2024</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>1044</v>
@@ -22173,16 +22419,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B44" s="15">
         <v>2024</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>1044</v>
@@ -22193,16 +22439,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B45" s="15">
         <v>2024</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>1044</v>
@@ -22213,16 +22459,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B46" s="15">
         <v>2024</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>1044</v>
@@ -22233,16 +22479,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="B47" s="15">
         <v>2024</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>1044</v>
@@ -22253,16 +22499,16 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="B48" s="15">
         <v>2024</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>1044</v>
@@ -22273,16 +22519,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="B49" s="15">
         <v>2024</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>1044</v>
@@ -22293,16 +22539,16 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="B50" s="15">
         <v>2024</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>1044</v>
@@ -22313,16 +22559,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="B51" s="15">
         <v>2024</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>1044</v>
@@ -22333,16 +22579,16 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B52" s="15">
         <v>2024</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>1044</v>
@@ -22353,16 +22599,16 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B53" s="15">
         <v>2024</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1044</v>
@@ -22373,16 +22619,16 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B54" s="15">
         <v>2024</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>1044</v>
@@ -22393,16 +22639,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B55" s="15">
         <v>2024</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>1044</v>
@@ -22413,16 +22659,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B56" s="15">
         <v>2024</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>1044</v>
@@ -22433,16 +22679,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B57" s="15">
         <v>2024</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>1044</v>
@@ -22453,16 +22699,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="B58" s="15">
         <v>2024</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>1044</v>
@@ -22473,16 +22719,16 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="B59" s="15">
         <v>2024</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>1044</v>
@@ -22493,16 +22739,16 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="B60" s="15">
         <v>2024</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>1044</v>
@@ -22513,16 +22759,16 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="B61" s="15">
         <v>2024</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>1044</v>
@@ -22533,16 +22779,16 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="B62" s="15">
         <v>2024</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>1044</v>
@@ -22553,16 +22799,16 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="B63" s="15">
         <v>2024</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>1044</v>
@@ -22573,16 +22819,16 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="B64" s="15">
         <v>2024</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>1044</v>
@@ -22593,16 +22839,16 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B65" s="15">
         <v>2024</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>1044</v>
@@ -22613,16 +22859,16 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="B66" s="15">
         <v>2024</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>1044</v>
@@ -22633,16 +22879,16 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="B67" s="15">
         <v>2024</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>1044</v>
@@ -22653,16 +22899,16 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="B68" s="15">
         <v>2024</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>1044</v>
@@ -22673,16 +22919,16 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="B69" s="15">
         <v>2024</v>
       </c>
       <c r="C69" s="49" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>1044</v>
@@ -22693,16 +22939,16 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="B70" s="15">
         <v>2024</v>
       </c>
       <c r="C70" s="49" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>1044</v>
@@ -22713,16 +22959,16 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="B71" s="15">
         <v>2024</v>
       </c>
       <c r="C71" s="49" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>1044</v>
@@ -22733,19 +22979,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="B72" s="15">
         <v>2024</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="G72" s="48" t="s">
         <v>1037</v>
@@ -22753,19 +22999,19 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="B73" s="15">
         <v>2024</v>
       </c>
       <c r="C73" s="49" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="D73" s="49" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="G73" s="48" t="s">
         <v>1037</v>
@@ -22773,13 +23019,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="B74" s="15">
         <v>2025</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>1044</v>

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DD225E-A429-47BE-9FBD-3AF1011DDA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A54D254-A5BA-488B-A690-06BBE2E3AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="papers" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="1524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="1543">
   <si>
     <t>title</t>
   </si>
@@ -3818,9 +3818,6 @@
     <t>Vandeninden, Bram; De Clercq, Eva; Devleesschauwer, Brecht; Otavova, Martina; Masquelier, Bruno; Fierens, Frans; Faes, Christel; Bouland, Catherine</t>
   </si>
   <si>
-    <t>Methodology for assessing the impact of local traffic interventions on disease burden: a case study on paediatric asthma incidence in European cities</t>
-  </si>
-  <si>
     <t>Hubin, Pierre; Van den Borre, Laura; Braeye, Toon; Cavillot, Lisa; Billuart, Matthieu; Stouten, Veerle; Nasiadka, Léonore; Vermeiren, Elias; Van Evercooren, Izaak; Devleesschauwer, Brecht; Catteau, Lucy; van Loenhout, Joris A F</t>
   </si>
   <si>
@@ -4079,9 +4076,6 @@
     <t>Fascioliasis in north-central Vietnam: assessing community knowledge, attitudes, and practices</t>
   </si>
   <si>
-    <t>Quang Hoang, Vinh; Trung Do, Dun; Thi Lam Vu, Binh; Thi Thu Nguyen, Hien; Thi Tran, Tuyen; Thuy Le, Dung; Ngoc Nguyen, Ha; Duc Nguyen, Thuy; Devleesschauwer, Brecht; Levecke, Bruno; Polman, Katja; de Jong, Theodorus; Dorny, Pierre; Paredis, Linda; Goossens, Kathy; Dermauw, Veronique</t>
-  </si>
-  <si>
     <t>Van Acker, Lisa; Toribio, Luz; Chachage, Mkunde; Zeng, Hang; Devleesschauwer, Brecht; Garcia, Héctor H.; Gabriël, Sarah; on behalf of the NeuroSolve Consortium</t>
   </si>
   <si>
@@ -4403,12 +4397,6 @@
     <t>Pauwels, Arno; Demoury, Claire; De Clercq, Eva; Devleesschauwer, Brecht</t>
   </si>
   <si>
-    <t>Environmental Pollution</t>
-  </si>
-  <si>
-    <t>Environ. Pollut.</t>
-  </si>
-  <si>
     <t>The economic burden of alcohol in Belgium: incremental healthcare costs and lost productivity</t>
   </si>
   <si>
@@ -4469,9 +4457,6 @@
     <t>Estimating years of life lost due to premature mortality at regional level in France in 2017, using a probabilistic redistribution approach</t>
   </si>
   <si>
-    <t>Haneef, Romana; Scohy, Aline; Mahrouseh, Nour; Constantinou, Panayotis; Rachas, Antoine; Ghosn, Walid; Wyper, Grant M A; Devleesschauwer, Brecht</t>
-  </si>
-  <si>
     <t>A framework for quantifying the multisectoral burden of animal disease to support decision making</t>
   </si>
   <si>
@@ -4589,9 +4574,6 @@
     <t>Burden of disease using Disability Adjusted Life Years in the Middle East and North Africa (MENA) region: protocol of a systematic review</t>
   </si>
   <si>
-    <t>Mathew, Simy; Rifai, R; Grivna, M; Ostlundh, Linda; Devleesschauwer, Brecht; Adam, Balazs</t>
-  </si>
-  <si>
     <t>Nayani, Sarah; Guariguata, Leonor; Croes, Sarah; Schmidt, Masja; Gisle, Lydia; Vynckier, Pieter; Verhaeghe, Nick; De Pauw, Robby; Devleesschauwer, Brecht</t>
   </si>
   <si>
@@ -4605,6 +4587,81 @@
   </si>
   <si>
     <t xml:space="preserve">Haneef, Romana; Mahrouseh, Nour; Bessonneau, Pascal; Vandentorren, Stephanie; Minier, Nicolas; Chin, Francis; Bruyère, Olivier; Devleesschauwer, Brecht; Wyper, Grant M A </t>
+  </si>
+  <si>
+    <t>Impact assessment of local traffic interventions on disease burden: A case study on paediatric asthma incidence in two European cities</t>
+  </si>
+  <si>
+    <t>10.1016/j.jth.2024.101953</t>
+  </si>
+  <si>
+    <t>Quang, Hoang Vinh; Levecke, Bruno; Do Trung, Dun; Thi Lam, Binh Vu; Dung, Le Thuy; Nguyen, Thuy Duc; Tuyen, Thi Tran; Nguyen, Hien Thi Thu; HA, Ngoc Nguyen; Devleesschauwer, Brecht; Goossens, Kathy; de Jong, Theodorus; Paredis, Linda; De Wilde, Nathalie; Polman, Katja; Callens, Steven; Dorny, Pierre; Dermauw, Veronique</t>
+  </si>
+  <si>
+    <t>e0013324</t>
+  </si>
+  <si>
+    <t>10.1371/journal.pntd.0013324</t>
+  </si>
+  <si>
+    <t>Mathew, Simy; Sherif, M; Al-Rifai, RH; Grivna, M; Östlundh, Linda; Devleesschauwer, Brecht; Ádám, Balazs</t>
+  </si>
+  <si>
+    <t>e096214</t>
+  </si>
+  <si>
+    <t>10.1136/bmjopen-2024-096214</t>
+  </si>
+  <si>
+    <t>10.1186/s12889-025-23625-z</t>
+  </si>
+  <si>
+    <t>Haneef, Romana; Scohy, Aline; Mahrouseh, Nour; Coudin, Elise; Constantinou, Panayotis; Rachas, Antoine; Lesnik, Tina; Wyper, Grant M A; Devleesschauwer, Brecht</t>
+  </si>
+  <si>
+    <t>10.1186/s12889-025-23559-6</t>
+  </si>
+  <si>
+    <t>10.1186/s13690-025-01652-x</t>
+  </si>
+  <si>
+    <t>10.21203/rs.3.rs-5611920/v1</t>
+  </si>
+  <si>
+    <t>Pre-pandemic sub-national disparities in the disease burden of ischemic heart disease and stroke in France</t>
+  </si>
+  <si>
+    <t>Haneef, Romana; Monzo, Luca; Mahrouseh, Nour; von der Lippe, Elena; Devleesschauwer, Brecht; Wyper, Grant M A</t>
+  </si>
+  <si>
+    <t>BMC Cardiovascular Disorders</t>
+  </si>
+  <si>
+    <t>BMC Cardiovasc. Disord.</t>
+  </si>
+  <si>
+    <t>Long-term ambient nitrogen dioxide exposure and COPD: a systematic review and quantitative synthesis</t>
+  </si>
+  <si>
+    <t>Exposure-response relationship between transportation noise and cardiovascular disease outcomes: a systematic review and meta-regression analysis</t>
+  </si>
+  <si>
+    <t>Gonzato, Elia; Haverkate, Tessa M I, Breitner-Busch, Susanne; Kocbach Bølling, Anette; Aasvang, Gunn Marit; Brauer, Michael; Garcia, Vanessa; Spearman, Sandra; Devleesschauwer, Brecht; Haagsma, Juanita A; Charalampous, Periklis</t>
+  </si>
+  <si>
+    <t>Sub-national disparities in disease burden of diabetes mellitus and chronic kidney disease in France: A pre-pandemic analysis</t>
+  </si>
+  <si>
+    <t>Years of Life Lost due to the 2015 Gorkha Earthquake in Nepal</t>
+  </si>
+  <si>
+    <t>Tonnelier, Margo; Delforge, Damien; Bhandari, Manisha Panta; Devleesschauwer, Brecht; Haagsma, Juanita A; Wyper, Grant M A; Castin, Emilie; Speybroeck, Niko; Charalampous, Periklis</t>
+  </si>
+  <si>
+    <t>Haverkate, Tessa M I; Charalampous, Periklis; Gonzato, Elia; Pereda, Ana; Garcia, Vanessa; Brauer, Michael; Devleesschauwer, Brecht; Breitner-Busch, Susanne; Haagsma, Juanita A</t>
+  </si>
+  <si>
+    <t>Couchoud, Cécile; Raffray, Maxime; Mahrouseh, Nour; von der Lippe, Elena; Devleesschauwer, Brecht; Wyper, Grant M A; Haneef, Romana</t>
   </si>
 </sst>
 </file>
@@ -4946,6 +5003,86 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5109,86 +5246,6 @@
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5203,74 +5260,74 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U273" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:U273" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U273">
-    <sortCondition ref="K1:K273"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U279" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:U279" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U279">
+    <sortCondition ref="K1:K279"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="43"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="42" dataCellStyle="Neutral"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="36"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="35"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="34"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="51"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="50" dataCellStyle="Neutral"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="47"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="46"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="45"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="44"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="43"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="42"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="40">
   <autoFilter ref="A1:J12" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N50">
     <sortCondition ref="H1:H50"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G23" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:G23" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
-    <sortCondition ref="F1:F23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G22" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:G22" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
+    <sortCondition ref="F1:F17"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="21">
       <calculatedColumnFormula>TODAY()-F2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5279,18 +5336,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:F5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
     <sortCondition ref="E1:E14"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="13">
       <calculatedColumnFormula>(TODAY()-E2)/365</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5619,7 +5676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U273"/>
+  <dimension ref="A1:U279"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -18934,7 +18991,7 @@
         <v>101</v>
       </c>
       <c r="H245" s="18" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="I245" s="18" t="s">
         <v>14</v>
@@ -18951,7 +19008,7 @@
       </c>
       <c r="N245" s="11"/>
       <c r="O245" s="19" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="P245" s="7"/>
       <c r="Q245" s="24"/>
@@ -18969,7 +19026,7 @@
         <v>1088</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>1138</v>
@@ -18987,7 +19044,7 @@
         <v>91</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="I246" s="18" t="s">
         <v>14</v>
@@ -19004,7 +19061,7 @@
       </c>
       <c r="N246" s="11"/>
       <c r="O246" s="19" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="P246" s="7"/>
       <c r="Q246" s="24"/>
@@ -19040,7 +19097,7 @@
         <v>125</v>
       </c>
       <c r="H247" s="18" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="I247" s="18" t="s">
         <v>14</v>
@@ -19057,7 +19114,7 @@
       </c>
       <c r="N247" s="11"/>
       <c r="O247" s="19" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="P247" s="7"/>
       <c r="Q247" s="24"/>
@@ -19110,7 +19167,7 @@
       </c>
       <c r="N248" s="11"/>
       <c r="O248" s="19" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="P248" s="7"/>
       <c r="Q248" s="24"/>
@@ -19163,7 +19220,7 @@
       </c>
       <c r="N249" s="11"/>
       <c r="O249" s="19" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="P249" s="7"/>
       <c r="Q249" s="24"/>
@@ -19216,7 +19273,7 @@
       </c>
       <c r="N250" s="11"/>
       <c r="O250" s="19" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="P250" s="7"/>
       <c r="Q250" s="24"/>
@@ -19269,7 +19326,7 @@
       </c>
       <c r="N251" s="11"/>
       <c r="O251" s="19" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="P251" s="7"/>
       <c r="Q251" s="24"/>
@@ -19284,10 +19341,10 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>668</v>
@@ -19322,7 +19379,7 @@
       </c>
       <c r="N252" s="11"/>
       <c r="O252" s="19" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="P252" s="7"/>
       <c r="Q252" s="24"/>
@@ -19340,7 +19397,7 @@
         <v>1136</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>89</v>
@@ -19375,7 +19432,7 @@
       </c>
       <c r="N253" s="11"/>
       <c r="O253" s="19" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="P253" s="7"/>
       <c r="Q253" s="24"/>
@@ -19390,16 +19447,16 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B254" s="7" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C254" s="7" t="s">
         <v>1262</v>
       </c>
-      <c r="C254" s="7" t="s">
+      <c r="D254" s="7" t="s">
         <v>1263</v>
-      </c>
-      <c r="D254" s="7" t="s">
-        <v>1264</v>
       </c>
       <c r="E254" s="18">
         <v>2024</v>
@@ -19428,7 +19485,7 @@
       </c>
       <c r="N254" s="11"/>
       <c r="O254" s="19" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="P254" s="7"/>
       <c r="Q254" s="24"/>
@@ -19443,10 +19500,10 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B255" s="7" t="s">
         <v>1328</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>1329</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>813</v>
@@ -19481,7 +19538,7 @@
       </c>
       <c r="N255" s="11"/>
       <c r="O255" s="19" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="P255" s="7"/>
       <c r="Q255" s="24"/>
@@ -19534,7 +19591,7 @@
       </c>
       <c r="N256" s="11"/>
       <c r="O256" s="19" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="P256" s="7"/>
       <c r="Q256" s="24"/>
@@ -19549,7 +19606,7 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B257" s="7" t="s">
         <v>1063</v>
@@ -19587,7 +19644,7 @@
       </c>
       <c r="N257" s="11"/>
       <c r="O257" s="19" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="P257" s="7"/>
       <c r="Q257" s="24"/>
@@ -19602,10 +19659,10 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B258" s="7" t="s">
         <v>1274</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>1275</v>
       </c>
       <c r="C258" s="7" t="s">
         <v>108</v>
@@ -19640,7 +19697,7 @@
       </c>
       <c r="N258" s="11"/>
       <c r="O258" s="19" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="P258" s="7"/>
       <c r="Q258" s="24"/>
@@ -19655,16 +19712,16 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B259" s="7" t="s">
         <v>1338</v>
       </c>
-      <c r="B259" s="7" t="s">
-        <v>1339</v>
-      </c>
       <c r="C259" s="7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E259" s="18">
         <v>2024</v>
@@ -19693,7 +19750,7 @@
       </c>
       <c r="N259" s="11"/>
       <c r="O259" s="19" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="P259" s="7"/>
       <c r="Q259" s="24"/>
@@ -19708,16 +19765,16 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E260" s="18">
         <v>2024</v>
@@ -19729,7 +19786,7 @@
         <v>69</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="I260" s="18" t="s">
         <v>14</v>
@@ -19746,7 +19803,7 @@
       </c>
       <c r="N260" s="11"/>
       <c r="O260" s="19" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="P260" s="7"/>
       <c r="Q260" s="24"/>
@@ -19761,10 +19818,10 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C261" s="7" t="s">
         <v>267</v>
@@ -19799,7 +19856,7 @@
       </c>
       <c r="N261" s="11"/>
       <c r="O261" s="19" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="P261" s="7"/>
       <c r="Q261" s="24"/>
@@ -19852,7 +19909,7 @@
       </c>
       <c r="N262" s="11"/>
       <c r="O262" s="19" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="P262" s="7"/>
       <c r="Q262" s="24"/>
@@ -19867,16 +19924,16 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>1213</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="E263" s="18">
         <v>2025</v>
@@ -19888,7 +19945,7 @@
         <v>14</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="I263" s="18" t="s">
         <v>14</v>
@@ -19905,7 +19962,7 @@
       </c>
       <c r="N263" s="11"/>
       <c r="O263" s="19" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="P263" s="7"/>
       <c r="Q263" s="24"/>
@@ -19916,16 +19973,16 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C264" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D264" s="7" t="s">
         <v>1288</v>
-      </c>
-      <c r="D264" s="7" t="s">
-        <v>1289</v>
       </c>
       <c r="E264" s="18">
         <v>2025</v>
@@ -19954,7 +20011,7 @@
       </c>
       <c r="N264" s="11"/>
       <c r="O264" s="19" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="P264" s="7"/>
       <c r="Q264" s="24"/>
@@ -19969,10 +20026,10 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B265" s="7" t="s">
         <v>1292</v>
-      </c>
-      <c r="B265" s="7" t="s">
-        <v>1293</v>
       </c>
       <c r="C265" s="7" t="s">
         <v>1138</v>
@@ -19990,7 +20047,7 @@
         <v>101</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="I265" s="18" t="s">
         <v>14</v>
@@ -20007,7 +20064,7 @@
       </c>
       <c r="N265" s="11"/>
       <c r="O265" s="19" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="P265" s="7"/>
       <c r="Q265" s="24"/>
@@ -20018,16 +20075,16 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>267</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="E266" s="18">
         <v>2025</v>
@@ -20056,7 +20113,7 @@
       </c>
       <c r="N266" s="11"/>
       <c r="O266" s="19" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="P266" s="7"/>
       <c r="Q266" s="24"/>
@@ -20067,10 +20124,10 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B267" s="7" t="s">
         <v>1320</v>
-      </c>
-      <c r="B267" s="7" t="s">
-        <v>1321</v>
       </c>
       <c r="C267" s="7" t="s">
         <v>287</v>
@@ -20105,7 +20162,7 @@
       </c>
       <c r="N267" s="11"/>
       <c r="O267" s="19" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="P267" s="7"/>
       <c r="Q267" s="24"/>
@@ -20116,37 +20173,37 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
-        <v>1485</v>
+        <v>1518</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>1486</v>
+        <v>1260</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>1487</v>
+        <v>1259</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>1488</v>
+        <v>1265</v>
       </c>
       <c r="E268" s="18">
         <v>2025</v>
       </c>
       <c r="F268" s="18">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G268" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="H268" s="18" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="H268" s="18">
+        <v>101953</v>
       </c>
       <c r="I268" s="18" t="s">
-        <v>1489</v>
+        <v>14</v>
       </c>
       <c r="J268" s="18" t="s">
-        <v>1490</v>
+        <v>14</v>
       </c>
       <c r="K268" s="42">
-        <v>45706</v>
+        <v>45689</v>
       </c>
       <c r="L268" s="42"/>
       <c r="M268" s="42" t="s">
@@ -20154,7 +20211,7 @@
       </c>
       <c r="N268" s="11"/>
       <c r="O268" s="19" t="s">
-        <v>1491</v>
+        <v>1519</v>
       </c>
       <c r="P268" s="7"/>
       <c r="Q268" s="24"/>
@@ -20165,37 +20222,37 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>1498</v>
+        <v>1480</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>1501</v>
+        <v>1481</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>723</v>
+        <v>1482</v>
       </c>
       <c r="D269" s="7" t="s">
-        <v>723</v>
+        <v>1483</v>
       </c>
       <c r="E269" s="18">
         <v>2025</v>
       </c>
       <c r="F269" s="18">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G269" s="19" t="s">
-        <v>548</v>
+        <v>91</v>
       </c>
       <c r="H269" s="18" t="s">
-        <v>1512</v>
+        <v>14</v>
       </c>
       <c r="I269" s="18" t="s">
-        <v>14</v>
+        <v>1484</v>
       </c>
       <c r="J269" s="18" t="s">
-        <v>14</v>
+        <v>1485</v>
       </c>
       <c r="K269" s="42">
-        <v>45750</v>
+        <v>45706</v>
       </c>
       <c r="L269" s="42"/>
       <c r="M269" s="42" t="s">
@@ -20203,7 +20260,7 @@
       </c>
       <c r="N269" s="11"/>
       <c r="O269" s="19" t="s">
-        <v>1513</v>
+        <v>1486</v>
       </c>
       <c r="P269" s="7"/>
       <c r="Q269" s="24"/>
@@ -20214,16 +20271,16 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
-        <v>1472</v>
+        <v>1493</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>1509</v>
+        <v>1496</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>373</v>
+        <v>723</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>374</v>
+        <v>723</v>
       </c>
       <c r="E270" s="18">
         <v>2025</v>
@@ -20232,10 +20289,10 @@
         <v>15</v>
       </c>
       <c r="G270" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="H270" s="18">
-        <v>13683</v>
+        <v>548</v>
+      </c>
+      <c r="H270" s="18" t="s">
+        <v>1507</v>
       </c>
       <c r="I270" s="18" t="s">
         <v>14</v>
@@ -20244,7 +20301,7 @@
         <v>14</v>
       </c>
       <c r="K270" s="42">
-        <v>45768</v>
+        <v>45750</v>
       </c>
       <c r="L270" s="42"/>
       <c r="M270" s="42" t="s">
@@ -20252,7 +20309,7 @@
       </c>
       <c r="N270" s="11"/>
       <c r="O270" s="19" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="P270" s="7"/>
       <c r="Q270" s="24"/>
@@ -20263,28 +20320,28 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>1345</v>
+        <v>1468</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>1346</v>
+        <v>1504</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>1314</v>
+        <v>374</v>
       </c>
       <c r="E271" s="18">
         <v>2025</v>
       </c>
       <c r="F271" s="18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G271" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="H271" s="18" t="s">
-        <v>1511</v>
+        <v>101</v>
+      </c>
+      <c r="H271" s="18">
+        <v>13683</v>
       </c>
       <c r="I271" s="18" t="s">
         <v>14</v>
@@ -20293,7 +20350,7 @@
         <v>14</v>
       </c>
       <c r="K271" s="42">
-        <v>45769</v>
+        <v>45768</v>
       </c>
       <c r="L271" s="42"/>
       <c r="M271" s="42" t="s">
@@ -20301,7 +20358,7 @@
       </c>
       <c r="N271" s="11"/>
       <c r="O271" s="19" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
       <c r="P271" s="7"/>
       <c r="Q271" s="24"/>
@@ -20312,28 +20369,28 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
-        <v>1504</v>
+        <v>1344</v>
       </c>
       <c r="B272" s="7" t="s">
-        <v>1317</v>
+        <v>1345</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1505</v>
+        <v>160</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>1506</v>
+        <v>1313</v>
       </c>
       <c r="E272" s="18">
         <v>2025</v>
       </c>
       <c r="F272" s="18">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G272" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H272" s="18">
-        <v>22</v>
+        <v>548</v>
+      </c>
+      <c r="H272" s="18" t="s">
+        <v>1506</v>
       </c>
       <c r="I272" s="18" t="s">
         <v>14</v>
@@ -20342,7 +20399,7 @@
         <v>14</v>
       </c>
       <c r="K272" s="42">
-        <v>45772</v>
+        <v>45769</v>
       </c>
       <c r="L272" s="42"/>
       <c r="M272" s="42" t="s">
@@ -20350,7 +20407,7 @@
       </c>
       <c r="N272" s="11"/>
       <c r="O272" s="19" t="s">
-        <v>1507</v>
+        <v>1492</v>
       </c>
       <c r="P272" s="7"/>
       <c r="Q272" s="24"/>
@@ -20360,84 +20417,378 @@
       <c r="U272" s="7"/>
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A273" s="13" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B273" s="13" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C273" s="13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D273" s="13" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E273" s="14">
+      <c r="A273" s="7" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D273" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E273" s="18">
         <v>2025</v>
       </c>
-      <c r="F273" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G273" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H273" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I273" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J273" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K273" s="31">
-        <v>46023</v>
-      </c>
-      <c r="L273" s="31"/>
-      <c r="M273" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N273" s="45"/>
-      <c r="O273" s="44" t="s">
-        <v>1265</v>
-      </c>
-      <c r="P273" s="27"/>
+      <c r="F273" s="18">
+        <v>7</v>
+      </c>
+      <c r="G273" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H273" s="18">
+        <v>22</v>
+      </c>
+      <c r="I273" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J273" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K273" s="42">
+        <v>45772</v>
+      </c>
+      <c r="L273" s="42"/>
+      <c r="M273" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N273" s="11"/>
+      <c r="O273" s="19" t="s">
+        <v>1502</v>
+      </c>
+      <c r="P273" s="7"/>
       <c r="Q273" s="24"/>
       <c r="R273" s="25"/>
       <c r="S273" s="7"/>
       <c r="T273" s="7"/>
       <c r="U273" s="7"/>
     </row>
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A274" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="E274" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F274" s="18">
+        <v>15</v>
+      </c>
+      <c r="G274" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H274" s="18" t="s">
+        <v>1524</v>
+      </c>
+      <c r="I274" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J274" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K274" s="42">
+        <v>45832</v>
+      </c>
+      <c r="L274" s="42"/>
+      <c r="M274" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N274" s="11"/>
+      <c r="O274" s="19" t="s">
+        <v>1525</v>
+      </c>
+      <c r="P274" s="7"/>
+      <c r="Q274" s="24"/>
+      <c r="R274" s="25"/>
+      <c r="S274" s="7"/>
+      <c r="T274" s="7"/>
+      <c r="U274" s="7"/>
+    </row>
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A275" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E275" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F275" s="18">
+        <v>25</v>
+      </c>
+      <c r="G275" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H275" s="18">
+        <v>2375</v>
+      </c>
+      <c r="I275" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J275" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K275" s="42">
+        <v>45841</v>
+      </c>
+      <c r="L275" s="42"/>
+      <c r="M275" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N275" s="11"/>
+      <c r="O275" s="19" t="s">
+        <v>1528</v>
+      </c>
+      <c r="P275" s="7"/>
+      <c r="Q275" s="24"/>
+      <c r="R275" s="25"/>
+      <c r="S275" s="7"/>
+      <c r="T275" s="7"/>
+      <c r="U275" s="7"/>
+    </row>
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A276" s="7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C276" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E276" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F276" s="18">
+        <v>83</v>
+      </c>
+      <c r="G276" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H276" s="18">
+        <v>185</v>
+      </c>
+      <c r="I276" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J276" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K276" s="42">
+        <v>45849</v>
+      </c>
+      <c r="L276" s="42"/>
+      <c r="M276" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N276" s="11"/>
+      <c r="O276" s="19" t="s">
+        <v>1529</v>
+      </c>
+      <c r="P276" s="7"/>
+      <c r="Q276" s="24"/>
+      <c r="R276" s="25"/>
+      <c r="S276" s="7"/>
+      <c r="T276" s="7"/>
+      <c r="U276" s="7"/>
+    </row>
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A277" s="7" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E277" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F277" s="18">
+        <v>25</v>
+      </c>
+      <c r="G277" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H277" s="18">
+        <v>2439</v>
+      </c>
+      <c r="I277" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J277" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K277" s="42">
+        <v>45850</v>
+      </c>
+      <c r="L277" s="42"/>
+      <c r="M277" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N277" s="11"/>
+      <c r="O277" s="19" t="s">
+        <v>1526</v>
+      </c>
+      <c r="P277" s="7"/>
+      <c r="Q277" s="24"/>
+      <c r="R277" s="25"/>
+      <c r="S277" s="7"/>
+      <c r="T277" s="7"/>
+      <c r="U277" s="7"/>
+    </row>
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A278" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E278" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F278" s="18">
+        <v>19</v>
+      </c>
+      <c r="G278" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H278" s="18" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I278" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J278" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K278" s="42">
+        <v>45859</v>
+      </c>
+      <c r="L278" s="42"/>
+      <c r="M278" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N278" s="11"/>
+      <c r="O278" s="19" t="s">
+        <v>1522</v>
+      </c>
+      <c r="P278" s="7"/>
+      <c r="Q278" s="24"/>
+      <c r="R278" s="25"/>
+      <c r="S278" s="7"/>
+      <c r="T278" s="7"/>
+      <c r="U278" s="7"/>
+    </row>
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A279" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B279" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C279" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D279" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E279" s="14">
+        <v>2025</v>
+      </c>
+      <c r="F279" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G279" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H279" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I279" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J279" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K279" s="31">
+        <v>46023</v>
+      </c>
+      <c r="L279" s="31"/>
+      <c r="M279" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N279" s="45"/>
+      <c r="O279" s="44" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P279" s="27"/>
+      <c r="Q279" s="24"/>
+      <c r="R279" s="25"/>
+      <c r="S279" s="7"/>
+      <c r="T279" s="7"/>
+      <c r="U279" s="7"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T248:V1048576 T243:V245 T246:U246">
-    <cfRule type="cellIs" dxfId="63" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T113:U113">
-    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="29" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="30" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U241:U242">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T247:U247">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20836,7 +21187,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="40.7109375" customWidth="1"/>
@@ -20874,7 +21225,7 @@
       </c>
       <c r="J1" s="55">
         <f ca="1">AVERAGE(G:G)</f>
-        <v>163.5</v>
+        <v>145.14285714285714</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>1164</v>
@@ -20882,488 +21233,468 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1260</v>
+        <v>1306</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1259</v>
+        <v>1324</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1266</v>
+        <v>1325</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="10">
-        <v>45146</v>
+        <v>45488</v>
       </c>
       <c r="G2" s="12">
-        <f ca="1">TODAY()-F2</f>
-        <v>659</v>
+        <f t="shared" ref="G2:G22" ca="1" si="0">TODAY()-F2</f>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1306</v>
+        <v>1323</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1325</v>
+        <v>252</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1326</v>
+        <v>344</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="10">
-        <v>45488</v>
+        <v>45524</v>
       </c>
       <c r="G3" s="12">
-        <f ca="1">TODAY()-F3</f>
-        <v>317</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>252</v>
+        <v>1331</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>344</v>
+        <v>1334</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="10">
-        <v>45524</v>
+        <v>45562</v>
       </c>
       <c r="G4" s="12">
-        <f ca="1">TODAY()-F4</f>
-        <v>281</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1332</v>
+        <v>1095</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1335</v>
+        <v>1096</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="10">
-        <v>45562</v>
+        <v>45624</v>
       </c>
       <c r="G5" s="12">
-        <f ca="1">TODAY()-F5</f>
-        <v>243</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1347</v>
+        <v>1454</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1348</v>
+        <v>1320</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1314</v>
+        <v>89</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="10">
-        <v>45600</v>
+        <v>45624</v>
       </c>
       <c r="G6" s="12">
-        <f ca="1">TODAY()-F6</f>
-        <v>205</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1517</v>
+        <v>1450</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1518</v>
+        <v>1451</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>723</v>
+        <v>267</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="E7" s="7"/>
+        <v>268</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1530</v>
+      </c>
       <c r="F7" s="10">
-        <v>45602</v>
+        <v>45636</v>
       </c>
       <c r="G7" s="12">
-        <f ca="1">TODAY()-F7</f>
-        <v>203</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1336</v>
+        <v>1448</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1337</v>
+        <v>1449</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1095</v>
+        <v>668</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1096</v>
+        <v>669</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="10">
-        <v>45624</v>
+        <v>45637</v>
       </c>
       <c r="G8" s="12">
-        <f ca="1">TODAY()-F8</f>
-        <v>181</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1458</v>
+        <v>1463</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1321</v>
+        <v>1464</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>89</v>
+        <v>1462</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="7"/>
+        <v>1462</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>1465</v>
+      </c>
       <c r="F9" s="10">
-        <v>45624</v>
+        <v>45663</v>
       </c>
       <c r="G9" s="12">
-        <f ca="1">TODAY()-F9</f>
-        <v>181</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1454</v>
+        <v>1469</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1455</v>
+        <v>1470</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1456</v>
+        <v>287</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1457</v>
+        <v>330</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="10">
-        <v>45635</v>
+        <v>45671</v>
       </c>
       <c r="G10" s="12">
-        <f ca="1">TODAY()-F10</f>
-        <v>170</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1452</v>
+        <v>1314</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1453</v>
+        <v>1318</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>267</v>
+        <v>723</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>268</v>
+        <v>723</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="10">
-        <v>45636</v>
+        <v>45705</v>
       </c>
       <c r="G11" s="12">
-        <f ca="1">TODAY()-F11</f>
-        <v>169</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1451</v>
+        <v>1477</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>668</v>
+        <v>1478</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>669</v>
+        <v>1479</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="10">
-        <v>45637</v>
+        <v>45729</v>
       </c>
       <c r="G12" s="12">
-        <f ca="1">TODAY()-F12</f>
-        <v>168</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1467</v>
+        <v>1497</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1466</v>
+        <v>160</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1466</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>1469</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="E13" s="7"/>
       <c r="F13" s="10">
-        <v>45663</v>
+        <v>45735</v>
       </c>
       <c r="G13" s="12">
-        <f ca="1">TODAY()-F13</f>
-        <v>142</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1473</v>
+        <v>1511</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1474</v>
+        <v>1513</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>287</v>
+        <v>89</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>330</v>
+        <v>89</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="10">
-        <v>45671</v>
+        <v>45764</v>
       </c>
       <c r="G14" s="12">
-        <f ca="1">TODAY()-F14</f>
-        <v>134</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1477</v>
+        <v>1509</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="10">
-        <v>45681</v>
+        <v>45853</v>
       </c>
       <c r="G15" s="12">
-        <f ca="1">TODAY()-F15</f>
-        <v>124</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1315</v>
+        <v>1515</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1319</v>
+        <v>1517</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>723</v>
+        <v>1111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>723</v>
+        <v>1112</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="10">
-        <v>45705</v>
+        <v>45790</v>
       </c>
       <c r="G16" s="12">
-        <f ca="1">TODAY()-F16</f>
-        <v>100</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1499</v>
+        <v>1514</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1500</v>
+        <v>1516</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>267</v>
+        <v>1111</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>268</v>
+        <v>1112</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="10">
-        <v>45709</v>
+        <v>45803</v>
       </c>
       <c r="G17" s="12">
-        <f ca="1">TODAY()-F17</f>
-        <v>96</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1481</v>
+        <v>1531</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1482</v>
+        <v>1532</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1483</v>
+        <v>1533</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1484</v>
+        <v>1534</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="10">
-        <v>45729</v>
+        <v>45854</v>
       </c>
       <c r="G18" s="12">
-        <f ca="1">TODAY()-F18</f>
-        <v>76</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1502</v>
+        <v>1535</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1503</v>
+        <v>1541</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>160</v>
+        <v>1024</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1314</v>
+        <v>1026</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="10">
-        <v>45735</v>
+        <v>45860</v>
       </c>
       <c r="G19" s="12">
-        <f ca="1">TODAY()-F19</f>
-        <v>70</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1519</v>
+        <v>1537</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>89</v>
+        <v>1024</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>89</v>
+        <v>1026</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="10">
-        <v>45764</v>
+        <v>45860</v>
       </c>
       <c r="G20" s="12">
-        <f ca="1">TODAY()-F20</f>
-        <v>41</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1514</v>
+        <v>1538</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>1515</v>
+        <v>1542</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1466</v>
+        <v>267</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1466</v>
+        <v>268</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="10">
-        <v>45785</v>
+        <v>45848</v>
       </c>
       <c r="G21" s="12">
-        <f ca="1">TODAY()-F21</f>
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1521</v>
+        <v>1539</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1523</v>
+        <v>1540</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1111</v>
+        <v>89</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1112</v>
+        <v>89</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="10">
-        <v>45790</v>
+        <v>45845</v>
       </c>
       <c r="G22" s="12">
-        <f ca="1">TODAY()-F22</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>1520</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>1522</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10">
-        <v>45803</v>
-      </c>
-      <c r="G23" s="12">
-        <f ca="1">TODAY()-F23</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -21425,7 +21756,7 @@
       </c>
       <c r="F2" s="40">
         <f t="shared" ref="F2:F4" ca="1" si="0">(TODAY()-E2)/365</f>
-        <v>9.580821917808219</v>
+        <v>9.7397260273972606</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21446,7 +21777,7 @@
       </c>
       <c r="F3" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.580821917808219</v>
+        <v>9.7397260273972606</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21467,7 +21798,7 @@
       </c>
       <c r="F4" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9589041095890405</v>
+        <v>9.117808219178082</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21488,7 +21819,7 @@
       </c>
       <c r="F5" s="40">
         <f ca="1">(TODAY()-E5)/365</f>
-        <v>7.3287671232876717</v>
+        <v>7.4876712328767123</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -21562,7 +21893,7 @@
         <v>1045</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C2" s="52" t="s">
         <v>175</v>
@@ -22216,16 +22547,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B34" s="15">
         <v>2024</v>
       </c>
       <c r="C34" s="49" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D34" s="49" t="s">
         <v>1268</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>1269</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>1044</v>
@@ -22236,16 +22567,16 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B35" s="15">
         <v>2024</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>1044</v>
@@ -22256,16 +22587,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B36" s="15">
         <v>2024</v>
       </c>
       <c r="C36" s="49" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D36" s="49" t="s">
         <v>1283</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>1284</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>1044</v>
@@ -22276,16 +22607,16 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B37" s="15">
         <v>2024</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>1044</v>
@@ -22296,16 +22627,16 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B38" s="15">
         <v>2024</v>
       </c>
       <c r="C38" s="49" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D38" s="49" t="s">
         <v>1299</v>
-      </c>
-      <c r="D38" s="49" t="s">
-        <v>1300</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>1044</v>
@@ -22316,16 +22647,16 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B39" s="15">
         <v>2024</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>1044</v>
@@ -22336,16 +22667,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B40" s="15">
         <v>2024</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>1044</v>
@@ -22356,16 +22687,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B41" s="15">
         <v>2024</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>1044</v>
@@ -22376,16 +22707,16 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B42" s="15">
         <v>2024</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>1044</v>
@@ -22399,16 +22730,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B43" s="15">
         <v>2024</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>1044</v>
@@ -22419,16 +22750,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B44" s="15">
         <v>2024</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>1044</v>
@@ -22439,16 +22770,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B45" s="15">
         <v>2024</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>1044</v>
@@ -22459,16 +22790,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B46" s="15">
         <v>2024</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>1044</v>
@@ -22479,16 +22810,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B47" s="15">
         <v>2024</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>1044</v>
@@ -22499,16 +22830,16 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B48" s="15">
         <v>2024</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>1044</v>
@@ -22519,16 +22850,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B49" s="15">
         <v>2024</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>1044</v>
@@ -22539,16 +22870,16 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B50" s="15">
         <v>2024</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>1044</v>
@@ -22559,16 +22890,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B51" s="15">
         <v>2024</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>1044</v>
@@ -22579,16 +22910,16 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B52" s="15">
         <v>2024</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>1044</v>
@@ -22599,16 +22930,16 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B53" s="15">
         <v>2024</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1044</v>
@@ -22619,16 +22950,16 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B54" s="15">
         <v>2024</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>1044</v>
@@ -22639,16 +22970,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B55" s="15">
         <v>2024</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>1044</v>
@@ -22659,16 +22990,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B56" s="15">
         <v>2024</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>1044</v>
@@ -22679,16 +23010,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B57" s="15">
         <v>2024</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>1044</v>
@@ -22699,16 +23030,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B58" s="15">
         <v>2024</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>1044</v>
@@ -22719,16 +23050,16 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B59" s="15">
         <v>2024</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>1044</v>
@@ -22739,16 +23070,16 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B60" s="15">
         <v>2024</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>1044</v>
@@ -22759,16 +23090,16 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B61" s="15">
         <v>2024</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>1044</v>
@@ -22779,16 +23110,16 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="B62" s="15">
         <v>2024</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>1044</v>
@@ -22799,16 +23130,16 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B63" s="15">
         <v>2024</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>1044</v>
@@ -22819,16 +23150,16 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B64" s="15">
         <v>2024</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>1044</v>
@@ -22839,16 +23170,16 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B65" s="15">
         <v>2024</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>1044</v>
@@ -22859,16 +23190,16 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B66" s="15">
         <v>2024</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>1044</v>
@@ -22879,16 +23210,16 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B67" s="15">
         <v>2024</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>1044</v>
@@ -22899,16 +23230,16 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B68" s="15">
         <v>2024</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>1044</v>
@@ -22919,16 +23250,16 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B69" s="15">
         <v>2024</v>
       </c>
       <c r="C69" s="49" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>1044</v>
@@ -22939,16 +23270,16 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="B70" s="15">
         <v>2024</v>
       </c>
       <c r="C70" s="49" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>1044</v>
@@ -22959,16 +23290,16 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B71" s="15">
         <v>2024</v>
       </c>
       <c r="C71" s="49" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>1044</v>
@@ -22979,19 +23310,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="B72" s="15">
         <v>2024</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="G72" s="48" t="s">
         <v>1037</v>
@@ -22999,19 +23330,19 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="B73" s="15">
         <v>2024</v>
       </c>
       <c r="C73" s="49" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D73" s="49" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="G73" s="48" t="s">
         <v>1037</v>
@@ -23019,13 +23350,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="B74" s="15">
         <v>2025</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>1044</v>

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A54D254-A5BA-488B-A690-06BBE2E3AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13186BAF-33A1-411A-8A28-F0751E314714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,12 +28,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="1564">
   <si>
     <t>title</t>
   </si>
@@ -4430,9 +4433,6 @@
     <t>De Pauw, Robby; Lakha, Fatim; Fletcher, Eilidh; Stockton, Diane L; Baird, Emma; Connolly, Suzanne; Devleesschauwer, Brecht; Wyper, Grant M A</t>
   </si>
   <si>
-    <t>10.1101/2025.01.07.24319409</t>
-  </si>
-  <si>
     <t>e70487</t>
   </si>
   <si>
@@ -4625,9 +4625,6 @@
     <t>10.1186/s13690-025-01652-x</t>
   </si>
   <si>
-    <t>10.21203/rs.3.rs-5611920/v1</t>
-  </si>
-  <si>
     <t>Pre-pandemic sub-national disparities in the disease burden of ischemic heart disease and stroke in France</t>
   </si>
   <si>
@@ -4662,6 +4659,75 @@
   </si>
   <si>
     <t>Couchoud, Cécile; Raffray, Maxime; Mahrouseh, Nour; von der Lippe, Elena; Devleesschauwer, Brecht; Wyper, Grant M A; Haneef, Romana</t>
+  </si>
+  <si>
+    <t>10.1016/j.actatropica.2025.107828</t>
+  </si>
+  <si>
+    <t>10.1186/s12874-025-02661-8</t>
+  </si>
+  <si>
+    <t>Social inequalities in COVID-19-related years of life lost in metropolitan France, 2020</t>
+  </si>
+  <si>
+    <t>Haneef, Romana; Mahrouseh, Nour; Bessonneau, P; Vandentorren, Stephanie; Minier, N; Chin, F; Bruyère, Olivier; Devleesschauwer, Brecht; Wyper, Grant M A</t>
+  </si>
+  <si>
+    <t>10.1186/s13690-025-01704-2</t>
+  </si>
+  <si>
+    <t>Past trends, future forecasts and socio-demographic patterns of cigarette smoking in Belgium, 1997 to 2040</t>
+  </si>
+  <si>
+    <t>10.1186/s13690-025-01694-1</t>
+  </si>
+  <si>
+    <t>10.1016/j.puhe.2025.105981</t>
+  </si>
+  <si>
+    <t>10.1093/eurpub/ckaf190</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10.1186/s13690-025-01767-1 </t>
+  </si>
+  <si>
+    <t>Subtype-specific health and economic impact of delayed breast cancer diagnosis during the early COVID-19 pandemic in Belgium: a Markov model analysis</t>
+  </si>
+  <si>
+    <t>10.1186/s13058-025-02207-2</t>
+  </si>
+  <si>
+    <t>Breast Cancer Res.</t>
+  </si>
+  <si>
+    <t>Breast Cancer Research</t>
+  </si>
+  <si>
+    <t>Khan, Yasmine; Verhaeghe, Nick; Monten, Chris; Vanthomme, Katrien; Gadeyne, Sylvie; Devleesschauwer, Brecht; Verdoodt, Freija; Peacock, Hanna M; De Smedt, Delphine</t>
+  </si>
+  <si>
+    <t>Social inequalities in in-hospital mortality following COVID-19 hospitalization in Belgium: a competing risk survival analysis</t>
+  </si>
+  <si>
+    <t>BMC Health Services Research</t>
+  </si>
+  <si>
+    <t>BMC Health. Serv. Res.</t>
+  </si>
+  <si>
+    <t>Social inequalities in cause-specific premature mortality in rural and urban areas of mainland France using population attributable fractions (PAFs): a pre-pandemic analysis</t>
+  </si>
+  <si>
+    <t>Mahrouseh, Nour; Bonnet, Florian; Varga, Orsolya; Scohy, Aline; Bruyère, Olivier; Delpierre, Cyrille; Devleesschauwer, Brecht; Wyper, Grant M A;  Haneef, Romana</t>
+  </si>
+  <si>
+    <t>Boiy, Elin; Cavillot, Lisa; Devleesschauwer, Brecht; De Smedt, Delphine; Gadeyne, Sylvie; Speybroeck, Niko; Van den Borre, Laura; Vanthomme, Katrien; Verhaege, Nick; De Pauw, Robby</t>
+  </si>
+  <si>
+    <t>World Health Organization estimates of the global, regional, and national burden of seven foodborne bacterial and viral invasive enteric diseases and one foodborne intoxication, 2000-2021: an updated data synthesis</t>
+  </si>
+  <si>
+    <t>Majowicz, Shannon E; Scallan Walter, Elaine; Pires, Sara M; Minato, Yuki; Founou, Luria; Devleesschauwer, Brecht; Di Bari, Carlotta; Havelaar, Arie H; Vaes, Louise; Estrada Garcia, Teresa; Roberts, Charlee; Gobena, Tesfaye; Kumar, Ashok; Al Natour, Fadi; Lake, Robin J; Nane, Gabriela F; Fernandez, Kim; Crump, John A; Kirk, Martyn D</t>
   </si>
 </sst>
 </file>
@@ -5083,6 +5149,82 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5170,82 +5312,6 @@
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5260,74 +5326,74 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U279" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:U279" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U279">
-    <sortCondition ref="K1:K279"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U288" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="A1:U288" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U286">
+    <sortCondition ref="K1:K286"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="51"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="50" dataCellStyle="Neutral"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="47"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="46"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="45"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="44"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="43"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="42"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="22" dataCellStyle="Neutral"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="63">
   <autoFilter ref="A1:J12" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N50">
     <sortCondition ref="H1:H50"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="60"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G22" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:G22" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
-    <sortCondition ref="F1:F17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G19" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
+  <autoFilter ref="A1:G19" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
+    <sortCondition ref="F1:F16"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="44">
       <calculatedColumnFormula>TODAY()-F2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5336,18 +5402,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A1:F5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
     <sortCondition ref="E1:E14"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="36">
       <calculatedColumnFormula>(TODAY()-E2)/365</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5676,7 +5742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U288"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -19924,7 +19990,7 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>1213</v>
@@ -19945,7 +20011,7 @@
         <v>14</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="I263" s="18" t="s">
         <v>14</v>
@@ -19962,14 +20028,16 @@
       </c>
       <c r="N263" s="11"/>
       <c r="O263" s="19" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="P263" s="7"/>
       <c r="Q263" s="24"/>
       <c r="R263" s="25"/>
       <c r="S263" s="7"/>
       <c r="T263" s="7"/>
-      <c r="U263" s="7"/>
+      <c r="U263" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
@@ -20047,7 +20115,7 @@
         <v>101</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="I265" s="18" t="s">
         <v>14</v>
@@ -20064,27 +20132,29 @@
       </c>
       <c r="N265" s="11"/>
       <c r="O265" s="19" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="P265" s="7"/>
       <c r="Q265" s="24"/>
       <c r="R265" s="25"/>
       <c r="S265" s="7"/>
       <c r="T265" s="7"/>
-      <c r="U265" s="7"/>
+      <c r="U265" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B266" s="7" t="s">
         <v>1488</v>
-      </c>
-      <c r="B266" s="7" t="s">
-        <v>1489</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>267</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E266" s="18">
         <v>2025</v>
@@ -20113,14 +20183,16 @@
       </c>
       <c r="N266" s="11"/>
       <c r="O266" s="19" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="P266" s="7"/>
       <c r="Q266" s="24"/>
       <c r="R266" s="25"/>
       <c r="S266" s="7"/>
       <c r="T266" s="7"/>
-      <c r="U266" s="7"/>
+      <c r="U266" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
@@ -20162,18 +20234,20 @@
       </c>
       <c r="N267" s="11"/>
       <c r="O267" s="19" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="P267" s="7"/>
       <c r="Q267" s="24"/>
       <c r="R267" s="25"/>
       <c r="S267" s="7"/>
       <c r="T267" s="7"/>
-      <c r="U267" s="7"/>
+      <c r="U267" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B268" s="7" t="s">
         <v>1260</v>
@@ -20211,27 +20285,29 @@
       </c>
       <c r="N268" s="11"/>
       <c r="O268" s="19" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="P268" s="7"/>
       <c r="Q268" s="24"/>
       <c r="R268" s="25"/>
       <c r="S268" s="7"/>
       <c r="T268" s="7"/>
-      <c r="U268" s="7"/>
+      <c r="U268" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B269" s="7" t="s">
         <v>1480</v>
       </c>
-      <c r="B269" s="7" t="s">
+      <c r="C269" s="7" t="s">
         <v>1481</v>
       </c>
-      <c r="C269" s="7" t="s">
+      <c r="D269" s="7" t="s">
         <v>1482</v>
-      </c>
-      <c r="D269" s="7" t="s">
-        <v>1483</v>
       </c>
       <c r="E269" s="18">
         <v>2025</v>
@@ -20246,10 +20322,10 @@
         <v>14</v>
       </c>
       <c r="I269" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J269" s="18" t="s">
         <v>1484</v>
-      </c>
-      <c r="J269" s="18" t="s">
-        <v>1485</v>
       </c>
       <c r="K269" s="42">
         <v>45706</v>
@@ -20260,21 +20336,23 @@
       </c>
       <c r="N269" s="11"/>
       <c r="O269" s="19" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="P269" s="7"/>
       <c r="Q269" s="24"/>
       <c r="R269" s="25"/>
       <c r="S269" s="7"/>
       <c r="T269" s="7"/>
-      <c r="U269" s="7"/>
+      <c r="U269" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C270" s="7" t="s">
         <v>723</v>
@@ -20292,7 +20370,7 @@
         <v>548</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="I270" s="18" t="s">
         <v>14</v>
@@ -20309,21 +20387,23 @@
       </c>
       <c r="N270" s="11"/>
       <c r="O270" s="19" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="P270" s="7"/>
       <c r="Q270" s="24"/>
       <c r="R270" s="25"/>
       <c r="S270" s="7"/>
       <c r="T270" s="7"/>
-      <c r="U270" s="7"/>
+      <c r="U270" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>373</v>
@@ -20358,14 +20438,16 @@
       </c>
       <c r="N271" s="11"/>
       <c r="O271" s="19" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="P271" s="7"/>
       <c r="Q271" s="24"/>
       <c r="R271" s="25"/>
       <c r="S271" s="7"/>
       <c r="T271" s="7"/>
-      <c r="U271" s="7"/>
+      <c r="U271" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
@@ -20390,7 +20472,7 @@
         <v>548</v>
       </c>
       <c r="H272" s="18" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="I272" s="18" t="s">
         <v>14</v>
@@ -20407,27 +20489,29 @@
       </c>
       <c r="N272" s="11"/>
       <c r="O272" s="19" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="P272" s="7"/>
       <c r="Q272" s="24"/>
       <c r="R272" s="25"/>
       <c r="S272" s="7"/>
       <c r="T272" s="7"/>
-      <c r="U272" s="7"/>
+      <c r="U272" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B273" s="7" t="s">
         <v>1316</v>
       </c>
       <c r="C273" s="7" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D273" s="7" t="s">
         <v>1500</v>
-      </c>
-      <c r="D273" s="7" t="s">
-        <v>1501</v>
       </c>
       <c r="E273" s="18">
         <v>2025</v>
@@ -20456,21 +20540,23 @@
       </c>
       <c r="N273" s="11"/>
       <c r="O273" s="19" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="P273" s="7"/>
       <c r="Q273" s="24"/>
       <c r="R273" s="25"/>
       <c r="S273" s="7"/>
       <c r="T273" s="7"/>
-      <c r="U273" s="7"/>
+      <c r="U273" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C274" s="7" t="s">
         <v>723</v>
@@ -20488,7 +20574,7 @@
         <v>111</v>
       </c>
       <c r="H274" s="18" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="I274" s="18" t="s">
         <v>14</v>
@@ -20505,21 +20591,23 @@
       </c>
       <c r="N274" s="11"/>
       <c r="O274" s="19" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="P274" s="7"/>
       <c r="Q274" s="24"/>
       <c r="R274" s="25"/>
       <c r="S274" s="7"/>
       <c r="T274" s="7"/>
-      <c r="U274" s="7"/>
+      <c r="U274" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C275" s="7" t="s">
         <v>89</v>
@@ -20554,21 +20642,23 @@
       </c>
       <c r="N275" s="11"/>
       <c r="O275" s="19" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="P275" s="7"/>
       <c r="Q275" s="24"/>
       <c r="R275" s="25"/>
       <c r="S275" s="7"/>
       <c r="T275" s="7"/>
-      <c r="U275" s="7"/>
+      <c r="U275" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B276" s="7" t="s">
         <v>1494</v>
-      </c>
-      <c r="B276" s="7" t="s">
-        <v>1495</v>
       </c>
       <c r="C276" s="7" t="s">
         <v>267</v>
@@ -20603,14 +20693,16 @@
       </c>
       <c r="N276" s="11"/>
       <c r="O276" s="19" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="P276" s="7"/>
       <c r="Q276" s="24"/>
       <c r="R276" s="25"/>
       <c r="S276" s="7"/>
       <c r="T276" s="7"/>
-      <c r="U276" s="7"/>
+      <c r="U276" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
@@ -20652,21 +20744,23 @@
       </c>
       <c r="N277" s="11"/>
       <c r="O277" s="19" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="P277" s="7"/>
       <c r="Q277" s="24"/>
       <c r="R277" s="25"/>
       <c r="S277" s="7"/>
       <c r="T277" s="7"/>
-      <c r="U277" s="7"/>
+      <c r="U277" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>1346</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C278" s="7" t="s">
         <v>160</v>
@@ -20684,7 +20778,7 @@
         <v>153</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="I278" s="18" t="s">
         <v>14</v>
@@ -20701,66 +20795,513 @@
       </c>
       <c r="N278" s="11"/>
       <c r="O278" s="19" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="P278" s="7"/>
       <c r="Q278" s="24"/>
       <c r="R278" s="25"/>
       <c r="S278" s="7"/>
       <c r="T278" s="7"/>
-      <c r="U278" s="7"/>
+      <c r="U278" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A279" s="13" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B279" s="13" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C279" s="13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D279" s="13" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E279" s="14">
+      <c r="A279" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E279" s="18">
         <v>2025</v>
       </c>
-      <c r="F279" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G279" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H279" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I279" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J279" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K279" s="31">
-        <v>46023</v>
-      </c>
-      <c r="L279" s="31"/>
-      <c r="M279" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N279" s="45"/>
-      <c r="O279" s="44" t="s">
-        <v>1264</v>
-      </c>
-      <c r="P279" s="27"/>
+      <c r="F279" s="18">
+        <v>83</v>
+      </c>
+      <c r="G279" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H279" s="18">
+        <v>215</v>
+      </c>
+      <c r="I279" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J279" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K279" s="42">
+        <v>45891</v>
+      </c>
+      <c r="L279" s="42"/>
+      <c r="M279" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N279" s="11"/>
+      <c r="O279" s="19" t="s">
+        <v>1545</v>
+      </c>
+      <c r="P279" s="7"/>
       <c r="Q279" s="24"/>
       <c r="R279" s="25"/>
       <c r="S279" s="7"/>
       <c r="T279" s="7"/>
-      <c r="U279" s="7"/>
+      <c r="U279" s="7" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A280" s="7" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="E280" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F280" s="18">
+        <v>25</v>
+      </c>
+      <c r="G280" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H280" s="18">
+        <v>209</v>
+      </c>
+      <c r="I280" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J280" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K280" s="42">
+        <v>45902</v>
+      </c>
+      <c r="L280" s="42"/>
+      <c r="M280" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N280" s="11"/>
+      <c r="O280" s="19" t="s">
+        <v>1542</v>
+      </c>
+      <c r="P280" s="7"/>
+      <c r="Q280" s="24"/>
+      <c r="R280" s="25"/>
+      <c r="S280" s="7"/>
+      <c r="T280" s="7"/>
+      <c r="U280" s="7" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A281" s="7" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E281" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F281" s="18">
+        <v>270</v>
+      </c>
+      <c r="G281" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H281" s="18">
+        <v>107828</v>
+      </c>
+      <c r="I281" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J281" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K281" s="42">
+        <v>45931</v>
+      </c>
+      <c r="L281" s="42"/>
+      <c r="M281" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N281" s="11"/>
+      <c r="O281" s="19" t="s">
+        <v>1541</v>
+      </c>
+      <c r="P281" s="7"/>
+      <c r="Q281" s="24"/>
+      <c r="R281" s="25"/>
+      <c r="S281" s="7"/>
+      <c r="T281" s="7"/>
+      <c r="U281" s="7" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A282" s="7" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E282" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F282" s="18">
+        <v>83</v>
+      </c>
+      <c r="G282" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H282" s="18">
+        <v>256</v>
+      </c>
+      <c r="I282" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J282" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K282" s="42">
+        <v>45953</v>
+      </c>
+      <c r="L282" s="42"/>
+      <c r="M282" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N282" s="11"/>
+      <c r="O282" s="19" t="s">
+        <v>1547</v>
+      </c>
+      <c r="P282" s="7"/>
+      <c r="Q282" s="24"/>
+      <c r="R282" s="25"/>
+      <c r="S282" s="7"/>
+      <c r="T282" s="7"/>
+      <c r="U282" s="7"/>
+    </row>
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A283" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E283" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F283" s="18">
+        <v>35</v>
+      </c>
+      <c r="G283" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H283" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I283" s="18">
+        <v>1122</v>
+      </c>
+      <c r="J283" s="18">
+        <v>1128</v>
+      </c>
+      <c r="K283" s="42">
+        <v>45960</v>
+      </c>
+      <c r="L283" s="42"/>
+      <c r="M283" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N283" s="11"/>
+      <c r="O283" s="19" t="s">
+        <v>1549</v>
+      </c>
+      <c r="P283" s="7"/>
+      <c r="Q283" s="24"/>
+      <c r="R283" s="25"/>
+      <c r="S283" s="7"/>
+      <c r="T283" s="7"/>
+      <c r="U283" s="7"/>
+    </row>
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A284" s="7" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E284" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F284" s="18">
+        <v>248</v>
+      </c>
+      <c r="G284" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H284" s="18">
+        <v>105981</v>
+      </c>
+      <c r="I284" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J284" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K284" s="42">
+        <v>45962</v>
+      </c>
+      <c r="L284" s="42"/>
+      <c r="M284" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N284" s="11"/>
+      <c r="O284" s="19" t="s">
+        <v>1548</v>
+      </c>
+      <c r="P284" s="7"/>
+      <c r="Q284" s="24"/>
+      <c r="R284" s="25"/>
+      <c r="S284" s="7"/>
+      <c r="T284" s="7"/>
+      <c r="U284" s="7"/>
+    </row>
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A285" s="7" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E285" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F285" s="18">
+        <v>83</v>
+      </c>
+      <c r="G285" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H285" s="18">
+        <v>298</v>
+      </c>
+      <c r="I285" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J285" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K285" s="42">
+        <v>46001</v>
+      </c>
+      <c r="L285" s="42"/>
+      <c r="M285" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N285" s="11"/>
+      <c r="O285" s="19" t="s">
+        <v>1550</v>
+      </c>
+      <c r="P285" s="7"/>
+      <c r="Q285" s="24"/>
+      <c r="R285" s="25"/>
+      <c r="S285" s="7"/>
+      <c r="T285" s="7"/>
+      <c r="U285" s="7"/>
+    </row>
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A286" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B286" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C286" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D286" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E286" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F286" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G286" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H286" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I286" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J286" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K286" s="31">
+        <v>46023</v>
+      </c>
+      <c r="L286" s="31"/>
+      <c r="M286" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N286" s="45"/>
+      <c r="O286" s="44" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P286" s="27"/>
+      <c r="Q286" s="24"/>
+      <c r="R286" s="25"/>
+      <c r="S286" s="7"/>
+      <c r="T286" s="7"/>
+      <c r="U286" s="7"/>
+    </row>
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A287" s="13" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B287" s="13" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C287" s="13" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D287" s="13" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E287" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F287" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G287" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H287" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I287" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J287" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K287" s="31">
+        <v>46024</v>
+      </c>
+      <c r="L287" s="31"/>
+      <c r="M287" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N287" s="45"/>
+      <c r="O287" s="44" t="s">
+        <v>1552</v>
+      </c>
+      <c r="P287" s="27"/>
+      <c r="Q287" s="24"/>
+      <c r="R287" s="25"/>
+      <c r="S287" s="7"/>
+      <c r="T287" s="7"/>
+      <c r="U287" s="7"/>
+    </row>
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A288" s="13" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C288" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D288" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E288" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F288" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G288" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H288" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I288" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J288" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K288" s="31">
+        <v>46025</v>
+      </c>
+      <c r="L288" s="31"/>
+      <c r="M288" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N288" s="45"/>
+      <c r="O288" s="44"/>
+      <c r="P288" s="27"/>
+      <c r="Q288" s="24"/>
+      <c r="R288" s="25"/>
+      <c r="S288" s="7"/>
+      <c r="T288" s="7"/>
+      <c r="U288" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T248:V1048576 T243:V245 T246:U246">
+  <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T243:V245 T246:U246 T248:V1048576">
     <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
@@ -21187,7 +21728,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="40.7109375" customWidth="1"/>
@@ -21221,11 +21762,11 @@
       </c>
       <c r="I1" s="55" t="str">
         <f ca="1">ROUND(J1/30,0)&amp;" md"</f>
-        <v>5 md</v>
+        <v>8 md</v>
       </c>
       <c r="J1" s="55">
         <f ca="1">AVERAGE(G:G)</f>
-        <v>145.14285714285714</v>
+        <v>237.88888888888889</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>1164</v>
@@ -21249,8 +21790,8 @@
         <v>45488</v>
       </c>
       <c r="G2" s="12">
-        <f t="shared" ref="G2:G22" ca="1" si="0">TODAY()-F2</f>
-        <v>375</v>
+        <f t="shared" ref="G2:G19" ca="1" si="0">TODAY()-F2</f>
+        <v>535</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -21272,7 +21813,7 @@
       </c>
       <c r="G3" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>339</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -21294,7 +21835,7 @@
       </c>
       <c r="G4" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>301</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -21316,385 +21857,315 @@
       </c>
       <c r="G5" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1454</v>
+        <v>1314</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>89</v>
+        <v>723</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>723</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="10">
-        <v>45624</v>
+        <v>45705</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1451</v>
+        <v>1476</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>267</v>
+        <v>1477</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>1530</v>
-      </c>
+        <v>1478</v>
+      </c>
+      <c r="E7" s="7"/>
       <c r="F7" s="10">
-        <v>45636</v>
+        <v>45729</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>227</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1448</v>
+        <v>1510</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1449</v>
+        <v>1512</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>668</v>
+        <v>89</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>669</v>
+        <v>89</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="10">
-        <v>45637</v>
+        <v>45764</v>
       </c>
       <c r="G8" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>226</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1463</v>
+        <v>1514</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1464</v>
+        <v>1516</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1462</v>
+        <v>1111</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>1465</v>
-      </c>
+        <v>1112</v>
+      </c>
+      <c r="E9" s="7"/>
       <c r="F9" s="10">
-        <v>45663</v>
+        <v>45790</v>
       </c>
       <c r="G9" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1469</v>
+        <v>1513</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1470</v>
+        <v>1515</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>287</v>
+        <v>1557</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>330</v>
+        <v>1558</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="10">
-        <v>45671</v>
+        <v>45803</v>
       </c>
       <c r="G10" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>192</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1314</v>
+        <v>1537</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1318</v>
+        <v>1538</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>723</v>
+        <v>89</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>723</v>
+        <v>89</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="10">
-        <v>45705</v>
+        <v>45845</v>
       </c>
       <c r="G11" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>158</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1476</v>
+        <v>1508</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1477</v>
+        <v>1509</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1478</v>
+        <v>108</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1479</v>
+        <v>109</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="10">
-        <v>45729</v>
+        <v>45853</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>134</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1497</v>
+        <v>1529</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1498</v>
+        <v>1530</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>160</v>
+        <v>1531</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1313</v>
+        <v>1532</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="10">
-        <v>45735</v>
+        <v>45854</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1511</v>
+        <v>1533</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1513</v>
+        <v>1539</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>89</v>
+        <v>1024</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>89</v>
+        <v>1026</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="10">
-        <v>45764</v>
+        <v>45860</v>
       </c>
       <c r="G14" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1509</v>
+        <v>1534</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1510</v>
+        <v>1535</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>108</v>
+        <v>1024</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>109</v>
+        <v>1026</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="10">
-        <v>45853</v>
+        <v>45860</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1515</v>
+        <v>1546</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1111</v>
+        <v>108</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1112</v>
+        <v>109</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="10">
-        <v>45790</v>
+        <v>45896</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1514</v>
+        <v>1559</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1516</v>
+        <v>1560</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1111</v>
+        <v>108</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1112</v>
+        <v>109</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="10">
-        <v>45803</v>
+        <v>46008</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1531</v>
+        <v>1556</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1532</v>
+        <v>1561</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1533</v>
+        <v>1462</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1534</v>
+        <v>1462</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="10">
-        <v>45854</v>
+        <v>45944</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1535</v>
+        <v>1562</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1541</v>
+        <v>1563</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1024</v>
+        <v>120</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1026</v>
+        <v>121</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="10">
-        <v>45860</v>
+        <v>46023</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>1536</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10">
-        <v>45860</v>
-      </c>
-      <c r="G20" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>1538</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10">
-        <v>45848</v>
-      </c>
-      <c r="G21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10">
-        <v>45845</v>
-      </c>
-      <c r="G22" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21756,7 +22227,7 @@
       </c>
       <c r="F2" s="40">
         <f t="shared" ref="F2:F4" ca="1" si="0">(TODAY()-E2)/365</f>
-        <v>9.7397260273972606</v>
+        <v>10.178082191780822</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21777,7 +22248,7 @@
       </c>
       <c r="F3" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.7397260273972606</v>
+        <v>10.178082191780822</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21798,7 +22269,7 @@
       </c>
       <c r="F4" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.117808219178082</v>
+        <v>9.5561643835616437</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21819,7 +22290,7 @@
       </c>
       <c r="F5" s="40">
         <f ca="1">(TODAY()-E5)/365</f>
-        <v>7.4876712328767123</v>
+        <v>7.9260273972602739</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -23350,13 +23821,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B74" s="15">
         <v>2025</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>1044</v>

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13186BAF-33A1-411A-8A28-F0751E314714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA10AF8E-8101-4BA1-B61A-6B6BF7F47406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="1569">
   <si>
     <t>title</t>
   </si>
@@ -4728,6 +4728,21 @@
   </si>
   <si>
     <t>Majowicz, Shannon E; Scallan Walter, Elaine; Pires, Sara M; Minato, Yuki; Founou, Luria; Devleesschauwer, Brecht; Di Bari, Carlotta; Havelaar, Arie H; Vaes, Louise; Estrada Garcia, Teresa; Roberts, Charlee; Gobena, Tesfaye; Kumar, Ashok; Al Natour, Fadi; Lake, Robin J; Nane, Gabriela F; Fernandez, Kim; Crump, John A; Kirk, Martyn D</t>
+  </si>
+  <si>
+    <t>10.1007/s10389-025-02660-5</t>
+  </si>
+  <si>
+    <t>World Health Organization estimates of the global, regional, and national foodborne burdens of 14 invasive parasitic diseases from 2000 to 2021: an updated data synthesis</t>
+  </si>
+  <si>
+    <t>World Health Organization Estimates of the Global, Regional, and National Disease Burden of Nine Foodborne Chemicals, 2000-2021: An Updated Data Synthesis</t>
+  </si>
+  <si>
+    <t>Jakobsen, Lea Sletting; Agudo, Antonio; Vaes, Louise; Al Huthiel, Mohammed; Al Natour, Fadi; Di Bari, Carlotta; Devleesschauwer, Brecht; Nane, Gabiela F; Pires, Sara M; Thomsen, Sofie Theresa; Redondo, Hernan Gomez; Gibb, Herman; Lake, Robin J; Havelaar, Arie H; Roberts, Charlee; Minato, Yuki; Ingenbleek, Luc</t>
+  </si>
+  <si>
+    <t>Robertson, Lucy J; Minato, Yuki; Devleesschauwer, Brecht; Di Bari, Carlotta; Vaes, Louise; Keddy, Karen H; Sripa, Banchob; Fernandez, Kim; Pires, Sara M; Majowicz, Shannon E; Lake, Robin J; Roberts, Charlee; Nane, Gabriela F; Kretzschmar, Mirjam; Mughini-Gras, Lapo ; Rostami, Ali; Carabin, Hélène; Budke, Christine M; Donadeu, Meritxell; Torgerson, Paul R</t>
   </si>
 </sst>
 </file>
@@ -5149,82 +5164,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5312,6 +5251,82 @@
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5326,74 +5341,74 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U288" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <autoFilter ref="A1:U288" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U289" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:U289" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U286">
     <sortCondition ref="K1:K286"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="22" dataCellStyle="Neutral"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="authors" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="journal_full" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="journal_short" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="year" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="volume" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="issue" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="eID" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="from" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="to" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="date" dataDxfId="51"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="date_submitted" dataDxfId="50" dataCellStyle="Neutral"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="classification" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="IF" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DOI" dataDxfId="47"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="WoS" dataDxfId="46"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="rank" dataDxfId="45"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="quartile" dataDxfId="44"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="category" dataDxfId="43"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SC" dataDxfId="42"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="UGent" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabel14" displayName="Tabel14" ref="A1:J12" totalsRowShown="0" headerRowDxfId="40">
   <autoFilter ref="A1:J12" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N50">
     <sortCondition ref="H1:H50"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="60"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="54"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="title" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="authors" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="editors" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="book" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="year" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="from" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="to" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="date" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="IF" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="DOI" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G19" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
-  <autoFilter ref="A1:G19" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
-    <sortCondition ref="F1:F16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G20" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:G20" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
+    <sortCondition ref="F1:F15"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="authors" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="journal_full" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="journal_short" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doi_preprint" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="date" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="COUNT" dataDxfId="21">
       <calculatedColumnFormula>TODAY()-F2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5402,18 +5417,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabel135" displayName="Tabel135" ref="A1:F5" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:F5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
     <sortCondition ref="E1:E14"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="title" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="authors" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="journal_full" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="journal_short" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="date" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="COUNT" dataDxfId="13">
       <calculatedColumnFormula>(TODAY()-E2)/365</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5742,7 +5757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U288"/>
+  <dimension ref="A1:U289"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -21006,7 +21021,9 @@
       <c r="R282" s="25"/>
       <c r="S282" s="7"/>
       <c r="T282" s="7"/>
-      <c r="U282" s="7"/>
+      <c r="U282" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
@@ -21055,7 +21072,9 @@
       <c r="R283" s="25"/>
       <c r="S283" s="7"/>
       <c r="T283" s="7"/>
-      <c r="U283" s="7"/>
+      <c r="U283" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
@@ -21104,7 +21123,9 @@
       <c r="R284" s="25"/>
       <c r="S284" s="7"/>
       <c r="T284" s="7"/>
-      <c r="U284" s="7"/>
+      <c r="U284" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
@@ -21153,51 +21174,53 @@
       <c r="R285" s="25"/>
       <c r="S285" s="7"/>
       <c r="T285" s="7"/>
-      <c r="U285" s="7"/>
+      <c r="U285" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="286" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A286" s="13" t="s">
+      <c r="A286" s="7" t="s">
         <v>1093</v>
       </c>
-      <c r="B286" s="13" t="s">
+      <c r="B286" s="7" t="s">
         <v>1094</v>
       </c>
-      <c r="C286" s="13" t="s">
+      <c r="C286" s="7" t="s">
         <v>1095</v>
       </c>
-      <c r="D286" s="13" t="s">
+      <c r="D286" s="7" t="s">
         <v>1096</v>
       </c>
-      <c r="E286" s="14">
-        <v>2026</v>
-      </c>
-      <c r="F286" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G286" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H286" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I286" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J286" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K286" s="31">
-        <v>46023</v>
-      </c>
-      <c r="L286" s="31"/>
-      <c r="M286" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N286" s="45"/>
-      <c r="O286" s="44" t="s">
+      <c r="E286" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F286" s="18">
+        <v>33</v>
+      </c>
+      <c r="G286" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H286" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I286" s="18">
+        <v>2027</v>
+      </c>
+      <c r="J286" s="18">
+        <v>2038</v>
+      </c>
+      <c r="K286" s="42">
+        <v>45901</v>
+      </c>
+      <c r="L286" s="42"/>
+      <c r="M286" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N286" s="11"/>
+      <c r="O286" s="19" t="s">
         <v>1264</v>
       </c>
-      <c r="P286" s="27"/>
+      <c r="P286" s="7"/>
       <c r="Q286" s="24"/>
       <c r="R286" s="25"/>
       <c r="S286" s="7"/>
@@ -21299,6 +21322,55 @@
       <c r="S288" s="7"/>
       <c r="T288" s="7"/>
       <c r="U288" s="7"/>
+    </row>
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A289" s="13" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B289" s="13" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C289" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D289" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E289" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F289" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G289" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H289" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I289" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J289" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K289" s="31">
+        <v>46026</v>
+      </c>
+      <c r="L289" s="31"/>
+      <c r="M289" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N289" s="45"/>
+      <c r="O289" s="44" t="s">
+        <v>1564</v>
+      </c>
+      <c r="P289" s="27"/>
+      <c r="Q289" s="24"/>
+      <c r="R289" s="25"/>
+      <c r="S289" s="7"/>
+      <c r="T289" s="7"/>
+      <c r="U289" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T243:V245 T246:U246 T248:V1048576">
@@ -21728,7 +21800,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="40.7109375" customWidth="1"/>
@@ -21762,11 +21834,11 @@
       </c>
       <c r="I1" s="55" t="str">
         <f ca="1">ROUND(J1/30,0)&amp;" md"</f>
-        <v>8 md</v>
+        <v>7 md</v>
       </c>
       <c r="J1" s="55">
         <f ca="1">AVERAGE(G:G)</f>
-        <v>237.88888888888889</v>
+        <v>220.26315789473685</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>1164</v>
@@ -21790,8 +21862,8 @@
         <v>45488</v>
       </c>
       <c r="G2" s="12">
-        <f t="shared" ref="G2:G19" ca="1" si="0">TODAY()-F2</f>
-        <v>535</v>
+        <f t="shared" ref="G2:G20" ca="1" si="0">TODAY()-F2</f>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -21813,7 +21885,7 @@
       </c>
       <c r="G3" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>499</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -21835,213 +21907,213 @@
       </c>
       <c r="G4" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1335</v>
+        <v>1314</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1095</v>
+        <v>723</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1096</v>
+        <v>723</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="10">
-        <v>45624</v>
+        <v>45705</v>
       </c>
       <c r="G5" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>399</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1314</v>
+        <v>1475</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1318</v>
+        <v>1476</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>723</v>
+        <v>1477</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>723</v>
+        <v>1478</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="10">
-        <v>45705</v>
+        <v>45729</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1475</v>
+        <v>1510</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1476</v>
+        <v>1512</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1477</v>
+        <v>89</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1478</v>
+        <v>89</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="10">
-        <v>45729</v>
+        <v>45764</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>89</v>
+        <v>1111</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>1112</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="10">
-        <v>45764</v>
+        <v>45790</v>
       </c>
       <c r="G8" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1111</v>
+        <v>1557</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1112</v>
+        <v>1558</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="10">
-        <v>45790</v>
+        <v>45803</v>
       </c>
       <c r="G9" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1513</v>
+        <v>1537</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1515</v>
+        <v>1538</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1557</v>
+        <v>89</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1558</v>
+        <v>89</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="10">
-        <v>45803</v>
+        <v>45845</v>
       </c>
       <c r="G10" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>220</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1537</v>
+        <v>1508</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1538</v>
+        <v>1509</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="10">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="G11" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1508</v>
+        <v>1529</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1509</v>
+        <v>1530</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>108</v>
+        <v>1531</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>109</v>
+        <v>1532</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="10">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1531</v>
+        <v>1024</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1532</v>
+        <v>1026</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="10">
-        <v>45854</v>
+        <v>45860</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>1024</v>
@@ -22055,37 +22127,37 @@
       </c>
       <c r="G14" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1534</v>
+        <v>1546</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1535</v>
+        <v>1512</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1024</v>
+        <v>108</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1026</v>
+        <v>109</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="10">
-        <v>45860</v>
+        <v>45896</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1546</v>
+        <v>1559</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1512</v>
+        <v>1560</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>108</v>
@@ -22095,63 +22167,63 @@
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="10">
-        <v>45896</v>
+        <v>46008</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>127</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>108</v>
+        <v>1462</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>109</v>
+        <v>1462</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="10">
-        <v>46008</v>
+        <v>45944</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1462</v>
+        <v>120</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1462</v>
+        <v>121</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="10">
-        <v>45944</v>
+        <v>46023</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>120</v>
@@ -22161,11 +22233,33 @@
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="10">
-        <v>46023</v>
+        <v>46029</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="10">
+        <v>46038</v>
+      </c>
+      <c r="G20" s="12">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -22227,7 +22321,7 @@
       </c>
       <c r="F2" s="40">
         <f t="shared" ref="F2:F4" ca="1" si="0">(TODAY()-E2)/365</f>
-        <v>10.178082191780822</v>
+        <v>10.224657534246575</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22248,7 +22342,7 @@
       </c>
       <c r="F3" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>10.178082191780822</v>
+        <v>10.224657534246575</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22269,7 +22363,7 @@
       </c>
       <c r="F4" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5561643835616437</v>
+        <v>9.6027397260273979</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22290,7 +22384,7 @@
       </c>
       <c r="F5" s="40">
         <f ca="1">(TODAY()-E5)/365</f>
-        <v>7.9260273972602739</v>
+        <v>7.9726027397260273</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA10AF8E-8101-4BA1-B61A-6B6BF7F47406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066BEE09-E854-47E7-A895-FF344756ECF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="papers" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="1594">
   <si>
     <t>title</t>
   </si>
@@ -4007,9 +4007,6 @@
     <t>10.1186/s13023-024-03342-3</t>
   </si>
   <si>
-    <t>The role of vaccination, underlying health conditions, and working in healthcare in the socioeconomic disparities in COVID-19 hospitalization: A mediation analysis using interventional effect models</t>
-  </si>
-  <si>
     <t>Journal of Business &amp; Economic Statistics</t>
   </si>
   <si>
@@ -4743,16 +4740,93 @@
   </si>
   <si>
     <t>Robertson, Lucy J; Minato, Yuki; Devleesschauwer, Brecht; Di Bari, Carlotta; Vaes, Louise; Keddy, Karen H; Sripa, Banchob; Fernandez, Kim; Pires, Sara M; Majowicz, Shannon E; Lake, Robin J; Roberts, Charlee; Nane, Gabriela F; Kretzschmar, Mirjam; Mughini-Gras, Lapo ; Rostami, Ali; Carabin, Hélène; Budke, Christine M; Donadeu, Meritxell; Torgerson, Paul R</t>
+  </si>
+  <si>
+    <t>Journal of Exposure Science &amp; Environmental Epidemiology</t>
+  </si>
+  <si>
+    <t>J. Expo. Sci. Environ. Epidemiol.</t>
+  </si>
+  <si>
+    <t>10.1038/s41370-026-00856-9</t>
+  </si>
+  <si>
+    <t>10.1186/s12963-026-00467-4</t>
+  </si>
+  <si>
+    <t>10.1186/s12889-026-27054-4</t>
+  </si>
+  <si>
+    <t>10.1186/s12963-026-00464-7</t>
+  </si>
+  <si>
+    <t>The role of vaccination, underlying health conditions, and working in healthcare in the socioeconomic disparities in COVID-19 hospitalization: a mediation analysis using interventional effect models</t>
+  </si>
+  <si>
+    <t>10.1186/s12879-026-12907-5</t>
+  </si>
+  <si>
+    <t>10.1093/eurpub/ckaf254</t>
+  </si>
+  <si>
+    <t>10.1186/s12913-025-13949-2</t>
+  </si>
+  <si>
+    <t>Updated Estimates of the Global, Regional and National Burden, and Etiology of Diarrheal Diseases Transmissible via Food: A Systematic Review and Meta-Analytical Modelling Study for the World Health Organization</t>
+  </si>
+  <si>
+    <t>Colston, Josh M; Devleesschauwer, Brecht; Flynn, Thomas; Schiaffino, Francesca; Revathi,Adhvikaa Ambikapathi; Hossain, Nasif; Chen, Yen Ting; Meister, Danielle; Bagherian, Ava; Binggeli, Olivia; Zheng, Emily; David, Nhiya; Walter, Elaine Scallan; Kirk, Martyn D; Di Bari, Carlotta; Lake, Robin; Havelaar, Arie H; Pires, Sara M; Robertson; Lucy J; Minato, Yuki; Majowicz, Shannon E; Kosek, Margaret N</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10.64898/2026.01.26.26344508</t>
+  </si>
+  <si>
+    <t>From fish to fork: An analysis of the fishmeal feed chain &amp; presence of Anisakid material</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Schotte,Faust; Saelens, Ganna; Devleesschauwer, Brecht; Gabriël, Sarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Food Waterborne Parasitol.</t>
+  </si>
+  <si>
+    <t>e00328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.fawpar.2026.e00328 </t>
+  </si>
+  <si>
+    <t>World Health Organization Estimates of the Global, Regional, and National Burden of 14 Foodborne Diarrhoeal Enteric Hazards, 2000-2021: An Updated Data Synthesis</t>
+  </si>
+  <si>
+    <t>World Health Organization Estimates of the Global, Regional, and National Burden of 42 Foodborne Infectious and Chemical Hazards, 2000-2021</t>
+  </si>
+  <si>
+    <t>Lake, Robin J; Devleesschauwer, Brecht; Majowicz, Shannon E; Robertson, Lucy J; Jakobsen, Lea Sletting; Agudo, Antonio; Pires, Sara M; Kirk, Martyn D; Scallan Walter, Elaine; Keddy, Karen H; Di Bari, Carlotta; Vaes, Louise; Havelaar, Arie H; Roberts, Charlee; Gobena, Tesfaye; Kretzschmar, Mirjam; Nane, Gabriela F; Hoffmann, Sandra; Mughini-Gras, Lapo; Sripa, Banchob; Kubota, Kunihiro; Founou, Luria Lesley; Bai, Li; Al Huthiel, Mohammed; Rachmawati, Tety; Garcia, Teresa Estrada; Kumar, Ashok; Al Natour, Fadi; Jaffee, Steven; Henson, Spencer; Ingenbleek, Luc; Kumapley, Richard; Borghi, Elaine; Minato, Yuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majowicz, Shannon E; Colston, Josh M; Kirk, Martyn D; Pires, Sara M; Minato, Yuki; Founou, Luria; Devleesschauwer, Brecht; Di Bari, Carlotta; Garcia, Teresa Estrada; Vaes, Louise; Havelaar, Arie H; Roberts, Charlee; Gobena, Tesfaye; Kumar, Ashok; Al Natour, Fadi; Lake, Robin J; Nane, Gabriela F; Roberston, Lucy J; Fernandez, Kim; Scallan Walter, Elaine; Kosek, Margaret </t>
+  </si>
+  <si>
+    <t>Burden of disease attributable to dietary risk factors in Belgium: direct and indirect health impacts and the potential of a protein shift</t>
+  </si>
+  <si>
+    <t>Dénos, Claire; Gorasso, Vanessa; Boone, Lieselot; Cooreman-Algoed, Margot; Dewulf, Jo; Achten, Wouter M J; Devleesschauwer, Brecht; Moyersoen, Isabelle; Vandevijvere, Stefanie</t>
+  </si>
+  <si>
+    <t>A standardised approach to systematically select risk-outcome pairs in environmental burden of disease research</t>
+  </si>
+  <si>
+    <t>Haverkate, Tessa M I; Devleesschauwer, Brecht; Aasvang, Gunn Marit; Assunção, Ricardo; Breitner-Busch, Susanne; Buekers, Jurgen; Castro Fernández, Alberto; Gorasso, Vanessa; Hassen, Hamid Y; Kocbach Bølling, Anette; Martins, Carla; Charalampous, Periklis; Haagsma, Juanita A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -4986,7 +5060,7 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
@@ -4998,7 +5072,7 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5224,7 +5298,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -5279,15 +5353,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -5341,10 +5415,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U289" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:U289" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U286">
-    <sortCondition ref="K1:K286"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U297" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:U297" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U297">
+    <sortCondition ref="K1:K297"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="61"/>
@@ -5396,10 +5470,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G20" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:G20" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
-    <sortCondition ref="F1:F15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G18" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:G18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
+    <sortCondition ref="F1:F17"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="27"/>
@@ -5757,7 +5831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U289"/>
+  <dimension ref="A1:U297"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -19581,10 +19655,10 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B255" s="7" t="s">
         <v>1327</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>1328</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>813</v>
@@ -19619,7 +19693,7 @@
       </c>
       <c r="N255" s="11"/>
       <c r="O255" s="19" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="P255" s="7"/>
       <c r="Q255" s="24"/>
@@ -19725,7 +19799,7 @@
       </c>
       <c r="N257" s="11"/>
       <c r="O257" s="19" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="P257" s="7"/>
       <c r="Q257" s="24"/>
@@ -19778,7 +19852,7 @@
       </c>
       <c r="N258" s="11"/>
       <c r="O258" s="19" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="P258" s="7"/>
       <c r="Q258" s="24"/>
@@ -19793,10 +19867,10 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B259" s="7" t="s">
         <v>1337</v>
-      </c>
-      <c r="B259" s="7" t="s">
-        <v>1338</v>
       </c>
       <c r="C259" s="7" t="s">
         <v>1290</v>
@@ -19831,7 +19905,7 @@
       </c>
       <c r="N259" s="11"/>
       <c r="O259" s="19" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="P259" s="7"/>
       <c r="Q259" s="24"/>
@@ -19849,7 +19923,7 @@
         <v>1312</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>160</v>
@@ -19867,7 +19941,7 @@
         <v>69</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I260" s="18" t="s">
         <v>14</v>
@@ -19884,7 +19958,7 @@
       </c>
       <c r="N260" s="11"/>
       <c r="O260" s="19" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="P260" s="7"/>
       <c r="Q260" s="24"/>
@@ -19937,7 +20011,7 @@
       </c>
       <c r="N261" s="11"/>
       <c r="O261" s="19" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="P261" s="7"/>
       <c r="Q261" s="24"/>
@@ -19990,7 +20064,7 @@
       </c>
       <c r="N262" s="11"/>
       <c r="O262" s="19" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="P262" s="7"/>
       <c r="Q262" s="24"/>
@@ -20005,16 +20079,16 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>1213</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="E263" s="18">
         <v>2025</v>
@@ -20026,7 +20100,7 @@
         <v>14</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="I263" s="18" t="s">
         <v>14</v>
@@ -20043,7 +20117,7 @@
       </c>
       <c r="N263" s="11"/>
       <c r="O263" s="19" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="P263" s="7"/>
       <c r="Q263" s="24"/>
@@ -20056,10 +20130,10 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>1287</v>
@@ -20094,7 +20168,7 @@
       </c>
       <c r="N264" s="11"/>
       <c r="O264" s="19" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="P264" s="7"/>
       <c r="Q264" s="24"/>
@@ -20130,7 +20204,7 @@
         <v>101</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="I265" s="18" t="s">
         <v>14</v>
@@ -20147,7 +20221,7 @@
       </c>
       <c r="N265" s="11"/>
       <c r="O265" s="19" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="P265" s="7"/>
       <c r="Q265" s="24"/>
@@ -20160,16 +20234,16 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B266" s="7" t="s">
         <v>1487</v>
-      </c>
-      <c r="B266" s="7" t="s">
-        <v>1488</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>267</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="E266" s="18">
         <v>2025</v>
@@ -20198,7 +20272,7 @@
       </c>
       <c r="N266" s="11"/>
       <c r="O266" s="19" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="P266" s="7"/>
       <c r="Q266" s="24"/>
@@ -20249,7 +20323,7 @@
       </c>
       <c r="N267" s="11"/>
       <c r="O267" s="19" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="P267" s="7"/>
       <c r="Q267" s="24"/>
@@ -20262,7 +20336,7 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B268" s="7" t="s">
         <v>1260</v>
@@ -20300,7 +20374,7 @@
       </c>
       <c r="N268" s="11"/>
       <c r="O268" s="19" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="P268" s="7"/>
       <c r="Q268" s="24"/>
@@ -20313,16 +20387,16 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B269" s="7" t="s">
         <v>1479</v>
       </c>
-      <c r="B269" s="7" t="s">
+      <c r="C269" s="7" t="s">
         <v>1480</v>
       </c>
-      <c r="C269" s="7" t="s">
+      <c r="D269" s="7" t="s">
         <v>1481</v>
-      </c>
-      <c r="D269" s="7" t="s">
-        <v>1482</v>
       </c>
       <c r="E269" s="18">
         <v>2025</v>
@@ -20337,10 +20411,10 @@
         <v>14</v>
       </c>
       <c r="I269" s="18" t="s">
+        <v>1482</v>
+      </c>
+      <c r="J269" s="18" t="s">
         <v>1483</v>
-      </c>
-      <c r="J269" s="18" t="s">
-        <v>1484</v>
       </c>
       <c r="K269" s="42">
         <v>45706</v>
@@ -20351,7 +20425,7 @@
       </c>
       <c r="N269" s="11"/>
       <c r="O269" s="19" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="P269" s="7"/>
       <c r="Q269" s="24"/>
@@ -20364,10 +20438,10 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="C270" s="7" t="s">
         <v>723</v>
@@ -20385,7 +20459,7 @@
         <v>548</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="I270" s="18" t="s">
         <v>14</v>
@@ -20402,7 +20476,7 @@
       </c>
       <c r="N270" s="11"/>
       <c r="O270" s="19" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="P270" s="7"/>
       <c r="Q270" s="24"/>
@@ -20415,10 +20489,10 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>373</v>
@@ -20453,7 +20527,7 @@
       </c>
       <c r="N271" s="11"/>
       <c r="O271" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="P271" s="7"/>
       <c r="Q271" s="24"/>
@@ -20466,10 +20540,10 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B272" s="7" t="s">
         <v>1344</v>
-      </c>
-      <c r="B272" s="7" t="s">
-        <v>1345</v>
       </c>
       <c r="C272" s="7" t="s">
         <v>160</v>
@@ -20487,7 +20561,7 @@
         <v>548</v>
       </c>
       <c r="H272" s="18" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="I272" s="18" t="s">
         <v>14</v>
@@ -20504,7 +20578,7 @@
       </c>
       <c r="N272" s="11"/>
       <c r="O272" s="19" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="P272" s="7"/>
       <c r="Q272" s="24"/>
@@ -20517,16 +20591,16 @@
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B273" s="7" t="s">
         <v>1316</v>
       </c>
       <c r="C273" s="7" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D273" s="7" t="s">
         <v>1499</v>
-      </c>
-      <c r="D273" s="7" t="s">
-        <v>1500</v>
       </c>
       <c r="E273" s="18">
         <v>2025</v>
@@ -20555,7 +20629,7 @@
       </c>
       <c r="N273" s="11"/>
       <c r="O273" s="19" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="P273" s="7"/>
       <c r="Q273" s="24"/>
@@ -20568,10 +20642,10 @@
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C274" s="7" t="s">
         <v>723</v>
@@ -20589,7 +20663,7 @@
         <v>111</v>
       </c>
       <c r="H274" s="18" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="I274" s="18" t="s">
         <v>14</v>
@@ -20606,7 +20680,7 @@
       </c>
       <c r="N274" s="11"/>
       <c r="O274" s="19" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="P274" s="7"/>
       <c r="Q274" s="24"/>
@@ -20619,10 +20693,10 @@
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C275" s="7" t="s">
         <v>89</v>
@@ -20657,7 +20731,7 @@
       </c>
       <c r="N275" s="11"/>
       <c r="O275" s="19" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="P275" s="7"/>
       <c r="Q275" s="24"/>
@@ -20670,10 +20744,10 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B276" s="7" t="s">
         <v>1493</v>
-      </c>
-      <c r="B276" s="7" t="s">
-        <v>1494</v>
       </c>
       <c r="C276" s="7" t="s">
         <v>267</v>
@@ -20708,7 +20782,7 @@
       </c>
       <c r="N276" s="11"/>
       <c r="O276" s="19" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="P276" s="7"/>
       <c r="Q276" s="24"/>
@@ -20721,10 +20795,10 @@
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B277" s="7" t="s">
         <v>1452</v>
-      </c>
-      <c r="B277" s="7" t="s">
-        <v>1453</v>
       </c>
       <c r="C277" s="7" t="s">
         <v>89</v>
@@ -20759,7 +20833,7 @@
       </c>
       <c r="N277" s="11"/>
       <c r="O277" s="19" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="P277" s="7"/>
       <c r="Q277" s="24"/>
@@ -20772,10 +20846,10 @@
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C278" s="7" t="s">
         <v>160</v>
@@ -20793,7 +20867,7 @@
         <v>153</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="I278" s="18" t="s">
         <v>14</v>
@@ -20810,7 +20884,7 @@
       </c>
       <c r="N278" s="11"/>
       <c r="O278" s="19" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="P278" s="7"/>
       <c r="Q278" s="24"/>
@@ -20823,10 +20897,10 @@
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B279" s="7" t="s">
         <v>1543</v>
-      </c>
-      <c r="B279" s="7" t="s">
-        <v>1544</v>
       </c>
       <c r="C279" s="7" t="s">
         <v>267</v>
@@ -20861,7 +20935,7 @@
       </c>
       <c r="N279" s="11"/>
       <c r="O279" s="19" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="P279" s="7"/>
       <c r="Q279" s="24"/>
@@ -20874,37 +20948,37 @@
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
-        <v>1448</v>
+        <v>1093</v>
       </c>
       <c r="B280" s="7" t="s">
-        <v>1449</v>
+        <v>1094</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>668</v>
+        <v>1095</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>669</v>
+        <v>1096</v>
       </c>
       <c r="E280" s="18">
         <v>2025</v>
       </c>
       <c r="F280" s="18">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G280" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="H280" s="18">
-        <v>209</v>
-      </c>
-      <c r="I280" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J280" s="18" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="H280" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I280" s="18">
+        <v>2027</v>
+      </c>
+      <c r="J280" s="18">
+        <v>2038</v>
       </c>
       <c r="K280" s="42">
-        <v>45902</v>
+        <v>45901</v>
       </c>
       <c r="L280" s="42"/>
       <c r="M280" s="42" t="s">
@@ -20912,41 +20986,39 @@
       </c>
       <c r="N280" s="11"/>
       <c r="O280" s="19" t="s">
-        <v>1542</v>
+        <v>1264</v>
       </c>
       <c r="P280" s="7"/>
       <c r="Q280" s="24"/>
       <c r="R280" s="25"/>
       <c r="S280" s="7"/>
       <c r="T280" s="7"/>
-      <c r="U280" s="7" t="s">
-        <v>603</v>
-      </c>
+      <c r="U280" s="7"/>
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>1496</v>
+        <v>1447</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>1497</v>
+        <v>1448</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>133</v>
+        <v>668</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>134</v>
+        <v>669</v>
       </c>
       <c r="E281" s="18">
         <v>2025</v>
       </c>
       <c r="F281" s="18">
-        <v>270</v>
+        <v>25</v>
       </c>
       <c r="G281" s="19" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="H281" s="18">
-        <v>107828</v>
+        <v>209</v>
       </c>
       <c r="I281" s="18" t="s">
         <v>14</v>
@@ -20955,7 +21027,7 @@
         <v>14</v>
       </c>
       <c r="K281" s="42">
-        <v>45931</v>
+        <v>45902</v>
       </c>
       <c r="L281" s="42"/>
       <c r="M281" s="42" t="s">
@@ -20976,28 +21048,28 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
-        <v>1450</v>
+        <v>1495</v>
       </c>
       <c r="B282" s="7" t="s">
-        <v>1451</v>
+        <v>1496</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>267</v>
+        <v>133</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="E282" s="18">
         <v>2025</v>
       </c>
       <c r="F282" s="18">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="G282" s="19" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="H282" s="18">
-        <v>256</v>
+        <v>107828</v>
       </c>
       <c r="I282" s="18" t="s">
         <v>14</v>
@@ -21006,7 +21078,7 @@
         <v>14</v>
       </c>
       <c r="K282" s="42">
-        <v>45953</v>
+        <v>45931</v>
       </c>
       <c r="L282" s="42"/>
       <c r="M282" s="42" t="s">
@@ -21014,7 +21086,7 @@
       </c>
       <c r="N282" s="11"/>
       <c r="O282" s="19" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="P282" s="7"/>
       <c r="Q282" s="24"/>
@@ -21027,37 +21099,37 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>1468</v>
+        <v>1449</v>
       </c>
       <c r="B283" s="7" t="s">
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>330</v>
+        <v>268</v>
       </c>
       <c r="E283" s="18">
         <v>2025</v>
       </c>
       <c r="F283" s="18">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="G283" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="H283" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I283" s="18">
-        <v>1122</v>
-      </c>
-      <c r="J283" s="18">
-        <v>1128</v>
+        <v>101</v>
+      </c>
+      <c r="H283" s="18">
+        <v>256</v>
+      </c>
+      <c r="I283" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J283" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="K283" s="42">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="L283" s="42"/>
       <c r="M283" s="42" t="s">
@@ -21065,7 +21137,7 @@
       </c>
       <c r="N283" s="11"/>
       <c r="O283" s="19" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="P283" s="7"/>
       <c r="Q283" s="24"/>
@@ -21078,37 +21150,37 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="B284" s="7" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>1462</v>
+        <v>287</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>1462</v>
+        <v>330</v>
       </c>
       <c r="E284" s="18">
         <v>2025</v>
       </c>
       <c r="F284" s="18">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="G284" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H284" s="18">
-        <v>105981</v>
-      </c>
-      <c r="I284" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J284" s="18" t="s">
-        <v>14</v>
+        <v>111</v>
+      </c>
+      <c r="H284" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I284" s="18">
+        <v>1122</v>
+      </c>
+      <c r="J284" s="18">
+        <v>1128</v>
       </c>
       <c r="K284" s="42">
-        <v>45962</v>
+        <v>45960</v>
       </c>
       <c r="L284" s="42"/>
       <c r="M284" s="42" t="s">
@@ -21129,28 +21201,28 @@
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
-        <v>1536</v>
+        <v>1462</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>1540</v>
+        <v>1463</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>267</v>
+        <v>1461</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>268</v>
+        <v>1461</v>
       </c>
       <c r="E285" s="18">
         <v>2025</v>
       </c>
       <c r="F285" s="18">
-        <v>83</v>
+        <v>248</v>
       </c>
       <c r="G285" s="19" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="H285" s="18">
-        <v>298</v>
+        <v>105981</v>
       </c>
       <c r="I285" s="18" t="s">
         <v>14</v>
@@ -21159,7 +21231,7 @@
         <v>14</v>
       </c>
       <c r="K285" s="42">
-        <v>46001</v>
+        <v>45962</v>
       </c>
       <c r="L285" s="42"/>
       <c r="M285" s="42" t="s">
@@ -21167,7 +21239,7 @@
       </c>
       <c r="N285" s="11"/>
       <c r="O285" s="19" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="P285" s="7"/>
       <c r="Q285" s="24"/>
@@ -21180,37 +21252,37 @@
     </row>
     <row r="286" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
-        <v>1093</v>
+        <v>1535</v>
       </c>
       <c r="B286" s="7" t="s">
-        <v>1094</v>
+        <v>1539</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>1095</v>
+        <v>267</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>1096</v>
+        <v>268</v>
       </c>
       <c r="E286" s="18">
         <v>2025</v>
       </c>
       <c r="F286" s="18">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="G286" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H286" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I286" s="18">
-        <v>2027</v>
-      </c>
-      <c r="J286" s="18">
-        <v>2038</v>
+        <v>101</v>
+      </c>
+      <c r="H286" s="18">
+        <v>298</v>
+      </c>
+      <c r="I286" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J286" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="K286" s="42">
-        <v>45901</v>
+        <v>46001</v>
       </c>
       <c r="L286" s="42"/>
       <c r="M286" s="42" t="s">
@@ -21218,58 +21290,60 @@
       </c>
       <c r="N286" s="11"/>
       <c r="O286" s="19" t="s">
-        <v>1264</v>
+        <v>1549</v>
       </c>
       <c r="P286" s="7"/>
       <c r="Q286" s="24"/>
       <c r="R286" s="25"/>
       <c r="S286" s="7"/>
       <c r="T286" s="7"/>
-      <c r="U286" s="7"/>
+      <c r="U286" s="7" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="287" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A287" s="13" t="s">
+      <c r="A287" s="7" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E287" s="18">
+        <v>2025</v>
+      </c>
+      <c r="F287" s="18">
+        <v>28</v>
+      </c>
+      <c r="G287" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H287" s="18">
+        <v>41</v>
+      </c>
+      <c r="I287" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J287" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K287" s="42">
+        <v>46019</v>
+      </c>
+      <c r="L287" s="42"/>
+      <c r="M287" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N287" s="11"/>
+      <c r="O287" s="19" t="s">
         <v>1551</v>
       </c>
-      <c r="B287" s="13" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C287" s="13" t="s">
-        <v>1554</v>
-      </c>
-      <c r="D287" s="13" t="s">
-        <v>1553</v>
-      </c>
-      <c r="E287" s="14">
-        <v>2026</v>
-      </c>
-      <c r="F287" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G287" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H287" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I287" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J287" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K287" s="31">
-        <v>46024</v>
-      </c>
-      <c r="L287" s="31"/>
-      <c r="M287" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N287" s="45"/>
-      <c r="O287" s="44" t="s">
-        <v>1552</v>
-      </c>
-      <c r="P287" s="27"/>
+      <c r="P287" s="7"/>
       <c r="Q287" s="24"/>
       <c r="R287" s="25"/>
       <c r="S287" s="7"/>
@@ -21277,46 +21351,48 @@
       <c r="U287" s="7"/>
     </row>
     <row r="288" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A288" s="13" t="s">
-        <v>1454</v>
-      </c>
-      <c r="B288" s="13" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C288" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D288" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E288" s="14">
+      <c r="A288" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E288" s="18">
         <v>2026</v>
       </c>
-      <c r="F288" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G288" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H288" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I288" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J288" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K288" s="31">
-        <v>46025</v>
-      </c>
-      <c r="L288" s="31"/>
-      <c r="M288" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N288" s="45"/>
-      <c r="O288" s="44"/>
-      <c r="P288" s="27"/>
+      <c r="F288" s="18">
+        <v>26</v>
+      </c>
+      <c r="G288" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H288" s="18">
+        <v>266</v>
+      </c>
+      <c r="I288" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J288" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K288" s="42">
+        <v>46046</v>
+      </c>
+      <c r="L288" s="42"/>
+      <c r="M288" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N288" s="11"/>
+      <c r="O288" s="19" t="s">
+        <v>1577</v>
+      </c>
+      <c r="P288" s="7"/>
       <c r="Q288" s="24"/>
       <c r="R288" s="25"/>
       <c r="S288" s="7"/>
@@ -21324,53 +21400,443 @@
       <c r="U288" s="7"/>
     </row>
     <row r="289" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A289" s="13" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B289" s="13" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C289" s="13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D289" s="13" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E289" s="14">
+      <c r="A289" s="7" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E289" s="18">
         <v>2026</v>
       </c>
-      <c r="F289" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G289" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H289" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I289" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J289" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K289" s="31">
-        <v>46026</v>
-      </c>
-      <c r="L289" s="31"/>
-      <c r="M289" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N289" s="45"/>
-      <c r="O289" s="44" t="s">
-        <v>1564</v>
-      </c>
-      <c r="P289" s="27"/>
+      <c r="F289" s="18">
+        <v>26</v>
+      </c>
+      <c r="G289" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H289" s="18">
+        <v>497</v>
+      </c>
+      <c r="I289" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J289" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K289" s="42">
+        <v>46072</v>
+      </c>
+      <c r="L289" s="42"/>
+      <c r="M289" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N289" s="11"/>
+      <c r="O289" s="19" t="s">
+        <v>1575</v>
+      </c>
+      <c r="P289" s="7"/>
       <c r="Q289" s="24"/>
       <c r="R289" s="25"/>
       <c r="S289" s="7"/>
       <c r="T289" s="7"/>
       <c r="U289" s="7"/>
+    </row>
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A290" s="7" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E290" s="18">
+        <v>2026</v>
+      </c>
+      <c r="F290" s="18">
+        <v>43</v>
+      </c>
+      <c r="G290" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H290" s="18" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I290" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J290" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K290" s="42">
+        <v>46088</v>
+      </c>
+      <c r="L290" s="42"/>
+      <c r="M290" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N290" s="11"/>
+      <c r="O290" s="19" t="s">
+        <v>1585</v>
+      </c>
+      <c r="P290" s="7"/>
+      <c r="Q290" s="24"/>
+      <c r="R290" s="25"/>
+      <c r="S290" s="7"/>
+      <c r="T290" s="7"/>
+      <c r="U290" s="7"/>
+    </row>
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A291" s="7" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E291" s="18">
+        <v>2026</v>
+      </c>
+      <c r="F291" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G291" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H291" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I291" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J291" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K291" s="42">
+        <v>46098</v>
+      </c>
+      <c r="L291" s="42"/>
+      <c r="M291" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N291" s="11"/>
+      <c r="O291" s="19" t="s">
+        <v>1573</v>
+      </c>
+      <c r="P291" s="7"/>
+      <c r="Q291" s="24"/>
+      <c r="R291" s="25"/>
+      <c r="S291" s="7"/>
+      <c r="T291" s="7"/>
+      <c r="U291" s="7"/>
+    </row>
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A292" s="7" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E292" s="18">
+        <v>2026</v>
+      </c>
+      <c r="F292" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G292" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H292" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I292" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J292" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K292" s="42">
+        <v>46106</v>
+      </c>
+      <c r="L292" s="42"/>
+      <c r="M292" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N292" s="11"/>
+      <c r="O292" s="19" t="s">
+        <v>1572</v>
+      </c>
+      <c r="P292" s="7"/>
+      <c r="Q292" s="24"/>
+      <c r="R292" s="25"/>
+      <c r="S292" s="7"/>
+      <c r="T292" s="7"/>
+      <c r="U292" s="7"/>
+    </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A293" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E293" s="18">
+        <v>2026</v>
+      </c>
+      <c r="F293" s="18">
+        <v>24</v>
+      </c>
+      <c r="G293" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H293" s="18">
+        <v>21</v>
+      </c>
+      <c r="I293" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J293" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K293" s="42">
+        <v>46107</v>
+      </c>
+      <c r="L293" s="42"/>
+      <c r="M293" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N293" s="11"/>
+      <c r="O293" s="19" t="s">
+        <v>1571</v>
+      </c>
+      <c r="P293" s="7"/>
+      <c r="Q293" s="24"/>
+      <c r="R293" s="25"/>
+      <c r="S293" s="7"/>
+      <c r="T293" s="7"/>
+      <c r="U293" s="7"/>
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A294" s="7" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E294" s="18">
+        <v>2026</v>
+      </c>
+      <c r="F294" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G294" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H294" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I294" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J294" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K294" s="42">
+        <v>46118</v>
+      </c>
+      <c r="L294" s="42"/>
+      <c r="M294" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N294" s="11"/>
+      <c r="O294" s="19" t="s">
+        <v>1570</v>
+      </c>
+      <c r="P294" s="7"/>
+      <c r="Q294" s="24"/>
+      <c r="R294" s="25"/>
+      <c r="S294" s="7"/>
+      <c r="T294" s="7"/>
+      <c r="U294" s="7"/>
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A295" s="13" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B295" s="13" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C295" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D295" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E295" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F295" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G295" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H295" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I295" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J295" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K295" s="31">
+        <v>46389</v>
+      </c>
+      <c r="L295" s="31"/>
+      <c r="M295" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N295" s="45"/>
+      <c r="O295" s="44" t="s">
+        <v>1576</v>
+      </c>
+      <c r="P295" s="27"/>
+      <c r="Q295" s="24"/>
+      <c r="R295" s="25"/>
+      <c r="S295" s="7"/>
+      <c r="T295" s="7"/>
+      <c r="U295" s="7"/>
+    </row>
+    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A296" s="13" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C296" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D296" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E296" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F296" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G296" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H296" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I296" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J296" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K296" s="31">
+        <v>46390</v>
+      </c>
+      <c r="L296" s="31"/>
+      <c r="M296" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N296" s="45"/>
+      <c r="O296" s="44" t="s">
+        <v>1563</v>
+      </c>
+      <c r="P296" s="27"/>
+      <c r="Q296" s="24"/>
+      <c r="R296" s="25"/>
+      <c r="S296" s="7"/>
+      <c r="T296" s="7"/>
+      <c r="U296" s="7"/>
+    </row>
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A297" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B297" s="13" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C297" s="13" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D297" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E297" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F297" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G297" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H297" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I297" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J297" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K297" s="31">
+        <v>46391</v>
+      </c>
+      <c r="L297" s="31"/>
+      <c r="M297" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N297" s="45"/>
+      <c r="O297" s="44"/>
+      <c r="P297" s="27"/>
+      <c r="Q297" s="24"/>
+      <c r="R297" s="25"/>
+      <c r="S297" s="7"/>
+      <c r="T297" s="7"/>
+      <c r="U297" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T243:V245 T246:U246 T248:V1048576">
@@ -21800,7 +22266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="40.7109375" customWidth="1"/>
@@ -21838,7 +22304,7 @@
       </c>
       <c r="J1" s="55">
         <f ca="1">AVERAGE(G:G)</f>
-        <v>220.26315789473685</v>
+        <v>212.05882352941177</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>1164</v>
@@ -21852,414 +22318,372 @@
         <v>1306</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>1324</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>1325</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="10">
         <v>45488</v>
       </c>
       <c r="G2" s="12">
-        <f t="shared" ref="G2:G20" ca="1" si="0">TODAY()-F2</f>
-        <v>552</v>
+        <f ca="1">TODAY()-F2</f>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>252</v>
+        <v>1330</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>344</v>
+        <v>1333</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="10">
-        <v>45524</v>
+        <v>45562</v>
       </c>
       <c r="G3" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>516</v>
+        <f ca="1">TODAY()-F3</f>
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1332</v>
+        <v>1314</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1333</v>
+        <v>1318</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1331</v>
+        <v>723</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1334</v>
+        <v>723</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="10">
-        <v>45562</v>
+        <v>45705</v>
       </c>
       <c r="G4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>478</v>
+        <f ca="1">TODAY()-F4</f>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1314</v>
+        <v>1509</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1318</v>
+        <v>1511</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>723</v>
+        <v>89</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>723</v>
+        <v>89</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="10">
-        <v>45705</v>
+        <v>45764</v>
       </c>
       <c r="G5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>335</v>
+        <f ca="1">TODAY()-F5</f>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1475</v>
+        <v>1513</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1476</v>
+        <v>1515</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1477</v>
+        <v>1111</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1478</v>
+        <v>1112</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="10">
-        <v>45729</v>
+        <v>45790</v>
       </c>
       <c r="G6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>311</v>
+        <f ca="1">TODAY()-F6</f>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1510</v>
+        <v>1528</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1512</v>
+        <v>1529</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>89</v>
+        <v>1530</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>1531</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="10">
-        <v>45764</v>
+        <v>45854</v>
       </c>
       <c r="G7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>276</v>
+        <f ca="1">TODAY()-F7</f>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1514</v>
+        <v>1532</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1516</v>
+        <v>1538</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1111</v>
+        <v>1024</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1112</v>
+        <v>1026</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="10">
-        <v>45790</v>
+        <v>45860</v>
       </c>
       <c r="G8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>250</v>
+        <f ca="1">TODAY()-F8</f>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1513</v>
+        <v>1555</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1515</v>
+        <v>1560</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1557</v>
+        <v>1461</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1558</v>
+        <v>1461</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="10">
-        <v>45803</v>
+        <v>45944</v>
       </c>
       <c r="G9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>237</v>
+        <f ca="1">TODAY()-F9</f>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1537</v>
+        <v>1558</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1538</v>
+        <v>1559</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="10">
-        <v>45845</v>
+        <v>46008</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>195</v>
+        <f ca="1">TODAY()-F10</f>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1508</v>
+        <v>1561</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1509</v>
+        <v>1562</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="10">
-        <v>45853</v>
+        <v>46023</v>
       </c>
       <c r="G11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>187</v>
+        <f ca="1">TODAY()-F11</f>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1529</v>
+        <v>1564</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1530</v>
+        <v>1567</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1531</v>
+        <v>120</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1532</v>
+        <v>121</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="10">
-        <v>45854</v>
+        <v>46029</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>186</v>
+        <f ca="1">TODAY()-F12</f>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1533</v>
+        <v>1565</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1539</v>
+        <v>1566</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1024</v>
+        <v>120</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1026</v>
+        <v>121</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="10">
-        <v>45860</v>
+        <v>46038</v>
       </c>
       <c r="G13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>180</v>
+        <f ca="1">TODAY()-F13</f>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1534</v>
+        <v>1587</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1535</v>
+        <v>1588</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1024</v>
+        <v>120</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1026</v>
+        <v>121</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="10">
-        <v>45860</v>
+      <c r="F14" s="42">
+        <v>46044</v>
       </c>
       <c r="G14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>180</v>
+        <f ca="1">TODAY()-F14</f>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1546</v>
+        <v>1586</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1512</v>
+        <v>1589</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E15" s="7"/>
-      <c r="F15" s="10">
-        <v>45896</v>
+      <c r="F15" s="42">
+        <v>46047</v>
       </c>
       <c r="G15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>144</v>
+        <f ca="1">TODAY()-F15</f>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1559</v>
+        <v>1578</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1560</v>
+        <v>1579</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="10">
-        <v>46008</v>
+        <v>144</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F16" s="42">
+        <v>46072</v>
       </c>
       <c r="G16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">TODAY()-F16</f>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1556</v>
+        <v>1590</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1561</v>
+        <v>1591</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1462</v>
+        <v>89</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1462</v>
+        <v>89</v>
       </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="10">
-        <v>45944</v>
+      <c r="F17" s="42">
+        <v>46104</v>
       </c>
       <c r="G17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <f ca="1">TODAY()-F17</f>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1563</v>
+        <v>1593</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="10">
-        <v>46023</v>
+      <c r="F18" s="42">
+        <v>46086</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>1565</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>1568</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10">
-        <v>46029</v>
-      </c>
-      <c r="G19" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10">
-        <v>46038</v>
-      </c>
-      <c r="G20" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <f ca="1">TODAY()-F18</f>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -22321,7 +22745,7 @@
       </c>
       <c r="F2" s="40">
         <f t="shared" ref="F2:F4" ca="1" si="0">(TODAY()-E2)/365</f>
-        <v>10.224657534246575</v>
+        <v>10.441095890410958</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22342,7 +22766,7 @@
       </c>
       <c r="F3" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>10.224657534246575</v>
+        <v>10.441095890410958</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22363,7 +22787,7 @@
       </c>
       <c r="F4" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.6027397260273979</v>
+        <v>9.8191780821917813</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22384,7 +22808,7 @@
       </c>
       <c r="F5" s="40">
         <f ca="1">(TODAY()-E5)/365</f>
-        <v>7.9726027397260273</v>
+        <v>8.1890410958904116</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -22458,7 +22882,7 @@
         <v>1045</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C2" s="52" t="s">
         <v>175</v>
@@ -23232,16 +23656,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B40" s="15">
         <v>2024</v>
       </c>
       <c r="C40" s="49" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D40" s="49" t="s">
         <v>1352</v>
-      </c>
-      <c r="D40" s="49" t="s">
-        <v>1353</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>1044</v>
@@ -23252,16 +23676,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B41" s="15">
         <v>2024</v>
       </c>
       <c r="C41" s="49" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D41" s="49" t="s">
         <v>1354</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>1355</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>1044</v>
@@ -23272,16 +23696,16 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B42" s="15">
         <v>2024</v>
       </c>
       <c r="C42" s="49" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D42" s="49" t="s">
         <v>1358</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>1359</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>1044</v>
@@ -23295,16 +23719,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B43" s="15">
         <v>2024</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>1044</v>
@@ -23315,16 +23739,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B44" s="15">
         <v>2024</v>
       </c>
       <c r="C44" s="49" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D44" s="49" t="s">
         <v>1363</v>
-      </c>
-      <c r="D44" s="49" t="s">
-        <v>1364</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>1044</v>
@@ -23335,16 +23759,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B45" s="15">
         <v>2024</v>
       </c>
       <c r="C45" s="49" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D45" s="49" t="s">
         <v>1366</v>
-      </c>
-      <c r="D45" s="49" t="s">
-        <v>1367</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>1044</v>
@@ -23355,16 +23779,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B46" s="15">
         <v>2024</v>
       </c>
       <c r="C46" s="49" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D46" s="49" t="s">
         <v>1369</v>
-      </c>
-      <c r="D46" s="49" t="s">
-        <v>1370</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>1044</v>
@@ -23375,16 +23799,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B47" s="15">
         <v>2024</v>
       </c>
       <c r="C47" s="49" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D47" s="49" t="s">
         <v>1372</v>
-      </c>
-      <c r="D47" s="49" t="s">
-        <v>1373</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>1044</v>
@@ -23395,16 +23819,16 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B48" s="15">
         <v>2024</v>
       </c>
       <c r="C48" s="49" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D48" s="49" t="s">
         <v>1375</v>
-      </c>
-      <c r="D48" s="49" t="s">
-        <v>1376</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>1044</v>
@@ -23415,16 +23839,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B49" s="15">
         <v>2024</v>
       </c>
       <c r="C49" s="49" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D49" s="49" t="s">
         <v>1378</v>
-      </c>
-      <c r="D49" s="49" t="s">
-        <v>1379</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>1044</v>
@@ -23435,16 +23859,16 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B50" s="15">
         <v>2024</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>1044</v>
@@ -23455,16 +23879,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B51" s="15">
         <v>2024</v>
       </c>
       <c r="C51" s="49" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D51" s="49" t="s">
         <v>1384</v>
-      </c>
-      <c r="D51" s="49" t="s">
-        <v>1385</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>1044</v>
@@ -23475,16 +23899,16 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B52" s="15">
         <v>2024</v>
       </c>
       <c r="C52" s="49" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D52" s="49" t="s">
         <v>1387</v>
-      </c>
-      <c r="D52" s="49" t="s">
-        <v>1388</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>1044</v>
@@ -23495,16 +23919,16 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B53" s="15">
         <v>2024</v>
       </c>
       <c r="C53" s="49" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D53" s="49" t="s">
         <v>1390</v>
-      </c>
-      <c r="D53" s="49" t="s">
-        <v>1391</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1044</v>
@@ -23515,16 +23939,16 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B54" s="15">
         <v>2024</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>1044</v>
@@ -23535,16 +23959,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B55" s="15">
         <v>2024</v>
       </c>
       <c r="C55" s="49" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D55" s="49" t="s">
         <v>1396</v>
-      </c>
-      <c r="D55" s="49" t="s">
-        <v>1397</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>1044</v>
@@ -23555,16 +23979,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B56" s="15">
         <v>2024</v>
       </c>
       <c r="C56" s="49" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D56" s="49" t="s">
         <v>1399</v>
-      </c>
-      <c r="D56" s="49" t="s">
-        <v>1400</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>1044</v>
@@ -23575,16 +23999,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B57" s="15">
         <v>2024</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>1044</v>
@@ -23595,16 +24019,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B58" s="15">
         <v>2024</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>1044</v>
@@ -23615,16 +24039,16 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B59" s="15">
         <v>2024</v>
       </c>
       <c r="C59" s="49" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D59" s="49" t="s">
         <v>1408</v>
-      </c>
-      <c r="D59" s="49" t="s">
-        <v>1409</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>1044</v>
@@ -23635,16 +24059,16 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B60" s="15">
         <v>2024</v>
       </c>
       <c r="C60" s="49" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D60" s="49" t="s">
         <v>1411</v>
-      </c>
-      <c r="D60" s="49" t="s">
-        <v>1412</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>1044</v>
@@ -23655,16 +24079,16 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B61" s="15">
         <v>2024</v>
       </c>
       <c r="C61" s="49" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D61" s="49" t="s">
         <v>1414</v>
-      </c>
-      <c r="D61" s="49" t="s">
-        <v>1415</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>1044</v>
@@ -23675,16 +24099,16 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B62" s="15">
         <v>2024</v>
       </c>
       <c r="C62" s="49" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D62" s="49" t="s">
         <v>1417</v>
-      </c>
-      <c r="D62" s="49" t="s">
-        <v>1418</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>1044</v>
@@ -23695,16 +24119,16 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B63" s="15">
         <v>2024</v>
       </c>
       <c r="C63" s="49" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D63" s="49" t="s">
         <v>1420</v>
-      </c>
-      <c r="D63" s="49" t="s">
-        <v>1421</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>1044</v>
@@ -23715,16 +24139,16 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B64" s="15">
         <v>2024</v>
       </c>
       <c r="C64" s="49" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D64" s="49" t="s">
         <v>1423</v>
-      </c>
-      <c r="D64" s="49" t="s">
-        <v>1424</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>1044</v>
@@ -23735,16 +24159,16 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B65" s="15">
         <v>2024</v>
       </c>
       <c r="C65" s="49" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D65" s="49" t="s">
         <v>1426</v>
-      </c>
-      <c r="D65" s="49" t="s">
-        <v>1427</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>1044</v>
@@ -23755,16 +24179,16 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B66" s="15">
         <v>2024</v>
       </c>
       <c r="C66" s="49" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D66" s="49" t="s">
         <v>1429</v>
-      </c>
-      <c r="D66" s="49" t="s">
-        <v>1430</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>1044</v>
@@ -23775,16 +24199,16 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B67" s="15">
         <v>2024</v>
       </c>
       <c r="C67" s="49" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D67" s="49" t="s">
         <v>1432</v>
-      </c>
-      <c r="D67" s="49" t="s">
-        <v>1433</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>1044</v>
@@ -23795,16 +24219,16 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B68" s="15">
         <v>2024</v>
       </c>
       <c r="C68" s="49" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D68" s="49" t="s">
         <v>1435</v>
-      </c>
-      <c r="D68" s="49" t="s">
-        <v>1436</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>1044</v>
@@ -23815,16 +24239,16 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B69" s="15">
         <v>2024</v>
       </c>
       <c r="C69" s="49" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D69" s="49" t="s">
         <v>1438</v>
-      </c>
-      <c r="D69" s="49" t="s">
-        <v>1439</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>1044</v>
@@ -23835,16 +24259,16 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B70" s="15">
         <v>2024</v>
       </c>
       <c r="C70" s="49" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D70" s="49" t="s">
         <v>1441</v>
-      </c>
-      <c r="D70" s="49" t="s">
-        <v>1442</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>1044</v>
@@ -23855,16 +24279,16 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B71" s="15">
         <v>2024</v>
       </c>
       <c r="C71" s="49" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D71" s="49" t="s">
         <v>1443</v>
-      </c>
-      <c r="D71" s="49" t="s">
-        <v>1444</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>1044</v>
@@ -23875,19 +24299,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B72" s="15">
         <v>2024</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G72" s="48" t="s">
         <v>1037</v>
@@ -23895,19 +24319,19 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B73" s="15">
         <v>2024</v>
       </c>
       <c r="C73" s="49" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D73" s="49" t="s">
         <v>1460</v>
       </c>
-      <c r="D73" s="49" t="s">
-        <v>1461</v>
-      </c>
       <c r="E73" s="15" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G73" s="48" t="s">
         <v>1037</v>
@@ -23915,13 +24339,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B74" s="15">
         <v>2025</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>1044</v>

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066BEE09-E854-47E7-A895-FF344756ECF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C822A8-1252-4DE5-877B-1F57B688268A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="papers" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="1594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3849" uniqueCount="1602">
   <si>
     <t>title</t>
   </si>
@@ -3977,9 +3977,6 @@
     <t>Accuracy of immunological tests on serum and urine for diagnosis of Taenia solium neurocysticercosis: A systematic review</t>
   </si>
   <si>
-    <t>PLOS Neglect. Trop. Dis.</t>
-  </si>
-  <si>
     <t>The role of socio-economic determinants in SARS-CoV-2 health outcomes: systematic review of population-based studies</t>
   </si>
   <si>
@@ -4460,12 +4457,6 @@
     <t>https://doi.org/10.3389/fvets.2025.1476505</t>
   </si>
   <si>
-    <t>One-year post-acute organ complications following COVID-19 hospitalization and related socioeconomic inequalities</t>
-  </si>
-  <si>
-    <t>Cavillot, Lisa; Speybroeck, Niko; Van den Borre, Laura; Ghattas, Jinane; Boiy, Elin; van Loenhout, Joris; Hubin, Pierre; Smith, Pierre; De Smedt, Delphine; Vanthomme, Katrien; Gadeyne, Sylvie; De Pauw, Robby; Devleesschauwer, Brecht</t>
-  </si>
-  <si>
     <t>Nature Communications</t>
   </si>
   <si>
@@ -4577,15 +4568,9 @@
     <t>Post-acute healthcare expenditure following COVID-19 hospitalization and associated social inequalities in Belgium: a matched cohort study</t>
   </si>
   <si>
-    <t>Years of life lost due to COVID-19 attributable to social deprivation in metropolitan France, 2020</t>
-  </si>
-  <si>
     <t>Boiy, Elin; Cavillot, Lisa; Devleesschauwer, Brecht; De Pauw, Robby; De Smedt, Delphine; Gadeyne, Sylvie; Gorasso, Vanessa; Schmidt, Masja; Vanthomme, Katrien; Verhaege, Nick; Van den Borre, Laura</t>
   </si>
   <si>
-    <t xml:space="preserve">Haneef, Romana; Mahrouseh, Nour; Bessonneau, Pascal; Vandentorren, Stephanie; Minier, Nicolas; Chin, Francis; Bruyère, Olivier; Devleesschauwer, Brecht; Wyper, Grant M A </t>
-  </si>
-  <si>
     <t>Impact assessment of local traffic interventions on disease burden: A case study on paediatric asthma incidence in two European cities</t>
   </si>
   <si>
@@ -4625,9 +4610,6 @@
     <t>Pre-pandemic sub-national disparities in the disease burden of ischemic heart disease and stroke in France</t>
   </si>
   <si>
-    <t>Haneef, Romana; Monzo, Luca; Mahrouseh, Nour; von der Lippe, Elena; Devleesschauwer, Brecht; Wyper, Grant M A</t>
-  </si>
-  <si>
     <t>BMC Cardiovascular Disorders</t>
   </si>
   <si>
@@ -4712,9 +4694,6 @@
     <t>BMC Health. Serv. Res.</t>
   </si>
   <si>
-    <t>Social inequalities in cause-specific premature mortality in rural and urban areas of mainland France using population attributable fractions (PAFs): a pre-pandemic analysis</t>
-  </si>
-  <si>
     <t>Mahrouseh, Nour; Bonnet, Florian; Varga, Orsolya; Scohy, Aline; Bruyère, Olivier; Delpierre, Cyrille; Devleesschauwer, Brecht; Wyper, Grant M A;  Haneef, Romana</t>
   </si>
   <si>
@@ -4784,9 +4763,6 @@
     <t>From fish to fork: An analysis of the fishmeal feed chain &amp; presence of Anisakid material</t>
   </si>
   <si>
-    <t xml:space="preserve"> Schotte,Faust; Saelens, Ganna; Devleesschauwer, Brecht; Gabriël, Sarah</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Food Waterborne Parasitol.</t>
   </si>
   <si>
@@ -4818,6 +4794,55 @@
   </si>
   <si>
     <t>Haverkate, Tessa M I; Devleesschauwer, Brecht; Aasvang, Gunn Marit; Assunção, Ricardo; Breitner-Busch, Susanne; Buekers, Jurgen; Castro Fernández, Alberto; Gorasso, Vanessa; Hassen, Hamid Y; Kocbach Bølling, Anette; Martins, Carla; Charalampous, Periklis; Haagsma, Juanita A</t>
+  </si>
+  <si>
+    <t>Monzo, Luca; Mahrouseh, Nour; von der Lippe, Elena; Devleesschauwer, Brecht; Wyper, Grant M A; Haneef, Romana</t>
+  </si>
+  <si>
+    <t>10.1186/s12872-026-05960-0</t>
+  </si>
+  <si>
+    <t>The plight of the Monaco microstate in the GBD 2023 study</t>
+  </si>
+  <si>
+    <t>Wyper, Grant M A; Cuschieri, Sarah; Devleesschauwer, Brecht</t>
+  </si>
+  <si>
+    <t>10.1016/S0140-6736(26)00042-5</t>
+  </si>
+  <si>
+    <t>10542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Prevalence and risk factors related to Fasciola spp. transmission in north-Central Vietnam: A cross-sectional study in multiple host and environmental compartments</t>
+  </si>
+  <si>
+    <t>Vinh, H Q; Levecke, Bruno; Dung, D T; Binh, V T L; Hien, N T T; Ha, N N; Thanh, D T H; Devleesschauwer, Brecht; de Jong, Theo; Paredis, L; De Wilde, Nathalie; Casaert, Stijn; Polman, Katja; Callens, Steven; Dorny, Pierre; Dermauw, Veronique</t>
+  </si>
+  <si>
+    <t>10.1016/j.onehlt.2026.101417</t>
+  </si>
+  <si>
+    <t>Schotte,Faust; Saelens, Ganna; Devleesschauwer, Brecht; Gabriël, Sarah</t>
+  </si>
+  <si>
+    <t>Post-acute organ complications within one year following COVID-19 hospitalization and related socioeconomic inequalities</t>
+  </si>
+  <si>
+    <t>Cavillot, Lisa; Van den Borre, Laura; Ghattas, Jinane; Boiy, Elin; van Loenhout, Joris; Hubin, Pierre; Smith, Pierre; De Smedt, Delphine; Vanthomme, Katrien; Gadeyne, Sylvie; De Pauw, Robby; Speybroeck, Niko; Devleesschauwer, Brecht</t>
+  </si>
+  <si>
+    <t>Guariguata, Leonor; Nayani, Sarah; Croes, Sarah; Schmidt, Masja; Gisle, Lydia; Vynckier, Pieter; Verhaeghe, Nick; De Pauw, Robby; Devleesschauwer, Brecht</t>
+  </si>
+  <si>
+    <t>Social inequalities in cause-specific premature mortality in rural and urban France: a pre-pandemic population attributable fraction analysis</t>
+  </si>
+  <si>
+    <t>Listeriosis trends in 26 EU/EEA countries, 2010–2022</t>
+  </si>
+  <si>
+    <t>Speybroeck, Niko; Devleesschauwer, Brecht; Charalampous, Periklis; Delforge, Damien; Sanaa, Moez; Brandt, Patrick</t>
   </si>
 </sst>
 </file>
@@ -5415,10 +5440,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U297" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:U297" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U297">
-    <sortCondition ref="K1:K297"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabel1" displayName="Tabel1" ref="A1:U301" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:U301" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U300">
+    <sortCondition ref="K1:K300"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" dataDxfId="61"/>
@@ -5470,10 +5495,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G18" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:G18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
-    <sortCondition ref="F1:F17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabel13" displayName="Tabel13" ref="A1:G16" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:G16" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
+    <sortCondition ref="F1:F14"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="title" dataDxfId="27"/>
@@ -5831,25 +5856,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U297"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U301"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="8.85546875" style="2" customWidth="1"/>
-    <col min="11" max="12" width="11.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="33.28515625" style="2" customWidth="1"/>
-    <col min="16" max="18" width="8.85546875" customWidth="1"/>
+    <col min="1" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="2" customWidth="1"/>
+    <col min="9" max="10" width="8.88671875" style="2" customWidth="1"/>
+    <col min="11" max="12" width="11.5546875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" customWidth="1"/>
+    <col min="15" max="15" width="33.33203125" style="2" customWidth="1"/>
+    <col min="16" max="18" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5914,7 +5939,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>38</v>
       </c>
@@ -5969,7 +5994,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>40</v>
       </c>
@@ -6026,7 +6051,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
@@ -6083,7 +6108,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
@@ -6140,7 +6165,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -6197,7 +6222,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>19</v>
       </c>
@@ -6252,7 +6277,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -6309,7 +6334,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>37</v>
       </c>
@@ -6366,7 +6391,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>33</v>
       </c>
@@ -6423,7 +6448,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>34</v>
       </c>
@@ -6480,7 +6505,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -6537,7 +6562,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -6594,7 +6619,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
@@ -6651,7 +6676,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>9</v>
       </c>
@@ -6708,7 +6733,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>15</v>
       </c>
@@ -6765,7 +6790,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>70</v>
       </c>
@@ -6822,7 +6847,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>72</v>
       </c>
@@ -6879,7 +6904,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
@@ -6936,7 +6961,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>90</v>
       </c>
@@ -6993,7 +7018,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>611</v>
       </c>
@@ -7050,7 +7075,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>74</v>
       </c>
@@ -7107,7 +7132,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>103</v>
       </c>
@@ -7164,7 +7189,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>73</v>
       </c>
@@ -7221,7 +7246,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>126</v>
       </c>
@@ -7278,7 +7303,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>113</v>
       </c>
@@ -7335,7 +7360,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>97</v>
       </c>
@@ -7392,7 +7417,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>137</v>
       </c>
@@ -7449,7 +7474,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>609</v>
       </c>
@@ -7506,7 +7531,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>110</v>
       </c>
@@ -7563,7 +7588,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>118</v>
       </c>
@@ -7620,7 +7645,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>189</v>
       </c>
@@ -7677,7 +7702,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>163</v>
       </c>
@@ -7734,7 +7759,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>154</v>
       </c>
@@ -7791,7 +7816,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>146</v>
       </c>
@@ -7848,7 +7873,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>124</v>
       </c>
@@ -7905,7 +7930,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>143</v>
       </c>
@@ -7962,7 +7987,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>122</v>
       </c>
@@ -8019,7 +8044,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>140</v>
       </c>
@@ -8080,7 +8105,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>157</v>
       </c>
@@ -8141,7 +8166,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>130</v>
       </c>
@@ -8202,7 +8227,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>127</v>
       </c>
@@ -8263,7 +8288,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>166</v>
       </c>
@@ -8324,7 +8349,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>158</v>
       </c>
@@ -8385,7 +8410,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>151</v>
       </c>
@@ -8446,7 +8471,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>247</v>
       </c>
@@ -8507,7 +8532,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>173</v>
       </c>
@@ -8568,7 +8593,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>254</v>
       </c>
@@ -8629,7 +8654,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>354</v>
       </c>
@@ -8690,7 +8715,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>289</v>
       </c>
@@ -8749,7 +8774,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>164</v>
       </c>
@@ -8810,7 +8835,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>257</v>
       </c>
@@ -8871,7 +8896,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>135</v>
       </c>
@@ -8926,7 +8951,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>131</v>
       </c>
@@ -8981,7 +9006,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>336</v>
       </c>
@@ -9036,7 +9061,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>265</v>
       </c>
@@ -9091,7 +9116,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>242</v>
       </c>
@@ -9150,7 +9175,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="58" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>263</v>
       </c>
@@ -9205,7 +9230,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>340</v>
       </c>
@@ -9260,7 +9285,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>408</v>
       </c>
@@ -9315,7 +9340,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>418</v>
       </c>
@@ -9370,7 +9395,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>348</v>
       </c>
@@ -9425,7 +9450,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>331</v>
       </c>
@@ -9480,7 +9505,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>412</v>
       </c>
@@ -9535,7 +9560,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>455</v>
       </c>
@@ -9590,7 +9615,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>432</v>
       </c>
@@ -9645,7 +9670,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>358</v>
       </c>
@@ -9700,7 +9725,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>367</v>
       </c>
@@ -9759,7 +9784,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>363</v>
       </c>
@@ -9814,7 +9839,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>435</v>
       </c>
@@ -9869,7 +9894,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>413</v>
       </c>
@@ -9928,7 +9953,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>191</v>
       </c>
@@ -9983,7 +10008,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>285</v>
       </c>
@@ -10038,7 +10063,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>382</v>
       </c>
@@ -10093,7 +10118,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>420</v>
       </c>
@@ -10148,7 +10173,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>472</v>
       </c>
@@ -10203,7 +10228,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>446</v>
       </c>
@@ -10258,7 +10283,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>610</v>
       </c>
@@ -10313,7 +10338,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>388</v>
       </c>
@@ -10368,7 +10393,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>260</v>
       </c>
@@ -10423,7 +10448,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>456</v>
       </c>
@@ -10478,7 +10503,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>371</v>
       </c>
@@ -10533,7 +10558,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>463</v>
       </c>
@@ -10588,7 +10613,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>454</v>
       </c>
@@ -10643,7 +10668,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>269</v>
       </c>
@@ -10702,7 +10727,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>452</v>
       </c>
@@ -10757,7 +10782,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>473</v>
       </c>
@@ -10812,7 +10837,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>461</v>
       </c>
@@ -10867,7 +10892,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>495</v>
       </c>
@@ -10922,7 +10947,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>457</v>
       </c>
@@ -10977,7 +11002,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>530</v>
       </c>
@@ -11032,7 +11057,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
         <v>524</v>
       </c>
@@ -11087,7 +11112,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>554</v>
       </c>
@@ -11142,7 +11167,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>493</v>
       </c>
@@ -11197,7 +11222,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>573</v>
       </c>
@@ -11252,7 +11277,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>568</v>
       </c>
@@ -11307,7 +11332,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>551</v>
       </c>
@@ -11360,7 +11385,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
         <v>604</v>
       </c>
@@ -11413,7 +11438,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
         <v>517</v>
       </c>
@@ -11466,7 +11491,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
         <v>560</v>
       </c>
@@ -11519,7 +11544,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
         <v>542</v>
       </c>
@@ -11572,7 +11597,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
         <v>521</v>
       </c>
@@ -11625,7 +11650,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
         <v>534</v>
       </c>
@@ -11678,7 +11703,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
         <v>596</v>
       </c>
@@ -11731,7 +11756,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
         <v>553</v>
       </c>
@@ -11784,7 +11809,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
         <v>519</v>
       </c>
@@ -11837,7 +11862,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
         <v>577</v>
       </c>
@@ -11890,7 +11915,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
         <v>496</v>
       </c>
@@ -11943,7 +11968,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>628</v>
       </c>
@@ -11996,7 +12021,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
         <v>529</v>
       </c>
@@ -12049,7 +12074,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
         <v>613</v>
       </c>
@@ -12102,7 +12127,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
         <v>467</v>
       </c>
@@ -12155,7 +12180,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
         <v>515</v>
       </c>
@@ -12208,7 +12233,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>640</v>
       </c>
@@ -12261,7 +12286,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
         <v>622</v>
       </c>
@@ -12314,7 +12339,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
         <v>595</v>
       </c>
@@ -12367,7 +12392,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
         <v>385</v>
       </c>
@@ -12420,7 +12445,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
         <v>606</v>
       </c>
@@ -12473,7 +12498,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
         <v>623</v>
       </c>
@@ -12526,7 +12551,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
         <v>513</v>
       </c>
@@ -12579,7 +12604,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
         <v>558</v>
       </c>
@@ -12632,7 +12657,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
         <v>586</v>
       </c>
@@ -12685,7 +12710,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
         <v>540</v>
       </c>
@@ -12738,7 +12763,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
         <v>526</v>
       </c>
@@ -12791,7 +12816,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
         <v>544</v>
       </c>
@@ -12844,7 +12869,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
         <v>732</v>
       </c>
@@ -12891,7 +12916,7 @@
       <c r="T126" s="7"/>
       <c r="U126" s="7"/>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
         <v>661</v>
       </c>
@@ -12944,7 +12969,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="s">
         <v>679</v>
       </c>
@@ -12997,7 +13022,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
         <v>580</v>
       </c>
@@ -13050,7 +13075,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
         <v>736</v>
       </c>
@@ -13097,7 +13122,7 @@
       <c r="T130" s="7"/>
       <c r="U130" s="7"/>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
         <v>677</v>
       </c>
@@ -13150,7 +13175,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
         <v>670</v>
       </c>
@@ -13203,7 +13228,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
         <v>686</v>
       </c>
@@ -13256,7 +13281,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
         <v>666</v>
       </c>
@@ -13309,7 +13334,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
         <v>688</v>
       </c>
@@ -13360,7 +13385,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="s">
         <v>631</v>
       </c>
@@ -13413,7 +13438,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
         <v>682</v>
       </c>
@@ -13464,7 +13489,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="s">
         <v>693</v>
       </c>
@@ -13517,7 +13542,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
         <v>564</v>
       </c>
@@ -13568,7 +13593,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="s">
         <v>699</v>
       </c>
@@ -13621,7 +13646,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
         <v>713</v>
       </c>
@@ -13672,7 +13697,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="s">
         <v>715</v>
       </c>
@@ -13725,7 +13750,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A143" s="7" t="s">
         <v>673</v>
       </c>
@@ -13778,7 +13803,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="s">
         <v>680</v>
       </c>
@@ -13831,7 +13856,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="s">
         <v>739</v>
       </c>
@@ -13884,7 +13909,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="s">
         <v>704</v>
       </c>
@@ -13937,7 +13962,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
         <v>748</v>
       </c>
@@ -13988,7 +14013,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="s">
         <v>771</v>
       </c>
@@ -14041,7 +14066,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
         <v>810</v>
       </c>
@@ -14094,7 +14119,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
         <v>778</v>
       </c>
@@ -14147,7 +14172,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
         <v>741</v>
       </c>
@@ -14200,7 +14225,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="7" t="s">
         <v>650</v>
       </c>
@@ -14253,7 +14278,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
         <v>755</v>
       </c>
@@ -14306,7 +14331,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="7" t="s">
         <v>697</v>
       </c>
@@ -14359,7 +14384,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
         <v>809</v>
       </c>
@@ -14412,7 +14437,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="7" t="s">
         <v>760</v>
       </c>
@@ -14465,7 +14490,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="s">
         <v>814</v>
       </c>
@@ -14516,7 +14541,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
         <v>709</v>
       </c>
@@ -14569,7 +14594,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
         <v>806</v>
       </c>
@@ -14622,7 +14647,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="s">
         <v>793</v>
       </c>
@@ -14675,7 +14700,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
         <v>702</v>
       </c>
@@ -14728,7 +14753,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="7" t="s">
         <v>833</v>
       </c>
@@ -14781,7 +14806,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
         <v>743</v>
       </c>
@@ -14834,7 +14859,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" s="7" t="s">
         <v>769</v>
       </c>
@@ -14887,7 +14912,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
         <v>767</v>
       </c>
@@ -14938,7 +14963,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="s">
         <v>857</v>
       </c>
@@ -14991,7 +15016,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="s">
         <v>719</v>
       </c>
@@ -15044,7 +15069,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="s">
         <v>827</v>
       </c>
@@ -15095,7 +15120,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="s">
         <v>817</v>
       </c>
@@ -15148,7 +15173,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="s">
         <v>786</v>
       </c>
@@ -15201,7 +15226,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
         <v>804</v>
       </c>
@@ -15254,7 +15279,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="s">
         <v>828</v>
       </c>
@@ -15307,7 +15332,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="s">
         <v>780</v>
       </c>
@@ -15360,7 +15385,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="s">
         <v>885</v>
       </c>
@@ -15413,7 +15438,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="s">
         <v>883</v>
       </c>
@@ -15466,7 +15491,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="s">
         <v>830</v>
       </c>
@@ -15519,7 +15544,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="s">
         <v>868</v>
       </c>
@@ -15572,7 +15597,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A178" s="7" t="s">
         <v>837</v>
       </c>
@@ -15625,7 +15650,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="s">
         <v>729</v>
       </c>
@@ -15678,7 +15703,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="s">
         <v>1020</v>
       </c>
@@ -15731,7 +15756,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
         <v>846</v>
       </c>
@@ -15784,7 +15809,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A182" s="7" t="s">
         <v>707</v>
       </c>
@@ -15837,7 +15862,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
         <v>906</v>
       </c>
@@ -15890,7 +15915,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="s">
         <v>917</v>
       </c>
@@ -15943,7 +15968,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="s">
         <v>800</v>
       </c>
@@ -15996,7 +16021,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="s">
         <v>822</v>
       </c>
@@ -16049,7 +16074,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
         <v>889</v>
       </c>
@@ -16102,7 +16127,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A188" s="7" t="s">
         <v>865</v>
       </c>
@@ -16155,7 +16180,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
         <v>896</v>
       </c>
@@ -16208,7 +16233,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A190" s="7" t="s">
         <v>952</v>
       </c>
@@ -16261,7 +16286,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
         <v>922</v>
       </c>
@@ -16314,7 +16339,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A192" s="7" t="s">
         <v>875</v>
       </c>
@@ -16367,7 +16392,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
         <v>928</v>
       </c>
@@ -16420,7 +16445,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
         <v>844</v>
       </c>
@@ -16473,7 +16498,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="s">
         <v>911</v>
       </c>
@@ -16526,7 +16551,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A196" s="7" t="s">
         <v>940</v>
       </c>
@@ -16579,7 +16604,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>892</v>
       </c>
@@ -16632,7 +16657,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>974</v>
       </c>
@@ -16685,7 +16710,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>850</v>
       </c>
@@ -16738,7 +16763,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>915</v>
       </c>
@@ -16791,7 +16816,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>863</v>
       </c>
@@ -16844,7 +16869,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>872</v>
       </c>
@@ -16897,7 +16922,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>966</v>
       </c>
@@ -16950,7 +16975,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A204" s="7" t="s">
         <v>894</v>
       </c>
@@ -17003,7 +17028,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
         <v>1009</v>
       </c>
@@ -17056,7 +17081,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>910</v>
       </c>
@@ -17109,7 +17134,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
         <v>936</v>
       </c>
@@ -17162,7 +17187,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="s">
         <v>839</v>
       </c>
@@ -17215,7 +17240,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="s">
         <v>942</v>
       </c>
@@ -17268,7 +17293,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A210" s="7" t="s">
         <v>897</v>
       </c>
@@ -17321,7 +17346,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A211" s="7" t="s">
         <v>992</v>
       </c>
@@ -17374,7 +17399,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A212" s="7" t="s">
         <v>1004</v>
       </c>
@@ -17427,7 +17452,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A213" s="7" t="s">
         <v>938</v>
       </c>
@@ -17480,7 +17505,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A214" s="7" t="s">
         <v>1048</v>
       </c>
@@ -17533,7 +17558,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
         <v>1065</v>
       </c>
@@ -17586,7 +17611,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A216" s="7" t="s">
         <v>1023</v>
       </c>
@@ -17639,7 +17664,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A217" s="7" t="s">
         <v>790</v>
       </c>
@@ -17692,7 +17717,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A218" s="7" t="s">
         <v>1077</v>
       </c>
@@ -17745,7 +17770,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A219" s="7" t="s">
         <v>1090</v>
       </c>
@@ -17798,7 +17823,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A220" s="7" t="s">
         <v>968</v>
       </c>
@@ -17851,7 +17876,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A221" s="7" t="s">
         <v>999</v>
       </c>
@@ -17904,7 +17929,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A222" s="7" t="s">
         <v>1099</v>
       </c>
@@ -17957,7 +17982,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A223" s="7" t="s">
         <v>1014</v>
       </c>
@@ -18010,7 +18035,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A224" s="7" t="s">
         <v>1027</v>
       </c>
@@ -18063,7 +18088,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A225" s="7" t="s">
         <v>988</v>
       </c>
@@ -18116,7 +18141,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A226" s="7" t="s">
         <v>1110</v>
       </c>
@@ -18169,7 +18194,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A227" s="7" t="s">
         <v>1157</v>
       </c>
@@ -18222,7 +18247,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
         <v>1187</v>
       </c>
@@ -18275,7 +18300,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>1120</v>
       </c>
@@ -18328,7 +18353,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>1097</v>
       </c>
@@ -18381,7 +18406,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>1190</v>
       </c>
@@ -18434,7 +18459,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
         <v>1071</v>
       </c>
@@ -18487,7 +18512,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>958</v>
       </c>
@@ -18540,7 +18565,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>1081</v>
       </c>
@@ -18593,7 +18618,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>1201</v>
       </c>
@@ -18646,7 +18671,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
         <v>1010</v>
       </c>
@@ -18699,7 +18724,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>1100</v>
       </c>
@@ -18752,7 +18777,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>1028</v>
       </c>
@@ -18805,7 +18830,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>979</v>
       </c>
@@ -18858,7 +18883,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
         <v>1239</v>
       </c>
@@ -18911,7 +18936,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
         <v>1083</v>
       </c>
@@ -18964,7 +18989,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A242" s="7" t="s">
         <v>1220</v>
       </c>
@@ -19017,7 +19042,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A243" s="7" t="s">
         <v>1018</v>
       </c>
@@ -19070,7 +19095,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A244" s="7" t="s">
         <v>984</v>
       </c>
@@ -19123,7 +19148,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A245" s="7" t="s">
         <v>1204</v>
       </c>
@@ -19176,7 +19201,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A246" s="7" t="s">
         <v>1088</v>
       </c>
@@ -19229,7 +19254,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A247" s="7" t="s">
         <v>1209</v>
       </c>
@@ -19282,7 +19307,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A248" s="13" t="s">
         <v>1159</v>
       </c>
@@ -19335,7 +19360,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>1256</v>
       </c>
@@ -19388,7 +19413,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A250" s="7" t="s">
         <v>1079</v>
       </c>
@@ -19441,7 +19466,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A251" s="7" t="s">
         <v>971</v>
       </c>
@@ -19494,12 +19519,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A252" s="7" t="s">
         <v>1303</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>668</v>
@@ -19547,7 +19572,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A253" s="7" t="s">
         <v>1136</v>
       </c>
@@ -19600,7 +19625,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A254" s="7" t="s">
         <v>1307</v>
       </c>
@@ -19653,12 +19678,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A255" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B255" s="7" t="s">
         <v>1326</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>1327</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>813</v>
@@ -19693,7 +19718,7 @@
       </c>
       <c r="N255" s="11"/>
       <c r="O255" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="P255" s="7"/>
       <c r="Q255" s="24"/>
@@ -19706,7 +19731,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A256" s="7" t="s">
         <v>1061</v>
       </c>
@@ -19746,7 +19771,7 @@
       </c>
       <c r="N256" s="11"/>
       <c r="O256" s="19" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="P256" s="7"/>
       <c r="Q256" s="24"/>
@@ -19759,7 +19784,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A257" s="7" t="s">
         <v>1293</v>
       </c>
@@ -19799,7 +19824,7 @@
       </c>
       <c r="N257" s="11"/>
       <c r="O257" s="19" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="P257" s="7"/>
       <c r="Q257" s="24"/>
@@ -19812,7 +19837,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A258" s="7" t="s">
         <v>1273</v>
       </c>
@@ -19852,7 +19877,7 @@
       </c>
       <c r="N258" s="11"/>
       <c r="O258" s="19" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="P258" s="7"/>
       <c r="Q258" s="24"/>
@@ -19865,12 +19890,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A259" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B259" s="7" t="s">
         <v>1336</v>
-      </c>
-      <c r="B259" s="7" t="s">
-        <v>1337</v>
       </c>
       <c r="C259" s="7" t="s">
         <v>1290</v>
@@ -19905,7 +19930,7 @@
       </c>
       <c r="N259" s="11"/>
       <c r="O259" s="19" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="P259" s="7"/>
       <c r="Q259" s="24"/>
@@ -19918,18 +19943,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A260" s="7" t="s">
         <v>1312</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>1313</v>
+        <v>161</v>
       </c>
       <c r="E260" s="18">
         <v>2024</v>
@@ -19941,7 +19966,7 @@
         <v>69</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I260" s="18" t="s">
         <v>14</v>
@@ -19958,7 +19983,7 @@
       </c>
       <c r="N260" s="11"/>
       <c r="O260" s="19" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="P260" s="7"/>
       <c r="Q260" s="24"/>
@@ -19971,12 +19996,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A261" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C261" s="7" t="s">
         <v>267</v>
@@ -20011,7 +20036,7 @@
       </c>
       <c r="N261" s="11"/>
       <c r="O261" s="19" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="P261" s="7"/>
       <c r="Q261" s="24"/>
@@ -20024,7 +20049,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A262" s="13" t="s">
         <v>1254</v>
       </c>
@@ -20064,7 +20089,7 @@
       </c>
       <c r="N262" s="11"/>
       <c r="O262" s="19" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="P262" s="7"/>
       <c r="Q262" s="24"/>
@@ -20077,18 +20102,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A263" s="7" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>1213</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="E263" s="18">
         <v>2025</v>
@@ -20100,7 +20125,7 @@
         <v>14</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="I263" s="18" t="s">
         <v>14</v>
@@ -20117,7 +20142,7 @@
       </c>
       <c r="N263" s="11"/>
       <c r="O263" s="19" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="P263" s="7"/>
       <c r="Q263" s="24"/>
@@ -20128,12 +20153,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A264" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>1287</v>
@@ -20168,7 +20193,7 @@
       </c>
       <c r="N264" s="11"/>
       <c r="O264" s="19" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="P264" s="7"/>
       <c r="Q264" s="24"/>
@@ -20181,7 +20206,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A265" s="7" t="s">
         <v>1291</v>
       </c>
@@ -20204,7 +20229,7 @@
         <v>101</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="I265" s="18" t="s">
         <v>14</v>
@@ -20221,7 +20246,7 @@
       </c>
       <c r="N265" s="11"/>
       <c r="O265" s="19" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="P265" s="7"/>
       <c r="Q265" s="24"/>
@@ -20232,18 +20257,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>267</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="E266" s="18">
         <v>2025</v>
@@ -20272,7 +20297,7 @@
       </c>
       <c r="N266" s="11"/>
       <c r="O266" s="19" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="P266" s="7"/>
       <c r="Q266" s="24"/>
@@ -20283,12 +20308,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A267" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B267" s="7" t="s">
         <v>1319</v>
-      </c>
-      <c r="B267" s="7" t="s">
-        <v>1320</v>
       </c>
       <c r="C267" s="7" t="s">
         <v>287</v>
@@ -20323,7 +20348,7 @@
       </c>
       <c r="N267" s="11"/>
       <c r="O267" s="19" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="P267" s="7"/>
       <c r="Q267" s="24"/>
@@ -20334,9 +20359,9 @@
         <v>603</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="B268" s="7" t="s">
         <v>1260</v>
@@ -20374,7 +20399,7 @@
       </c>
       <c r="N268" s="11"/>
       <c r="O268" s="19" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="P268" s="7"/>
       <c r="Q268" s="24"/>
@@ -20385,18 +20410,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A269" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B269" s="7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D269" s="7" t="s">
         <v>1478</v>
-      </c>
-      <c r="B269" s="7" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C269" s="7" t="s">
-        <v>1480</v>
-      </c>
-      <c r="D269" s="7" t="s">
-        <v>1481</v>
       </c>
       <c r="E269" s="18">
         <v>2025</v>
@@ -20411,10 +20436,10 @@
         <v>14</v>
       </c>
       <c r="I269" s="18" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="J269" s="18" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="K269" s="42">
         <v>45706</v>
@@ -20425,7 +20450,7 @@
       </c>
       <c r="N269" s="11"/>
       <c r="O269" s="19" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="P269" s="7"/>
       <c r="Q269" s="24"/>
@@ -20436,12 +20461,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A270" s="7" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B270" s="7" t="s">
         <v>1491</v>
-      </c>
-      <c r="B270" s="7" t="s">
-        <v>1494</v>
       </c>
       <c r="C270" s="7" t="s">
         <v>723</v>
@@ -20459,7 +20484,7 @@
         <v>548</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="I270" s="18" t="s">
         <v>14</v>
@@ -20476,7 +20501,7 @@
       </c>
       <c r="N270" s="11"/>
       <c r="O270" s="19" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="P270" s="7"/>
       <c r="Q270" s="24"/>
@@ -20487,12 +20512,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A271" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>373</v>
@@ -20527,7 +20552,7 @@
       </c>
       <c r="N271" s="11"/>
       <c r="O271" s="19" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="P271" s="7"/>
       <c r="Q271" s="24"/>
@@ -20538,18 +20563,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A272" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B272" s="7" t="s">
         <v>1343</v>
-      </c>
-      <c r="B272" s="7" t="s">
-        <v>1344</v>
       </c>
       <c r="C272" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>1313</v>
+        <v>161</v>
       </c>
       <c r="E272" s="18">
         <v>2025</v>
@@ -20561,7 +20586,7 @@
         <v>548</v>
       </c>
       <c r="H272" s="18" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="I272" s="18" t="s">
         <v>14</v>
@@ -20578,7 +20603,7 @@
       </c>
       <c r="N272" s="11"/>
       <c r="O272" s="19" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="P272" s="7"/>
       <c r="Q272" s="24"/>
@@ -20589,18 +20614,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A273" s="7" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="E273" s="18">
         <v>2025</v>
@@ -20629,7 +20654,7 @@
       </c>
       <c r="N273" s="11"/>
       <c r="O273" s="19" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="P273" s="7"/>
       <c r="Q273" s="24"/>
@@ -20640,12 +20665,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A274" s="7" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="C274" s="7" t="s">
         <v>723</v>
@@ -20663,7 +20688,7 @@
         <v>111</v>
       </c>
       <c r="H274" s="18" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="I274" s="18" t="s">
         <v>14</v>
@@ -20680,7 +20705,7 @@
       </c>
       <c r="N274" s="11"/>
       <c r="O274" s="19" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="P274" s="7"/>
       <c r="Q274" s="24"/>
@@ -20691,12 +20716,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A275" s="7" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="C275" s="7" t="s">
         <v>89</v>
@@ -20731,7 +20756,7 @@
       </c>
       <c r="N275" s="11"/>
       <c r="O275" s="19" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="P275" s="7"/>
       <c r="Q275" s="24"/>
@@ -20742,12 +20767,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A276" s="7" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="B276" s="7" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="C276" s="7" t="s">
         <v>267</v>
@@ -20782,7 +20807,7 @@
       </c>
       <c r="N276" s="11"/>
       <c r="O276" s="19" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="P276" s="7"/>
       <c r="Q276" s="24"/>
@@ -20793,12 +20818,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A277" s="7" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B277" s="7" t="s">
         <v>1451</v>
-      </c>
-      <c r="B277" s="7" t="s">
-        <v>1452</v>
       </c>
       <c r="C277" s="7" t="s">
         <v>89</v>
@@ -20833,7 +20858,7 @@
       </c>
       <c r="N277" s="11"/>
       <c r="O277" s="19" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="P277" s="7"/>
       <c r="Q277" s="24"/>
@@ -20844,18 +20869,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A278" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="C278" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>1313</v>
+        <v>161</v>
       </c>
       <c r="E278" s="18">
         <v>2025</v>
@@ -20867,7 +20892,7 @@
         <v>153</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="I278" s="18" t="s">
         <v>14</v>
@@ -20884,7 +20909,7 @@
       </c>
       <c r="N278" s="11"/>
       <c r="O278" s="19" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="P278" s="7"/>
       <c r="Q278" s="24"/>
@@ -20895,12 +20920,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A279" s="7" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="C279" s="7" t="s">
         <v>267</v>
@@ -20935,7 +20960,7 @@
       </c>
       <c r="N279" s="11"/>
       <c r="O279" s="19" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="P279" s="7"/>
       <c r="Q279" s="24"/>
@@ -20946,7 +20971,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A280" s="7" t="s">
         <v>1093</v>
       </c>
@@ -20995,12 +21020,12 @@
       <c r="T280" s="7"/>
       <c r="U280" s="7"/>
     </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A281" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B281" s="7" t="s">
         <v>1447</v>
-      </c>
-      <c r="B281" s="7" t="s">
-        <v>1448</v>
       </c>
       <c r="C281" s="7" t="s">
         <v>668</v>
@@ -21035,7 +21060,7 @@
       </c>
       <c r="N281" s="11"/>
       <c r="O281" s="19" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="P281" s="7"/>
       <c r="Q281" s="24"/>
@@ -21046,12 +21071,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A282" s="7" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="B282" s="7" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="C282" s="7" t="s">
         <v>133</v>
@@ -21086,7 +21111,7 @@
       </c>
       <c r="N282" s="11"/>
       <c r="O282" s="19" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="P282" s="7"/>
       <c r="Q282" s="24"/>
@@ -21097,12 +21122,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A283" s="7" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B283" s="7" t="s">
         <v>1449</v>
-      </c>
-      <c r="B283" s="7" t="s">
-        <v>1450</v>
       </c>
       <c r="C283" s="7" t="s">
         <v>267</v>
@@ -21137,7 +21162,7 @@
       </c>
       <c r="N283" s="11"/>
       <c r="O283" s="19" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="P283" s="7"/>
       <c r="Q283" s="24"/>
@@ -21148,12 +21173,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A284" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B284" s="7" t="s">
         <v>1467</v>
-      </c>
-      <c r="B284" s="7" t="s">
-        <v>1468</v>
       </c>
       <c r="C284" s="7" t="s">
         <v>287</v>
@@ -21188,7 +21213,7 @@
       </c>
       <c r="N284" s="11"/>
       <c r="O284" s="19" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="P284" s="7"/>
       <c r="Q284" s="24"/>
@@ -21199,18 +21224,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A285" s="7" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B285" s="7" t="s">
         <v>1462</v>
       </c>
-      <c r="B285" s="7" t="s">
-        <v>1463</v>
-      </c>
       <c r="C285" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="E285" s="18">
         <v>2025</v>
@@ -21239,7 +21264,7 @@
       </c>
       <c r="N285" s="11"/>
       <c r="O285" s="19" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="P285" s="7"/>
       <c r="Q285" s="24"/>
@@ -21250,12 +21275,12 @@
         <v>603</v>
       </c>
     </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A286" s="7" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="B286" s="7" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="C286" s="7" t="s">
         <v>267</v>
@@ -21290,7 +21315,7 @@
       </c>
       <c r="N286" s="11"/>
       <c r="O286" s="19" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="P286" s="7"/>
       <c r="Q286" s="24"/>
@@ -21301,18 +21326,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A287" s="7" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="B287" s="7" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="E287" s="18">
         <v>2025</v>
@@ -21341,7 +21366,7 @@
       </c>
       <c r="N287" s="11"/>
       <c r="O287" s="19" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="P287" s="7"/>
       <c r="Q287" s="24"/>
@@ -21350,18 +21375,18 @@
       <c r="T287" s="7"/>
       <c r="U287" s="7"/>
     </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A288" s="7" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="B288" s="7" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="E288" s="18">
         <v>2026</v>
@@ -21390,7 +21415,7 @@
       </c>
       <c r="N288" s="11"/>
       <c r="O288" s="19" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="P288" s="7"/>
       <c r="Q288" s="24"/>
@@ -21399,12 +21424,12 @@
       <c r="T288" s="7"/>
       <c r="U288" s="7"/>
     </row>
-    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A289" s="7" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="B289" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C289" s="7" t="s">
         <v>252</v>
@@ -21439,7 +21464,7 @@
       </c>
       <c r="N289" s="11"/>
       <c r="O289" s="19" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="P289" s="7"/>
       <c r="Q289" s="24"/>
@@ -21448,18 +21473,18 @@
       <c r="T289" s="7"/>
       <c r="U289" s="7"/>
     </row>
-    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A290" s="7" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="B290" s="7" t="s">
-        <v>1582</v>
+        <v>1595</v>
       </c>
       <c r="C290" s="7" t="s">
         <v>415</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="E290" s="18">
         <v>2026</v>
@@ -21471,7 +21496,7 @@
         <v>14</v>
       </c>
       <c r="H290" s="18" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="I290" s="18" t="s">
         <v>14</v>
@@ -21488,7 +21513,7 @@
       </c>
       <c r="N290" s="11"/>
       <c r="O290" s="19" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="P290" s="7"/>
       <c r="Q290" s="24"/>
@@ -21497,12 +21522,12 @@
       <c r="T290" s="7"/>
       <c r="U290" s="7"/>
     </row>
-    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A291" s="7" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="B291" s="7" t="s">
-        <v>1511</v>
+        <v>1598</v>
       </c>
       <c r="C291" s="7" t="s">
         <v>108</v>
@@ -21537,7 +21562,7 @@
       </c>
       <c r="N291" s="11"/>
       <c r="O291" s="19" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="P291" s="7"/>
       <c r="Q291" s="24"/>
@@ -21546,12 +21571,12 @@
       <c r="T291" s="7"/>
       <c r="U291" s="7"/>
     </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A292" s="7" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
       <c r="B292" s="7" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="C292" s="7" t="s">
         <v>89</v>
@@ -21586,7 +21611,7 @@
       </c>
       <c r="N292" s="11"/>
       <c r="O292" s="19" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="P292" s="7"/>
       <c r="Q292" s="24"/>
@@ -21595,12 +21620,12 @@
       <c r="T292" s="7"/>
       <c r="U292" s="7"/>
     </row>
-    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A293" s="7" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="C293" s="7" t="s">
         <v>108</v>
@@ -21635,7 +21660,7 @@
       </c>
       <c r="N293" s="11"/>
       <c r="O293" s="19" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="P293" s="7"/>
       <c r="Q293" s="24"/>
@@ -21644,18 +21669,18 @@
       <c r="T293" s="7"/>
       <c r="U293" s="7"/>
     </row>
-    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A294" s="7" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="B294" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="E294" s="18">
         <v>2026</v>
@@ -21684,7 +21709,7 @@
       </c>
       <c r="N294" s="11"/>
       <c r="O294" s="19" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="P294" s="7"/>
       <c r="Q294" s="24"/>
@@ -21693,150 +21718,344 @@
       <c r="T294" s="7"/>
       <c r="U294" s="7"/>
     </row>
-    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A295" s="13" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B295" s="13" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C295" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D295" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E295" s="14">
+    <row r="295" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A295" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="E295" s="18">
         <v>2026</v>
       </c>
-      <c r="F295" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G295" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H295" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I295" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J295" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K295" s="31">
-        <v>46389</v>
-      </c>
-      <c r="L295" s="31"/>
-      <c r="M295" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N295" s="45"/>
-      <c r="O295" s="44" t="s">
-        <v>1576</v>
-      </c>
-      <c r="P295" s="27"/>
+      <c r="F295" s="18">
+        <v>22</v>
+      </c>
+      <c r="G295" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H295" s="18">
+        <v>101417</v>
+      </c>
+      <c r="I295" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J295" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K295" s="42">
+        <v>46133</v>
+      </c>
+      <c r="L295" s="42"/>
+      <c r="M295" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N295" s="11"/>
+      <c r="O295" s="19" t="s">
+        <v>1594</v>
+      </c>
+      <c r="P295" s="7"/>
       <c r="Q295" s="24"/>
       <c r="R295" s="25"/>
       <c r="S295" s="7"/>
       <c r="T295" s="7"/>
       <c r="U295" s="7"/>
     </row>
-    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A296" s="13" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B296" s="13" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C296" s="13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D296" s="13" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E296" s="14">
+    <row r="296" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A296" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E296" s="18">
         <v>2026</v>
       </c>
-      <c r="F296" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G296" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H296" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I296" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J296" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K296" s="31">
-        <v>46390</v>
-      </c>
-      <c r="L296" s="31"/>
-      <c r="M296" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N296" s="45"/>
-      <c r="O296" s="44" t="s">
-        <v>1563</v>
-      </c>
-      <c r="P296" s="27"/>
+      <c r="F296" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G296" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H296" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I296" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J296" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K296" s="42">
+        <v>46155</v>
+      </c>
+      <c r="L296" s="42"/>
+      <c r="M296" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N296" s="11"/>
+      <c r="O296" s="19" t="s">
+        <v>1587</v>
+      </c>
+      <c r="P296" s="7"/>
       <c r="Q296" s="24"/>
       <c r="R296" s="25"/>
       <c r="S296" s="7"/>
       <c r="T296" s="7"/>
       <c r="U296" s="7"/>
     </row>
-    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A297" s="13" t="s">
-        <v>1474</v>
-      </c>
-      <c r="B297" s="13" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C297" s="13" t="s">
-        <v>1476</v>
-      </c>
-      <c r="D297" s="13" t="s">
-        <v>1477</v>
-      </c>
-      <c r="E297" s="14">
+    <row r="297" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A297" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="E297" s="18">
         <v>2026</v>
       </c>
-      <c r="F297" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G297" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H297" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I297" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J297" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K297" s="31">
-        <v>46391</v>
-      </c>
-      <c r="L297" s="31"/>
-      <c r="M297" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="N297" s="45"/>
-      <c r="O297" s="44"/>
-      <c r="P297" s="27"/>
+      <c r="F297" s="18">
+        <v>407</v>
+      </c>
+      <c r="G297" s="19" t="s">
+        <v>1591</v>
+      </c>
+      <c r="H297" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I297" s="18">
+        <v>1915</v>
+      </c>
+      <c r="J297" s="18">
+        <v>1916</v>
+      </c>
+      <c r="K297" s="42">
+        <v>46158</v>
+      </c>
+      <c r="L297" s="42"/>
+      <c r="M297" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="N297" s="11"/>
+      <c r="O297" s="19" t="s">
+        <v>1590</v>
+      </c>
+      <c r="P297" s="7"/>
       <c r="Q297" s="24"/>
       <c r="R297" s="25"/>
       <c r="S297" s="7"/>
       <c r="T297" s="7"/>
       <c r="U297" s="7"/>
+    </row>
+    <row r="298" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A298" s="13" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C298" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D298" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E298" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F298" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G298" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H298" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I298" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J298" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K298" s="31">
+        <v>46389</v>
+      </c>
+      <c r="L298" s="31"/>
+      <c r="M298" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N298" s="45"/>
+      <c r="O298" s="44" t="s">
+        <v>1569</v>
+      </c>
+      <c r="P298" s="27"/>
+      <c r="Q298" s="24"/>
+      <c r="R298" s="25"/>
+      <c r="S298" s="7"/>
+      <c r="T298" s="7"/>
+      <c r="U298" s="7"/>
+    </row>
+    <row r="299" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A299" s="13" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B299" s="13" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C299" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D299" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E299" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F299" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G299" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H299" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I299" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J299" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K299" s="31">
+        <v>46390</v>
+      </c>
+      <c r="L299" s="31"/>
+      <c r="M299" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N299" s="45"/>
+      <c r="O299" s="44" t="s">
+        <v>1556</v>
+      </c>
+      <c r="P299" s="27"/>
+      <c r="Q299" s="24"/>
+      <c r="R299" s="25"/>
+      <c r="S299" s="7"/>
+      <c r="T299" s="7"/>
+      <c r="U299" s="7"/>
+    </row>
+    <row r="300" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A300" s="13" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C300" s="13" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D300" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E300" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F300" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G300" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H300" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I300" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J300" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K300" s="31">
+        <v>46391</v>
+      </c>
+      <c r="L300" s="31"/>
+      <c r="M300" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N300" s="45"/>
+      <c r="O300" s="44"/>
+      <c r="P300" s="27"/>
+      <c r="Q300" s="24"/>
+      <c r="R300" s="25"/>
+      <c r="S300" s="7"/>
+      <c r="T300" s="7"/>
+      <c r="U300" s="7"/>
+    </row>
+    <row r="301" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A301" s="13" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B301" s="13" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C301" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D301" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E301" s="14">
+        <v>2026</v>
+      </c>
+      <c r="F301" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G301" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H301" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I301" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J301" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K301" s="31">
+        <v>46392</v>
+      </c>
+      <c r="L301" s="31"/>
+      <c r="M301" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="N301" s="45"/>
+      <c r="O301" s="44"/>
+      <c r="P301" s="27"/>
+      <c r="Q301" s="24"/>
+      <c r="R301" s="25"/>
+      <c r="S301" s="7"/>
+      <c r="T301" s="7"/>
+      <c r="U301" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="T1:U112 T114:U231 V246:V247 T232:V240 V241:V242 T241:T242 T243:V245 T246:U246 T248:V1048576">
@@ -21882,17 +22101,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" style="2"/>
-    <col min="8" max="8" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -21924,7 +22143,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>95</v>
       </c>
@@ -21956,7 +22175,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>276</v>
       </c>
@@ -21986,7 +22205,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>277</v>
       </c>
@@ -22016,7 +22235,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>486</v>
       </c>
@@ -22046,7 +22265,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>489</v>
       </c>
@@ -22076,7 +22295,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>491</v>
       </c>
@@ -22106,7 +22325,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>724</v>
       </c>
@@ -22136,7 +22355,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>904</v>
       </c>
@@ -22166,7 +22385,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>899</v>
       </c>
@@ -22196,7 +22415,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>945</v>
       </c>
@@ -22226,7 +22445,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>1134</v>
       </c>
@@ -22266,17 +22485,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="15" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="40.6640625" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -22300,17 +22519,17 @@
       </c>
       <c r="I1" s="55" t="str">
         <f ca="1">ROUND(J1/30,0)&amp;" md"</f>
-        <v>7 md</v>
+        <v>8 md</v>
       </c>
       <c r="J1" s="55">
         <f ca="1">AVERAGE(G:G)</f>
-        <v>212.05882352941177</v>
+        <v>230.8</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>1164</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>1305</v>
       </c>
@@ -22318,48 +22537,48 @@
         <v>1306</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>1323</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>1324</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="10">
         <v>45488</v>
       </c>
       <c r="G2" s="12">
-        <f ca="1">TODAY()-F2</f>
-        <v>631</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="G2:G16" ca="1" si="0">TODAY()-F2</f>
+        <v>671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1331</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1332</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1330</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1333</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="10">
         <v>45562</v>
       </c>
       <c r="G3" s="12">
-        <f ca="1">TODAY()-F3</f>
-        <v>557</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>723</v>
@@ -22372,16 +22591,16 @@
         <v>45705</v>
       </c>
       <c r="G4" s="12">
-        <f ca="1">TODAY()-F4</f>
-        <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>89</v>
@@ -22394,99 +22613,99 @@
         <v>45764</v>
       </c>
       <c r="G5" s="12">
-        <f ca="1">TODAY()-F5</f>
-        <v>355</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1513</v>
+        <v>1526</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1515</v>
+        <v>1532</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1111</v>
+        <v>1024</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1112</v>
+        <v>1026</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="10">
-        <v>45790</v>
+        <v>45860</v>
       </c>
       <c r="G6" s="12">
-        <f ca="1">TODAY()-F6</f>
-        <v>329</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1528</v>
+        <v>1549</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1529</v>
+        <v>1553</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1530</v>
+        <v>1460</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1531</v>
+        <v>1460</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="10">
-        <v>45854</v>
+        <v>45944</v>
       </c>
       <c r="G7" s="12">
-        <f ca="1">TODAY()-F7</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>1532</v>
+        <v>1554</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1538</v>
+        <v>1555</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1024</v>
+        <v>120</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1026</v>
+        <v>121</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="10">
-        <v>45860</v>
+        <v>46023</v>
       </c>
       <c r="G8" s="12">
-        <f ca="1">TODAY()-F8</f>
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>1560</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1461</v>
+        <v>120</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1461</v>
+        <v>121</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="10">
-        <v>45944</v>
+        <v>46029</v>
       </c>
       <c r="G9" s="12">
-        <f ca="1">TODAY()-F9</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>1558</v>
       </c>
@@ -22494,26 +22713,26 @@
         <v>1559</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="10">
-        <v>46008</v>
+        <v>46038</v>
       </c>
       <c r="G10" s="12">
-        <f ca="1">TODAY()-F10</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1561</v>
+        <v>1579</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1562</v>
+        <v>1580</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>120</v>
@@ -22522,20 +22741,20 @@
         <v>121</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="F11" s="10">
-        <v>46023</v>
+      <c r="F11" s="42">
+        <v>46044</v>
       </c>
       <c r="G11" s="12">
-        <f ca="1">TODAY()-F11</f>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>120</v>
@@ -22544,146 +22763,102 @@
         <v>121</v>
       </c>
       <c r="E12" s="7"/>
-      <c r="F12" s="10">
-        <v>46029</v>
+      <c r="F12" s="42">
+        <v>46047</v>
       </c>
       <c r="G12" s="12">
-        <f ca="1">TODAY()-F12</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1566</v>
+        <v>1572</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10">
-        <v>46038</v>
+        <v>144</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F13" s="42">
+        <v>46072</v>
       </c>
       <c r="G13" s="12">
-        <f ca="1">TODAY()-F13</f>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="42">
-        <v>46044</v>
+        <v>46104</v>
       </c>
       <c r="G14" s="12">
-        <f ca="1">TODAY()-F14</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1589</v>
+        <v>1585</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="42">
-        <v>46047</v>
+        <v>46086</v>
       </c>
       <c r="G15" s="12">
-        <f ca="1">TODAY()-F15</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>1578</v>
+        <v>1600</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1579</v>
+        <v>1601</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>144</v>
+        <v>575</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>1580</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="E16" s="7"/>
       <c r="F16" s="42">
-        <v>46072</v>
+        <v>46157</v>
       </c>
       <c r="G16" s="12">
-        <f ca="1">TODAY()-F16</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>1590</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>1591</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="42">
-        <v>46104</v>
-      </c>
-      <c r="G17" s="12">
-        <f ca="1">TODAY()-F17</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="42">
-        <v>46086</v>
-      </c>
-      <c r="G18" s="12">
-        <f ca="1">TODAY()-F18</f>
-        <v>33</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -22698,16 +22873,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -22727,7 +22902,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>168</v>
       </c>
@@ -22745,10 +22920,10 @@
       </c>
       <c r="F2" s="40">
         <f t="shared" ref="F2:F4" ca="1" si="0">(TODAY()-E2)/365</f>
-        <v>10.441095890410958</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10.550684931506849</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>169</v>
       </c>
@@ -22766,10 +22941,10 @@
       </c>
       <c r="F3" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>10.441095890410958</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10.550684931506849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>256</v>
       </c>
@@ -22787,10 +22962,10 @@
       </c>
       <c r="F4" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>9.8191780821917813</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9.9287671232876704</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>346</v>
       </c>
@@ -22808,10 +22983,10 @@
       </c>
       <c r="F5" s="40">
         <f ca="1">(TODAY()-E5)/365</f>
-        <v>8.1890410958904116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8.2986301369863007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>1136</v>
       </c>
@@ -22842,16 +23017,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:N74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="81.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="15" customWidth="1"/>
-    <col min="3" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="15"/>
-    <col min="6" max="10" width="9.140625" style="48"/>
+    <col min="1" max="1" width="81.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="15" customWidth="1"/>
+    <col min="3" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="15"/>
+    <col min="6" max="10" width="9.109375" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="F1" s="50">
         <f>COUNTA(F3:F990)</f>
         <v>9</v>
@@ -22877,12 +23052,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
         <v>1045</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C2" s="52" t="s">
         <v>175</v>
@@ -22912,7 +23087,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1127</v>
       </c>
@@ -22935,7 +23110,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1126</v>
       </c>
@@ -22958,7 +23133,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1125</v>
       </c>
@@ -22981,7 +23156,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1124</v>
       </c>
@@ -23001,7 +23176,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1123</v>
       </c>
@@ -23021,7 +23196,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1068</v>
       </c>
@@ -23041,7 +23216,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1102</v>
       </c>
@@ -23061,7 +23236,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1116</v>
       </c>
@@ -23081,7 +23256,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1122</v>
       </c>
@@ -23101,7 +23276,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1130</v>
       </c>
@@ -23121,7 +23296,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1143</v>
       </c>
@@ -23141,7 +23316,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1146</v>
       </c>
@@ -23161,7 +23336,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1149</v>
       </c>
@@ -23179,7 +23354,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1151</v>
       </c>
@@ -23196,7 +23371,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1153</v>
       </c>
@@ -23216,7 +23391,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1161</v>
       </c>
@@ -23234,7 +23409,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1165</v>
       </c>
@@ -23254,7 +23429,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1171</v>
       </c>
@@ -23274,7 +23449,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1175</v>
       </c>
@@ -23294,7 +23469,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1179</v>
       </c>
@@ -23314,7 +23489,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1184</v>
       </c>
@@ -23334,7 +23509,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1195</v>
       </c>
@@ -23354,7 +23529,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1224</v>
       </c>
@@ -23374,7 +23549,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1227</v>
       </c>
@@ -23394,7 +23569,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1236</v>
       </c>
@@ -23414,7 +23589,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1243</v>
       </c>
@@ -23434,7 +23609,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1246</v>
       </c>
@@ -23454,7 +23629,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1105</v>
       </c>
@@ -23474,7 +23649,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1217</v>
       </c>
@@ -23494,7 +23669,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1230</v>
       </c>
@@ -23514,7 +23689,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1233</v>
       </c>
@@ -23534,7 +23709,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1266</v>
       </c>
@@ -23554,7 +23729,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1269</v>
       </c>
@@ -23574,7 +23749,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1281</v>
       </c>
@@ -23594,7 +23769,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1294</v>
       </c>
@@ -23614,7 +23789,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1297</v>
       </c>
@@ -23634,7 +23809,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1300</v>
       </c>
@@ -23654,18 +23829,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B40" s="15">
         <v>2024</v>
       </c>
       <c r="C40" s="49" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D40" s="49" t="s">
         <v>1351</v>
-      </c>
-      <c r="D40" s="49" t="s">
-        <v>1352</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>1044</v>
@@ -23674,18 +23849,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B41" s="15">
         <v>2024</v>
       </c>
       <c r="C41" s="49" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D41" s="49" t="s">
         <v>1353</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>1354</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>1044</v>
@@ -23694,18 +23869,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B42" s="15">
         <v>2024</v>
       </c>
       <c r="C42" s="49" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D42" s="49" t="s">
         <v>1357</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>1358</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>1044</v>
@@ -23717,18 +23892,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B43" s="15">
         <v>2024</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>1044</v>
@@ -23737,18 +23912,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B44" s="15">
         <v>2024</v>
       </c>
       <c r="C44" s="49" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D44" s="49" t="s">
         <v>1362</v>
-      </c>
-      <c r="D44" s="49" t="s">
-        <v>1363</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>1044</v>
@@ -23757,18 +23932,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B45" s="15">
         <v>2024</v>
       </c>
       <c r="C45" s="49" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D45" s="49" t="s">
         <v>1365</v>
-      </c>
-      <c r="D45" s="49" t="s">
-        <v>1366</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>1044</v>
@@ -23777,18 +23952,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B46" s="15">
         <v>2024</v>
       </c>
       <c r="C46" s="49" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D46" s="49" t="s">
         <v>1368</v>
-      </c>
-      <c r="D46" s="49" t="s">
-        <v>1369</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>1044</v>
@@ -23797,18 +23972,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B47" s="15">
         <v>2024</v>
       </c>
       <c r="C47" s="49" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D47" s="49" t="s">
         <v>1371</v>
-      </c>
-      <c r="D47" s="49" t="s">
-        <v>1372</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>1044</v>
@@ -23817,18 +23992,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B48" s="15">
         <v>2024</v>
       </c>
       <c r="C48" s="49" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D48" s="49" t="s">
         <v>1374</v>
-      </c>
-      <c r="D48" s="49" t="s">
-        <v>1375</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>1044</v>
@@ -23837,18 +24012,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B49" s="15">
         <v>2024</v>
       </c>
       <c r="C49" s="49" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D49" s="49" t="s">
         <v>1377</v>
-      </c>
-      <c r="D49" s="49" t="s">
-        <v>1378</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>1044</v>
@@ -23857,18 +24032,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B50" s="15">
         <v>2024</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>1044</v>
@@ -23877,18 +24052,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B51" s="15">
         <v>2024</v>
       </c>
       <c r="C51" s="49" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D51" s="49" t="s">
         <v>1383</v>
-      </c>
-      <c r="D51" s="49" t="s">
-        <v>1384</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>1044</v>
@@ -23897,18 +24072,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B52" s="15">
         <v>2024</v>
       </c>
       <c r="C52" s="49" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D52" s="49" t="s">
         <v>1386</v>
-      </c>
-      <c r="D52" s="49" t="s">
-        <v>1387</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>1044</v>
@@ -23917,18 +24092,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B53" s="15">
         <v>2024</v>
       </c>
       <c r="C53" s="49" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D53" s="49" t="s">
         <v>1389</v>
-      </c>
-      <c r="D53" s="49" t="s">
-        <v>1390</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1044</v>
@@ -23937,18 +24112,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B54" s="15">
         <v>2024</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>1044</v>
@@ -23957,18 +24132,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B55" s="15">
         <v>2024</v>
       </c>
       <c r="C55" s="49" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D55" s="49" t="s">
         <v>1395</v>
-      </c>
-      <c r="D55" s="49" t="s">
-        <v>1396</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>1044</v>
@@ -23977,18 +24152,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B56" s="15">
         <v>2024</v>
       </c>
       <c r="C56" s="49" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D56" s="49" t="s">
         <v>1398</v>
-      </c>
-      <c r="D56" s="49" t="s">
-        <v>1399</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>1044</v>
@@ -23997,18 +24172,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B57" s="15">
         <v>2024</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>1044</v>
@@ -24017,18 +24192,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B58" s="15">
         <v>2024</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>1044</v>
@@ -24037,18 +24212,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B59" s="15">
         <v>2024</v>
       </c>
       <c r="C59" s="49" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D59" s="49" t="s">
         <v>1407</v>
-      </c>
-      <c r="D59" s="49" t="s">
-        <v>1408</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>1044</v>
@@ -24057,18 +24232,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B60" s="15">
         <v>2024</v>
       </c>
       <c r="C60" s="49" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D60" s="49" t="s">
         <v>1410</v>
-      </c>
-      <c r="D60" s="49" t="s">
-        <v>1411</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>1044</v>
@@ -24077,18 +24252,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B61" s="15">
         <v>2024</v>
       </c>
       <c r="C61" s="49" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D61" s="49" t="s">
         <v>1413</v>
-      </c>
-      <c r="D61" s="49" t="s">
-        <v>1414</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>1044</v>
@@ -24097,18 +24272,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B62" s="15">
         <v>2024</v>
       </c>
       <c r="C62" s="49" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D62" s="49" t="s">
         <v>1416</v>
-      </c>
-      <c r="D62" s="49" t="s">
-        <v>1417</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>1044</v>
@@ -24117,18 +24292,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B63" s="15">
         <v>2024</v>
       </c>
       <c r="C63" s="49" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D63" s="49" t="s">
         <v>1419</v>
-      </c>
-      <c r="D63" s="49" t="s">
-        <v>1420</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>1044</v>
@@ -24137,18 +24312,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B64" s="15">
         <v>2024</v>
       </c>
       <c r="C64" s="49" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D64" s="49" t="s">
         <v>1422</v>
-      </c>
-      <c r="D64" s="49" t="s">
-        <v>1423</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>1044</v>
@@ -24157,18 +24332,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B65" s="15">
         <v>2024</v>
       </c>
       <c r="C65" s="49" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D65" s="49" t="s">
         <v>1425</v>
-      </c>
-      <c r="D65" s="49" t="s">
-        <v>1426</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>1044</v>
@@ -24177,18 +24352,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B66" s="15">
         <v>2024</v>
       </c>
       <c r="C66" s="49" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D66" s="49" t="s">
         <v>1428</v>
-      </c>
-      <c r="D66" s="49" t="s">
-        <v>1429</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>1044</v>
@@ -24197,18 +24372,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B67" s="15">
         <v>2024</v>
       </c>
       <c r="C67" s="49" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D67" s="49" t="s">
         <v>1431</v>
-      </c>
-      <c r="D67" s="49" t="s">
-        <v>1432</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>1044</v>
@@ -24217,18 +24392,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B68" s="15">
         <v>2024</v>
       </c>
       <c r="C68" s="49" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D68" s="49" t="s">
         <v>1434</v>
-      </c>
-      <c r="D68" s="49" t="s">
-        <v>1435</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>1044</v>
@@ -24237,18 +24412,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B69" s="15">
         <v>2024</v>
       </c>
       <c r="C69" s="49" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D69" s="49" t="s">
         <v>1437</v>
-      </c>
-      <c r="D69" s="49" t="s">
-        <v>1438</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>1044</v>
@@ -24257,18 +24432,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B70" s="15">
         <v>2024</v>
       </c>
       <c r="C70" s="49" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D70" s="49" t="s">
         <v>1440</v>
-      </c>
-      <c r="D70" s="49" t="s">
-        <v>1441</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>1044</v>
@@ -24277,18 +24452,18 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B71" s="15">
         <v>2024</v>
       </c>
       <c r="C71" s="49" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D71" s="49" t="s">
         <v>1442</v>
-      </c>
-      <c r="D71" s="49" t="s">
-        <v>1443</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>1044</v>
@@ -24297,55 +24472,55 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B72" s="15">
         <v>2024</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G72" s="48" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B73" s="15">
         <v>2024</v>
       </c>
       <c r="C73" s="49" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D73" s="49" t="s">
         <v>1459</v>
       </c>
-      <c r="D73" s="49" t="s">
-        <v>1460</v>
-      </c>
       <c r="E73" s="15" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G73" s="48" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B74" s="15">
         <v>2025</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>1044</v>
